--- a/research/traditional_assets/database/data/bangladesh/bangladesh_bank_money_center.xlsx
+++ b/research/traditional_assets/database/data/bangladesh/bangladesh_bank_money_center.xlsx
@@ -351,7 +351,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AQ31"/>
+  <dimension ref="A1:AQ30"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -579,7 +579,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>28</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -588,10 +588,10 @@
         </is>
       </c>
       <c r="D2">
-        <v>0.0916</v>
+        <v>0.0794</v>
       </c>
       <c r="E2">
-        <v>0.0857</v>
+        <v>0.04704999999999999</v>
       </c>
       <c r="G2">
         <v>0</v>
@@ -606,28 +606,28 @@
         <v>0</v>
       </c>
       <c r="K2">
-        <v>977.34</v>
+        <v>792.47</v>
       </c>
       <c r="L2">
-        <v>0.2093701799485861</v>
+        <v>0.1855945104100799</v>
       </c>
       <c r="M2">
-        <v>387.1346</v>
+        <v>267.53</v>
       </c>
       <c r="N2">
-        <v>0.04769018317996478</v>
+        <v>0.04518324607329843</v>
       </c>
       <c r="O2">
-        <v>0.3961104630937033</v>
+        <v>0.3375900665009401</v>
       </c>
       <c r="P2">
-        <v>387.1346</v>
+        <v>267.53</v>
       </c>
       <c r="Q2">
-        <v>0.04769018317996478</v>
+        <v>0.04518324607329843</v>
       </c>
       <c r="R2">
-        <v>0.3961104630937033</v>
+        <v>0.3375900665009401</v>
       </c>
       <c r="S2">
         <v>0</v>
@@ -636,55 +636,55 @@
         <v>0</v>
       </c>
       <c r="U2">
-        <v>8416.200000000001</v>
+        <v>7609.3</v>
       </c>
       <c r="V2">
-        <v>1.036771499316309</v>
+        <v>1.285137645667962</v>
       </c>
       <c r="W2">
-        <v>0.1230248306997743</v>
+        <v>0.09913406761412877</v>
       </c>
       <c r="X2">
-        <v>0.1113114638792151</v>
+        <v>0.1768210610502926</v>
       </c>
       <c r="Y2">
-        <v>0.01171336682055914</v>
+        <v>-0.07768699343616384</v>
       </c>
       <c r="Z2">
-        <v>0.4152766286797085</v>
+        <v>0.3020949038862908</v>
       </c>
       <c r="AA2">
         <v>0</v>
       </c>
       <c r="AB2">
-        <v>0.06420722949284918</v>
+        <v>0.09660123081038705</v>
       </c>
       <c r="AC2">
-        <v>-0.06420722949284918</v>
+        <v>-0.09660123081038705</v>
       </c>
       <c r="AD2">
-        <v>13091</v>
+        <v>13497.2</v>
       </c>
       <c r="AE2">
         <v>0</v>
       </c>
       <c r="AF2">
-        <v>13091</v>
+        <v>13497.2</v>
       </c>
       <c r="AG2">
-        <v>4674.799999999999</v>
+        <v>5887.900000000001</v>
       </c>
       <c r="AH2">
-        <v>0.6172466959313866</v>
+        <v>0.6950798735207177</v>
       </c>
       <c r="AI2">
-        <v>0.577301311507219</v>
+        <v>0.6135816050987843</v>
       </c>
       <c r="AJ2">
-        <v>0.3654328708227477</v>
+        <v>0.498598514679606</v>
       </c>
       <c r="AK2">
-        <v>0.3278260869565217</v>
+        <v>0.40922011940423</v>
       </c>
       <c r="AL2">
         <v>0</v>
@@ -710,10 +710,10 @@
         </is>
       </c>
       <c r="D3">
-        <v>0.0581</v>
+        <v>0.06900000000000001</v>
       </c>
       <c r="E3">
-        <v>0.0924</v>
+        <v>0.102</v>
       </c>
       <c r="G3">
         <v>0</v>
@@ -728,28 +728,28 @@
         <v>0</v>
       </c>
       <c r="K3">
-        <v>26.5</v>
+        <v>25</v>
       </c>
       <c r="L3">
-        <v>0.2347209920283437</v>
+        <v>0.2289377289377289</v>
       </c>
       <c r="M3">
-        <v>14.6</v>
+        <v>7.6</v>
       </c>
       <c r="N3">
-        <v>0.08649289099526065</v>
+        <v>0.05209047292666209</v>
       </c>
       <c r="O3">
-        <v>0.5509433962264151</v>
+        <v>0.304</v>
       </c>
       <c r="P3">
-        <v>14.6</v>
+        <v>7.6</v>
       </c>
       <c r="Q3">
-        <v>0.08649289099526065</v>
+        <v>0.05209047292666209</v>
       </c>
       <c r="R3">
-        <v>0.5509433962264151</v>
+        <v>0.304</v>
       </c>
       <c r="S3">
         <v>0</v>
@@ -758,55 +758,55 @@
         <v>0</v>
       </c>
       <c r="U3">
-        <v>204.8</v>
+        <v>128.1</v>
       </c>
       <c r="V3">
-        <v>1.213270142180095</v>
+        <v>0.8779986291980808</v>
       </c>
       <c r="W3">
-        <v>0.1322355289421158</v>
+        <v>0.1147315282239559</v>
       </c>
       <c r="X3">
-        <v>0.06443977659685442</v>
+        <v>0.09698392476578604</v>
       </c>
       <c r="Y3">
-        <v>0.06779575234526135</v>
+        <v>0.01774760345816989</v>
       </c>
       <c r="Z3">
-        <v>1.475816993464052</v>
+        <v>2.785714285714286</v>
       </c>
       <c r="AA3">
         <v>0</v>
       </c>
       <c r="AB3">
-        <v>0.06068917077635601</v>
+        <v>0.093120560684196</v>
       </c>
       <c r="AC3">
-        <v>-0.06068917077635601</v>
+        <v>-0.093120560684196</v>
       </c>
       <c r="AD3">
-        <v>26.1</v>
+        <v>17.9</v>
       </c>
       <c r="AE3">
         <v>0</v>
       </c>
       <c r="AF3">
-        <v>26.1</v>
+        <v>17.9</v>
       </c>
       <c r="AG3">
-        <v>-178.7</v>
+        <v>-110.2</v>
       </c>
       <c r="AH3">
-        <v>0.1339148281169831</v>
+        <v>0.1092796092796093</v>
       </c>
       <c r="AI3">
-        <v>0.1069672131147541</v>
+        <v>0.0838800374882849</v>
       </c>
       <c r="AJ3">
-        <v>18.05050505050504</v>
+        <v>-3.086834733893556</v>
       </c>
       <c r="AK3">
-        <v>-4.558673469387757</v>
+        <v>-1.291910902696366</v>
       </c>
       <c r="AL3">
         <v>0</v>
@@ -823,7 +823,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Rupali Bank Limited (DSE:RUPALIBANK)</t>
+          <t>National Bank Limited (DSE:NBL)</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -832,7 +832,7 @@
         </is>
       </c>
       <c r="D4">
-        <v>0.157</v>
+        <v>-0.146</v>
       </c>
       <c r="G4">
         <v>0</v>
@@ -847,85 +847,82 @@
         <v>0</v>
       </c>
       <c r="K4">
-        <v>1.93</v>
+        <v>-24.1</v>
       </c>
       <c r="L4">
-        <v>0.01403636363636364</v>
+        <v>-0.3990066225165563</v>
       </c>
       <c r="M4">
-        <v>5.0116</v>
+        <v>-0</v>
       </c>
       <c r="N4">
-        <v>0.02941079812206572</v>
+        <v>-0</v>
       </c>
       <c r="O4">
-        <v>2.596683937823834</v>
+        <v>0</v>
       </c>
       <c r="P4">
-        <v>5.0116</v>
+        <v>-0</v>
       </c>
       <c r="Q4">
-        <v>0.02941079812206572</v>
+        <v>-0</v>
       </c>
       <c r="R4">
-        <v>2.596683937823834</v>
+        <v>0</v>
       </c>
       <c r="S4">
         <v>0</v>
       </c>
-      <c r="T4">
-        <v>0</v>
-      </c>
       <c r="U4">
-        <v>434.4</v>
+        <v>44.8</v>
       </c>
       <c r="V4">
-        <v>2.549295774647887</v>
+        <v>0.1723739899961524</v>
       </c>
       <c r="W4">
-        <v>0.009400876765708718</v>
+        <v>-0.03855383138697809</v>
       </c>
       <c r="X4">
-        <v>0.0755455522055426</v>
+        <v>0.1151420024541229</v>
       </c>
       <c r="Y4">
-        <v>-0.06614467543983388</v>
+        <v>-0.153695833841101</v>
       </c>
       <c r="Z4">
-        <v>-7.947976878612711</v>
+        <v>0.07496586818915228</v>
       </c>
       <c r="AA4">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AB4">
-        <v>0.06211594248361207</v>
+        <v>0.0945949590042228</v>
       </c>
       <c r="AC4">
-        <v>-0.06211594248361207</v>
+        <v>-0.0945949590042228</v>
       </c>
       <c r="AD4">
-        <v>89.09999999999999</v>
+        <v>162</v>
       </c>
       <c r="AE4">
         <v>0</v>
       </c>
       <c r="AF4">
-        <v>89.09999999999999</v>
+        <v>162</v>
       </c>
       <c r="AG4">
-        <v>-345.3</v>
+        <v>117.2</v>
       </c>
       <c r="AH4">
-        <v>0.3433526011560694</v>
+        <v>0.3839772457928419</v>
       </c>
       <c r="AI4">
-        <v>0.2818728250553622</v>
+        <v>0.2328255245760276</v>
       </c>
       <c r="AJ4">
-        <v>1.974271012006861</v>
+        <v>0.3107928931317953</v>
       </c>
       <c r="AK4">
-        <v>2.918850380388843</v>
+        <v>0.1800307219662058</v>
       </c>
       <c r="AL4">
         <v>0</v>
@@ -942,7 +939,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>National Bank Limited (DSE:NBL)</t>
+          <t>Social Islami Bank Limited (DSE:SIBL)</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -951,10 +948,10 @@
         </is>
       </c>
       <c r="D5">
-        <v>0.00886</v>
+        <v>0.0454</v>
       </c>
       <c r="E5">
-        <v>-0.0555</v>
+        <v>-0.0097</v>
       </c>
       <c r="G5">
         <v>0</v>
@@ -969,82 +966,85 @@
         <v>0</v>
       </c>
       <c r="K5">
-        <v>42.4</v>
+        <v>21.4</v>
       </c>
       <c r="L5">
-        <v>0.2666666666666667</v>
+        <v>0.1975992613111727</v>
       </c>
       <c r="M5">
-        <v>-0</v>
+        <v>7.81</v>
       </c>
       <c r="N5">
-        <v>-0</v>
+        <v>0.06313662085691188</v>
       </c>
       <c r="O5">
-        <v>-0</v>
+        <v>0.3649532710280374</v>
       </c>
       <c r="P5">
-        <v>-0</v>
+        <v>7.81</v>
       </c>
       <c r="Q5">
-        <v>-0</v>
+        <v>0.06313662085691188</v>
       </c>
       <c r="R5">
-        <v>-0</v>
+        <v>0.3649532710280374</v>
       </c>
       <c r="S5">
         <v>0</v>
       </c>
+      <c r="T5">
+        <v>0</v>
+      </c>
       <c r="U5">
-        <v>46.5</v>
+        <v>190.4</v>
       </c>
       <c r="V5">
-        <v>0.1642529141646061</v>
+        <v>1.539207760711399</v>
       </c>
       <c r="W5">
-        <v>0.07100988109194439</v>
+        <v>0.09857208659603869</v>
       </c>
       <c r="X5">
-        <v>0.08091122217881</v>
+        <v>0.1224710781251746</v>
       </c>
       <c r="Y5">
-        <v>-0.009901341086865606</v>
+        <v>-0.02389899152913592</v>
       </c>
       <c r="Z5">
-        <v>0.2319474835886214</v>
+        <v>0.8561264822134389</v>
       </c>
       <c r="AA5">
         <v>0</v>
       </c>
       <c r="AB5">
-        <v>0.06258390657151086</v>
+        <v>0.09496097370654256</v>
       </c>
       <c r="AC5">
-        <v>-0.06258390657151086</v>
+        <v>-0.09496097370654256</v>
       </c>
       <c r="AD5">
-        <v>198.4</v>
+        <v>102.1</v>
       </c>
       <c r="AE5">
         <v>0</v>
       </c>
       <c r="AF5">
-        <v>198.4</v>
+        <v>102.1</v>
       </c>
       <c r="AG5">
-        <v>151.9</v>
+        <v>-88.30000000000001</v>
       </c>
       <c r="AH5">
-        <v>0.4120456905503634</v>
+        <v>0.4521700620017715</v>
       </c>
       <c r="AI5">
-        <v>0.2400483968542045</v>
+        <v>0.341929002009377</v>
       </c>
       <c r="AJ5">
-        <v>0.3491954022988506</v>
+        <v>-2.494350282485877</v>
       </c>
       <c r="AK5">
-        <v>0.1947435897435897</v>
+        <v>-0.8160813308687618</v>
       </c>
       <c r="AL5">
         <v>0</v>
@@ -1061,7 +1061,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Social Islami Bank Limited (DSE:SIBL)</t>
+          <t>Dutch-Bangla Bank Limited (DSE:DUTCHBANGL)</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -1070,10 +1070,10 @@
         </is>
       </c>
       <c r="D6">
-        <v>0.0478</v>
+        <v>0.104</v>
       </c>
       <c r="E6">
-        <v>-0.0684</v>
+        <v>0.195</v>
       </c>
       <c r="G6">
         <v>0</v>
@@ -1088,28 +1088,28 @@
         <v>0</v>
       </c>
       <c r="K6">
-        <v>19.3</v>
+        <v>55.6</v>
       </c>
       <c r="L6">
-        <v>0.1710992907801419</v>
+        <v>0.2052417866371355</v>
       </c>
       <c r="M6">
-        <v>10.8</v>
+        <v>11</v>
       </c>
       <c r="N6">
-        <v>0.06319485078993564</v>
+        <v>0.02596789423984891</v>
       </c>
       <c r="O6">
-        <v>0.5595854922279793</v>
+        <v>0.197841726618705</v>
       </c>
       <c r="P6">
-        <v>10.8</v>
+        <v>11</v>
       </c>
       <c r="Q6">
-        <v>0.06319485078993564</v>
+        <v>0.02596789423984891</v>
       </c>
       <c r="R6">
-        <v>0.5595854922279793</v>
+        <v>0.197841726618705</v>
       </c>
       <c r="S6">
         <v>0</v>
@@ -1118,55 +1118,55 @@
         <v>0</v>
       </c>
       <c r="U6">
-        <v>212.9</v>
+        <v>383</v>
       </c>
       <c r="V6">
-        <v>1.245757753071972</v>
+        <v>0.9041548630783758</v>
       </c>
       <c r="W6">
-        <v>0.09078080903104423</v>
+        <v>0.1335896203748198</v>
       </c>
       <c r="X6">
-        <v>0.08135786813288418</v>
+        <v>0.1322294543405071</v>
       </c>
       <c r="Y6">
-        <v>0.009422940898160051</v>
+        <v>0.00136016603431266</v>
       </c>
       <c r="Z6">
-        <v>1.009847806624888</v>
+        <v>0.5329529805233129</v>
       </c>
       <c r="AA6">
         <v>0</v>
       </c>
       <c r="AB6">
-        <v>0.06261848441004195</v>
+        <v>0.0953386889801916</v>
       </c>
       <c r="AC6">
-        <v>-0.06261848441004195</v>
+        <v>-0.0953386889801916</v>
       </c>
       <c r="AD6">
-        <v>122.3</v>
+        <v>463.6</v>
       </c>
       <c r="AE6">
         <v>0</v>
       </c>
       <c r="AF6">
-        <v>122.3</v>
+        <v>463.6</v>
       </c>
       <c r="AG6">
-        <v>-90.60000000000001</v>
+        <v>80.60000000000002</v>
       </c>
       <c r="AH6">
-        <v>0.4171214188267394</v>
+        <v>0.5225428313796213</v>
       </c>
       <c r="AI6">
-        <v>0.3603417796110784</v>
+        <v>0.5396345012222094</v>
       </c>
       <c r="AJ6">
-        <v>-1.12826899128269</v>
+        <v>0.1598571995239984</v>
       </c>
       <c r="AK6">
-        <v>-0.7162055335968381</v>
+        <v>0.1692921655114472</v>
       </c>
       <c r="AL6">
         <v>0</v>
@@ -1183,7 +1183,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>International Finance Investment and Commerce Bank Limited (DSE:IFIC)</t>
+          <t>Trust Bank Limited (DSE:TRUSTBANK)</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -1192,10 +1192,10 @@
         </is>
       </c>
       <c r="D7">
-        <v>0.0735</v>
+        <v>0.0926</v>
       </c>
       <c r="E7">
-        <v>0.1</v>
+        <v>0.0431</v>
       </c>
       <c r="G7">
         <v>0</v>
@@ -1210,82 +1210,85 @@
         <v>0</v>
       </c>
       <c r="K7">
-        <v>24.1</v>
+        <v>26.6</v>
       </c>
       <c r="L7">
-        <v>0.2058070025619129</v>
+        <v>0.2079749804534793</v>
       </c>
       <c r="M7">
-        <v>-0</v>
+        <v>8.779999999999999</v>
       </c>
       <c r="N7">
-        <v>-0</v>
+        <v>0.03323239969719909</v>
       </c>
       <c r="O7">
-        <v>-0</v>
+        <v>0.3300751879699247</v>
       </c>
       <c r="P7">
-        <v>-0</v>
+        <v>8.779999999999999</v>
       </c>
       <c r="Q7">
-        <v>-0</v>
+        <v>0.03323239969719909</v>
       </c>
       <c r="R7">
-        <v>-0</v>
+        <v>0.3300751879699247</v>
       </c>
       <c r="S7">
         <v>0</v>
       </c>
+      <c r="T7">
+        <v>0</v>
+      </c>
       <c r="U7">
-        <v>185.1</v>
+        <v>212.6</v>
       </c>
       <c r="V7">
-        <v>0.5494211932324132</v>
+        <v>0.8046934140802423</v>
       </c>
       <c r="W7">
-        <v>0.07385841250383084</v>
+        <v>0.1162587412587413</v>
       </c>
       <c r="X7">
-        <v>0.08329193373761731</v>
+        <v>0.1443175862524778</v>
       </c>
       <c r="Y7">
-        <v>-0.009433521233786477</v>
+        <v>-0.02805884499373658</v>
       </c>
       <c r="Z7">
-        <v>0.3366877515813686</v>
+        <v>0.2685282385051438</v>
       </c>
       <c r="AA7">
         <v>0</v>
       </c>
       <c r="AB7">
-        <v>0.06276157182841451</v>
+        <v>0.09569049581737207</v>
       </c>
       <c r="AC7">
-        <v>-0.06276157182841451</v>
+        <v>-0.09569049581737207</v>
       </c>
       <c r="AD7">
-        <v>262.7</v>
+        <v>377.2</v>
       </c>
       <c r="AE7">
         <v>0</v>
       </c>
       <c r="AF7">
-        <v>262.7</v>
+        <v>377.2</v>
       </c>
       <c r="AG7">
-        <v>77.59999999999999</v>
+        <v>164.6</v>
       </c>
       <c r="AH7">
-        <v>0.4381254169446298</v>
+        <v>0.5880885562831306</v>
       </c>
       <c r="AI7">
-        <v>0.4274324764074195</v>
+        <v>0.6522566142140758</v>
       </c>
       <c r="AJ7">
-        <v>0.1872135102533172</v>
+        <v>0.3838619402985075</v>
       </c>
       <c r="AK7">
-        <v>0.1806752037252619</v>
+        <v>0.4500957068635494</v>
       </c>
       <c r="AL7">
         <v>0</v>
@@ -1302,7 +1305,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Dutch-Bangla Bank Limited (DSE:DUTCHBANGL)</t>
+          <t>Jamuna Bank Limited (DSE:JAMUNABANK)</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -1311,10 +1314,10 @@
         </is>
       </c>
       <c r="D8">
-        <v>0.118</v>
+        <v>0.0779</v>
       </c>
       <c r="E8">
-        <v>0.166</v>
+        <v>0.0416</v>
       </c>
       <c r="G8">
         <v>0</v>
@@ -1329,28 +1332,28 @@
         <v>0</v>
       </c>
       <c r="K8">
-        <v>70.7</v>
+        <v>26.3</v>
       </c>
       <c r="L8">
-        <v>0.2186147186147187</v>
+        <v>0.2281006071118821</v>
       </c>
       <c r="M8">
-        <v>18.2</v>
+        <v>13</v>
       </c>
       <c r="N8">
-        <v>0.03143350604490501</v>
+        <v>0.08376288659793815</v>
       </c>
       <c r="O8">
-        <v>0.2574257425742574</v>
+        <v>0.4942965779467681</v>
       </c>
       <c r="P8">
-        <v>18.2</v>
+        <v>13</v>
       </c>
       <c r="Q8">
-        <v>0.03143350604490501</v>
+        <v>0.08376288659793815</v>
       </c>
       <c r="R8">
-        <v>0.2574257425742574</v>
+        <v>0.4942965779467681</v>
       </c>
       <c r="S8">
         <v>0</v>
@@ -1359,55 +1362,55 @@
         <v>0</v>
       </c>
       <c r="U8">
-        <v>170.3</v>
+        <v>33.7</v>
       </c>
       <c r="V8">
-        <v>0.2941278065630397</v>
+        <v>0.217139175257732</v>
       </c>
       <c r="W8">
-        <v>0.1990988453956632</v>
+        <v>0.0909405255878285</v>
       </c>
       <c r="X8">
-        <v>0.08738165362879295</v>
+        <v>0.1518240728003333</v>
       </c>
       <c r="Y8">
-        <v>0.1117171917668702</v>
+        <v>-0.06088354721250483</v>
       </c>
       <c r="Z8">
-        <v>0.5301639344262294</v>
+        <v>0.2181233446840712</v>
       </c>
       <c r="AA8">
         <v>0</v>
       </c>
       <c r="AB8">
-        <v>0.06303258645554896</v>
+        <v>0.09586416468941464</v>
       </c>
       <c r="AC8">
-        <v>-0.06303258645554896</v>
+        <v>-0.09586416468941464</v>
       </c>
       <c r="AD8">
-        <v>530</v>
+        <v>253.7</v>
       </c>
       <c r="AE8">
         <v>0</v>
       </c>
       <c r="AF8">
-        <v>530</v>
+        <v>253.7</v>
       </c>
       <c r="AG8">
-        <v>359.7</v>
+        <v>220</v>
       </c>
       <c r="AH8">
-        <v>0.4779080252479712</v>
+        <v>0.6204450966006358</v>
       </c>
       <c r="AI8">
-        <v>0.5601352779539209</v>
+        <v>0.5410535295372148</v>
       </c>
       <c r="AJ8">
-        <v>0.3831895174177053</v>
+        <v>0.5863539445628998</v>
       </c>
       <c r="AK8">
-        <v>0.4635906689006315</v>
+        <v>0.5055147058823529</v>
       </c>
       <c r="AL8">
         <v>0</v>
@@ -1433,10 +1436,10 @@
         </is>
       </c>
       <c r="D9">
-        <v>0.079</v>
+        <v>0.07490000000000001</v>
       </c>
       <c r="E9">
-        <v>0.079</v>
+        <v>0.0611</v>
       </c>
       <c r="G9">
         <v>0</v>
@@ -1451,28 +1454,28 @@
         <v>0</v>
       </c>
       <c r="K9">
-        <v>63.6</v>
+        <v>48.5</v>
       </c>
       <c r="L9">
-        <v>0.1409886943028153</v>
+        <v>0.1155036913550846</v>
       </c>
       <c r="M9">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="N9">
-        <v>0.0314621626097036</v>
+        <v>0.03096574414553899</v>
       </c>
       <c r="O9">
-        <v>0.2987421383647799</v>
+        <v>0.3298969072164948</v>
       </c>
       <c r="P9">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="Q9">
-        <v>0.0314621626097036</v>
+        <v>0.03096574414553899</v>
       </c>
       <c r="R9">
-        <v>0.2987421383647799</v>
+        <v>0.3298969072164948</v>
       </c>
       <c r="S9">
         <v>0</v>
@@ -1481,55 +1484,55 @@
         <v>0</v>
       </c>
       <c r="U9">
-        <v>988.1</v>
+        <v>1814.2</v>
       </c>
       <c r="V9">
-        <v>1.636198046034112</v>
+        <v>3.511128314302303</v>
       </c>
       <c r="W9">
-        <v>0.08772413793103448</v>
+        <v>0.06297883391767303</v>
       </c>
       <c r="X9">
-        <v>0.09471774826964137</v>
+        <v>0.1606595926875909</v>
       </c>
       <c r="Y9">
-        <v>-0.00699361033860689</v>
+        <v>-0.09768075876991783</v>
       </c>
       <c r="Z9">
-        <v>2.190869354055366</v>
+        <v>0.8717043803197008</v>
       </c>
       <c r="AA9">
         <v>0</v>
       </c>
       <c r="AB9">
-        <v>0.06343340276394795</v>
+        <v>0.096036582691678</v>
       </c>
       <c r="AC9">
-        <v>-0.06343340276394795</v>
+        <v>-0.096036582691678</v>
       </c>
       <c r="AD9">
-        <v>699.7</v>
+        <v>970.5</v>
       </c>
       <c r="AE9">
         <v>0</v>
       </c>
       <c r="AF9">
-        <v>699.7</v>
+        <v>970.5</v>
       </c>
       <c r="AG9">
-        <v>-288.4</v>
+        <v>-843.7</v>
       </c>
       <c r="AH9">
-        <v>0.5367444001227371</v>
+        <v>0.6525685852608929</v>
       </c>
       <c r="AI9">
-        <v>0.476051163423595</v>
+        <v>0.5895037356496386</v>
       </c>
       <c r="AJ9">
-        <v>-0.9141045958795562</v>
+        <v>2.580122324159022</v>
       </c>
       <c r="AK9">
-        <v>-0.598712891841395</v>
+        <v>5.025014889815364</v>
       </c>
       <c r="AL9">
         <v>0</v>
@@ -1546,7 +1549,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>NRB Commercial Bank Limited (DSE:NRBCBANK)</t>
+          <t>Southeast Bank Limited (DSE:SOUTHEASTB)</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1555,10 +1558,10 @@
         </is>
       </c>
       <c r="D10">
-        <v>0.264</v>
+        <v>0.00932</v>
       </c>
       <c r="E10">
-        <v>0.311</v>
+        <v>-0.09789999999999999</v>
       </c>
       <c r="G10">
         <v>0</v>
@@ -1573,28 +1576,28 @@
         <v>0</v>
       </c>
       <c r="K10">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="L10">
-        <v>0.241423125794155</v>
+        <v>0.1364877161055505</v>
       </c>
       <c r="M10">
-        <v>6.35</v>
+        <v>9.44</v>
       </c>
       <c r="N10">
-        <v>0.02792436235708003</v>
+        <v>0.05690174804098854</v>
       </c>
       <c r="O10">
-        <v>0.3342105263157895</v>
+        <v>0.6293333333333333</v>
       </c>
       <c r="P10">
-        <v>6.35</v>
+        <v>9.44</v>
       </c>
       <c r="Q10">
-        <v>0.02792436235708003</v>
+        <v>0.05690174804098854</v>
       </c>
       <c r="R10">
-        <v>0.3342105263157895</v>
+        <v>0.6293333333333333</v>
       </c>
       <c r="S10">
         <v>0</v>
@@ -1603,55 +1606,55 @@
         <v>0</v>
       </c>
       <c r="U10">
-        <v>71.8</v>
+        <v>295</v>
       </c>
       <c r="V10">
-        <v>0.3157431838170624</v>
+        <v>1.778179626280892</v>
       </c>
       <c r="W10">
-        <v>0.1997896950578339</v>
+        <v>0.03913383772501956</v>
       </c>
       <c r="X10">
-        <v>0.07310480890821415</v>
+        <v>0.1629542480237514</v>
       </c>
       <c r="Y10">
-        <v>0.1266848861496197</v>
+        <v>-0.1238204102987319</v>
       </c>
       <c r="Z10">
-        <v>1.067842605156038</v>
+        <v>0.1924356504990369</v>
       </c>
       <c r="AA10">
         <v>0</v>
       </c>
       <c r="AB10">
-        <v>0.0634505374846973</v>
+        <v>0.09607668966786923</v>
       </c>
       <c r="AC10">
-        <v>-0.0634505374846973</v>
+        <v>-0.09607668966786923</v>
       </c>
       <c r="AD10">
-        <v>100.5</v>
+        <v>322.1</v>
       </c>
       <c r="AE10">
         <v>0</v>
       </c>
       <c r="AF10">
-        <v>100.5</v>
+        <v>322.1</v>
       </c>
       <c r="AG10">
-        <v>28.7</v>
+        <v>27.10000000000002</v>
       </c>
       <c r="AH10">
-        <v>0.3064958828911253</v>
+        <v>0.6600409836065574</v>
       </c>
       <c r="AI10">
-        <v>0.415976821192053</v>
+        <v>0.4997672614429791</v>
       </c>
       <c r="AJ10">
-        <v>0.112065599375244</v>
+        <v>0.1404145077720208</v>
       </c>
       <c r="AK10">
-        <v>0.1690223792697291</v>
+        <v>0.07753934191702438</v>
       </c>
       <c r="AL10">
         <v>0</v>
@@ -1668,7 +1671,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Jamuna Bank Limited (DSE:JAMUNABANK)</t>
+          <t>National Credit and Commerce Bank Limited (DSE:NCCBANK)</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1677,10 +1680,10 @@
         </is>
       </c>
       <c r="D11">
-        <v>0.113</v>
+        <v>0.0675</v>
       </c>
       <c r="E11">
-        <v>0.131</v>
+        <v>0.0188</v>
       </c>
       <c r="G11">
         <v>0</v>
@@ -1695,28 +1698,28 @@
         <v>0</v>
       </c>
       <c r="K11">
-        <v>37.4</v>
+        <v>26.1</v>
       </c>
       <c r="L11">
-        <v>0.2850609756097561</v>
+        <v>0.2427906976744186</v>
       </c>
       <c r="M11">
-        <v>15.5</v>
+        <v>11.2</v>
       </c>
       <c r="N11">
-        <v>0.07542579075425791</v>
+        <v>0.07892882311486962</v>
       </c>
       <c r="O11">
-        <v>0.4144385026737968</v>
+        <v>0.4291187739463601</v>
       </c>
       <c r="P11">
-        <v>15.5</v>
+        <v>11.2</v>
       </c>
       <c r="Q11">
-        <v>0.07542579075425791</v>
+        <v>0.07892882311486962</v>
       </c>
       <c r="R11">
-        <v>0.4144385026737968</v>
+        <v>0.4291187739463601</v>
       </c>
       <c r="S11">
         <v>0</v>
@@ -1725,55 +1728,55 @@
         <v>0</v>
       </c>
       <c r="U11">
-        <v>37.2</v>
+        <v>73.09999999999999</v>
       </c>
       <c r="V11">
-        <v>0.181021897810219</v>
+        <v>0.5151515151515151</v>
       </c>
       <c r="W11">
-        <v>0.1547372776168804</v>
+        <v>0.1009280742459397</v>
       </c>
       <c r="X11">
-        <v>0.10036763967773</v>
+        <v>0.1719251795303436</v>
       </c>
       <c r="Y11">
-        <v>0.05436963793915039</v>
+        <v>-0.07099710528440391</v>
       </c>
       <c r="Z11">
-        <v>0.3071161048689138</v>
+        <v>0.2897574123989219</v>
       </c>
       <c r="AA11">
         <v>0</v>
       </c>
       <c r="AB11">
-        <v>0.06368543044080523</v>
+        <v>0.09621821517692285</v>
       </c>
       <c r="AC11">
-        <v>-0.06368543044080523</v>
+        <v>-0.09621821517692285</v>
       </c>
       <c r="AD11">
-        <v>276.6</v>
+        <v>310.6</v>
       </c>
       <c r="AE11">
         <v>0</v>
       </c>
       <c r="AF11">
-        <v>276.6</v>
+        <v>310.6</v>
       </c>
       <c r="AG11">
-        <v>239.4</v>
+        <v>237.5</v>
       </c>
       <c r="AH11">
-        <v>0.5737398879900436</v>
+        <v>0.6864088397790056</v>
       </c>
       <c r="AI11">
-        <v>0.4888653234358432</v>
+        <v>0.5730627306273063</v>
       </c>
       <c r="AJ11">
-        <v>0.5380984490896831</v>
+        <v>0.6259884027411703</v>
       </c>
       <c r="AK11">
-        <v>0.4528944381384791</v>
+        <v>0.5065045851994029</v>
       </c>
       <c r="AL11">
         <v>0</v>
@@ -1790,7 +1793,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Standard Bank Limited (DSE:STANDBANKL)</t>
+          <t>Pubali Bank Limited (DSE:PUBALIBANK)</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1799,10 +1802,10 @@
         </is>
       </c>
       <c r="D12">
-        <v>0.0554</v>
+        <v>0.0794</v>
       </c>
       <c r="E12">
-        <v>-0.0479</v>
+        <v>0.215</v>
       </c>
       <c r="G12">
         <v>0</v>
@@ -1817,28 +1820,28 @@
         <v>0</v>
       </c>
       <c r="K12">
-        <v>14.8</v>
+        <v>49.2</v>
       </c>
       <c r="L12">
-        <v>0.1733021077283372</v>
+        <v>0.2575916230366492</v>
       </c>
       <c r="M12">
-        <v>2.96</v>
+        <v>14.3</v>
       </c>
       <c r="N12">
-        <v>0.02289249806651198</v>
+        <v>0.05437262357414449</v>
       </c>
       <c r="O12">
-        <v>0.2</v>
+        <v>0.290650406504065</v>
       </c>
       <c r="P12">
-        <v>2.96</v>
+        <v>14.3</v>
       </c>
       <c r="Q12">
-        <v>0.02289249806651198</v>
+        <v>0.05437262357414449</v>
       </c>
       <c r="R12">
-        <v>0.2</v>
+        <v>0.290650406504065</v>
       </c>
       <c r="S12">
         <v>0</v>
@@ -1847,55 +1850,55 @@
         <v>0</v>
       </c>
       <c r="U12">
-        <v>220.1</v>
+        <v>150.9</v>
       </c>
       <c r="V12">
-        <v>1.702242846094354</v>
+        <v>0.5737642585551331</v>
       </c>
       <c r="W12">
-        <v>0.07868155236576289</v>
+        <v>0.09969604863221886</v>
       </c>
       <c r="X12">
-        <v>0.1020385343590284</v>
+        <v>0.1765353070777265</v>
       </c>
       <c r="Y12">
-        <v>-0.02335698199326547</v>
+        <v>-0.07683925844550764</v>
       </c>
       <c r="Z12">
-        <v>-9.704545454545443</v>
+        <v>0.3026941362916006</v>
       </c>
       <c r="AA12">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AB12">
-        <v>0.06375243023284111</v>
+        <v>0.09628273200744154</v>
       </c>
       <c r="AC12">
-        <v>-0.06375243023284111</v>
+        <v>-0.09628273200744154</v>
       </c>
       <c r="AD12">
-        <v>181.2</v>
+        <v>609.1</v>
       </c>
       <c r="AE12">
         <v>0</v>
       </c>
       <c r="AF12">
-        <v>181.2</v>
+        <v>609.1</v>
       </c>
       <c r="AG12">
-        <v>-38.90000000000001</v>
+        <v>458.2</v>
       </c>
       <c r="AH12">
-        <v>0.5835748792270531</v>
+        <v>0.6984290792340329</v>
       </c>
       <c r="AI12">
-        <v>0.4778481012658228</v>
+        <v>0.5902131782945736</v>
       </c>
       <c r="AJ12">
-        <v>-0.4303097345132744</v>
+        <v>0.6353300055463117</v>
       </c>
       <c r="AK12">
-        <v>-0.2445003142677562</v>
+        <v>0.5200317784587448</v>
       </c>
       <c r="AL12">
         <v>0</v>
@@ -1912,7 +1915,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Shahjalal Islami Bank Limited (DSE:SHAHJABANK)</t>
+          <t>Eastern Bank Limited (DSE:EBL)</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1921,10 +1924,10 @@
         </is>
       </c>
       <c r="D13">
-        <v>0.13</v>
+        <v>0.103</v>
       </c>
       <c r="E13">
-        <v>0.161</v>
+        <v>0.0877</v>
       </c>
       <c r="G13">
         <v>0</v>
@@ -1939,28 +1942,28 @@
         <v>0</v>
       </c>
       <c r="K13">
-        <v>34.5</v>
+        <v>46.2</v>
       </c>
       <c r="L13">
-        <v>0.290893760539629</v>
+        <v>0.2711267605633803</v>
       </c>
       <c r="M13">
-        <v>8.09</v>
+        <v>11.8</v>
       </c>
       <c r="N13">
-        <v>0.03076045627376426</v>
+        <v>0.03555287737270263</v>
       </c>
       <c r="O13">
-        <v>0.2344927536231884</v>
+        <v>0.2554112554112554</v>
       </c>
       <c r="P13">
-        <v>8.09</v>
+        <v>11.8</v>
       </c>
       <c r="Q13">
-        <v>0.03076045627376426</v>
+        <v>0.03555287737270263</v>
       </c>
       <c r="R13">
-        <v>0.2344927536231884</v>
+        <v>0.2554112554112554</v>
       </c>
       <c r="S13">
         <v>0</v>
@@ -1969,55 +1972,55 @@
         <v>0</v>
       </c>
       <c r="U13">
-        <v>72.5</v>
+        <v>236.7</v>
       </c>
       <c r="V13">
-        <v>0.2756653992395438</v>
+        <v>0.7131666164507382</v>
       </c>
       <c r="W13">
-        <v>0.1665861902462578</v>
+        <v>0.1255434782608696</v>
       </c>
       <c r="X13">
-        <v>0.1063194239949416</v>
+        <v>0.1771068150228587</v>
       </c>
       <c r="Y13">
-        <v>0.0602667662513162</v>
+        <v>-0.05156333676198915</v>
       </c>
       <c r="Z13">
-        <v>0.2651464341605186</v>
+        <v>0.2393258426966293</v>
       </c>
       <c r="AA13">
         <v>0</v>
       </c>
       <c r="AB13">
-        <v>0.06391076572176785</v>
+        <v>0.09629038707821198</v>
       </c>
       <c r="AC13">
-        <v>-0.06391076572176785</v>
+        <v>-0.09629038707821198</v>
       </c>
       <c r="AD13">
-        <v>405.9</v>
+        <v>773.9</v>
       </c>
       <c r="AE13">
         <v>0</v>
       </c>
       <c r="AF13">
-        <v>405.9</v>
+        <v>773.9</v>
       </c>
       <c r="AG13">
-        <v>333.4</v>
+        <v>537.2</v>
       </c>
       <c r="AH13">
-        <v>0.6068171625056062</v>
+        <v>0.6998553083740279</v>
       </c>
       <c r="AI13">
-        <v>0.6320460915602615</v>
+        <v>0.6938940195463105</v>
       </c>
       <c r="AJ13">
-        <v>0.5590207914151576</v>
+        <v>0.618110689218732</v>
       </c>
       <c r="AK13">
-        <v>0.5852202913814287</v>
+        <v>0.6114272706578648</v>
       </c>
       <c r="AL13">
         <v>0</v>
@@ -2034,7 +2037,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Pubali Bank Limited (DSE:PUBALIBANK)</t>
+          <t>Standard Bank Limited (DSE:STANDBANKL)</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -2043,10 +2046,10 @@
         </is>
       </c>
       <c r="D14">
-        <v>0.0872</v>
+        <v>0.046</v>
       </c>
       <c r="E14">
-        <v>0.225</v>
+        <v>-0.0741</v>
       </c>
       <c r="G14">
         <v>0</v>
@@ -2061,28 +2064,28 @@
         <v>0</v>
       </c>
       <c r="K14">
-        <v>62.9</v>
+        <v>7.71</v>
       </c>
       <c r="L14">
-        <v>0.2907998150716597</v>
+        <v>0.1166414523449319</v>
       </c>
       <c r="M14">
-        <v>18.8</v>
+        <v>3.16</v>
       </c>
       <c r="N14">
-        <v>0.05820433436532508</v>
+        <v>0.03476347634763476</v>
       </c>
       <c r="O14">
-        <v>0.2988871224165342</v>
+        <v>0.4098573281452659</v>
       </c>
       <c r="P14">
-        <v>18.8</v>
+        <v>3.16</v>
       </c>
       <c r="Q14">
-        <v>0.05820433436532508</v>
+        <v>0.03476347634763476</v>
       </c>
       <c r="R14">
-        <v>0.2988871224165342</v>
+        <v>0.4098573281452659</v>
       </c>
       <c r="S14">
         <v>0</v>
@@ -2091,55 +2094,55 @@
         <v>0</v>
       </c>
       <c r="U14">
-        <v>380.9</v>
+        <v>189.1</v>
       </c>
       <c r="V14">
-        <v>1.179256965944272</v>
+        <v>2.08030803080308</v>
       </c>
       <c r="W14">
-        <v>0.156936127744511</v>
+        <v>0.03893939393939394</v>
       </c>
       <c r="X14">
-        <v>0.1081773168821944</v>
+        <v>0.177643916370802</v>
       </c>
       <c r="Y14">
-        <v>0.04875881086231657</v>
+        <v>-0.138704522431408</v>
       </c>
       <c r="Z14">
-        <v>0.452510460251046</v>
+        <v>0.4154619736015084</v>
       </c>
       <c r="AA14">
         <v>0</v>
       </c>
       <c r="AB14">
-        <v>0.06397411300619105</v>
+        <v>0.09629751558211171</v>
       </c>
       <c r="AC14">
-        <v>-0.06397411300619105</v>
+        <v>-0.09629751558211171</v>
       </c>
       <c r="AD14">
-        <v>518.4</v>
+        <v>213.3</v>
       </c>
       <c r="AE14">
         <v>0</v>
       </c>
       <c r="AF14">
-        <v>518.4</v>
+        <v>213.3</v>
       </c>
       <c r="AG14">
-        <v>137.5</v>
+        <v>24.20000000000002</v>
       </c>
       <c r="AH14">
-        <v>0.6161159971476111</v>
+        <v>0.7011834319526626</v>
       </c>
       <c r="AI14">
-        <v>0.5123035873109991</v>
+        <v>0.5551795939614783</v>
       </c>
       <c r="AJ14">
-        <v>0.2985884907709012</v>
+        <v>0.2102519548218941</v>
       </c>
       <c r="AK14">
-        <v>0.2179080824088748</v>
+        <v>0.1240389543823681</v>
       </c>
       <c r="AL14">
         <v>0</v>
@@ -2156,7 +2159,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>National Credit and Commerce Bank Limited (DSE:NCCBANK)</t>
+          <t>Bank Asia Limited (DSE:BANKASIA)</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -2165,10 +2168,10 @@
         </is>
       </c>
       <c r="D15">
-        <v>0.128</v>
+        <v>0.06950000000000001</v>
       </c>
       <c r="E15">
-        <v>0.133</v>
+        <v>0.0555</v>
       </c>
       <c r="G15">
         <v>0</v>
@@ -2183,28 +2186,28 @@
         <v>0</v>
       </c>
       <c r="K15">
-        <v>31.1</v>
+        <v>30.8</v>
       </c>
       <c r="L15">
-        <v>0.2526401299756296</v>
+        <v>0.2256410256410256</v>
       </c>
       <c r="M15">
-        <v>24.8</v>
+        <v>17.6</v>
       </c>
       <c r="N15">
-        <v>0.1359649122807018</v>
+        <v>0.077125328659071</v>
       </c>
       <c r="O15">
-        <v>0.797427652733119</v>
+        <v>0.5714285714285715</v>
       </c>
       <c r="P15">
-        <v>24.8</v>
+        <v>17.6</v>
       </c>
       <c r="Q15">
-        <v>0.1359649122807018</v>
+        <v>0.077125328659071</v>
       </c>
       <c r="R15">
-        <v>0.797427652733119</v>
+        <v>0.5714285714285715</v>
       </c>
       <c r="S15">
         <v>0</v>
@@ -2213,55 +2216,55 @@
         <v>0</v>
       </c>
       <c r="U15">
-        <v>199.3</v>
+        <v>520</v>
       </c>
       <c r="V15">
-        <v>1.09265350877193</v>
+        <v>2.278702892199825</v>
       </c>
       <c r="W15">
-        <v>0.1309473684210526</v>
+        <v>0.0952970297029703</v>
       </c>
       <c r="X15">
-        <v>0.1113114638792151</v>
+        <v>0.1922698440882776</v>
       </c>
       <c r="Y15">
-        <v>0.01963590454183751</v>
+        <v>-0.09697281438530733</v>
       </c>
       <c r="Z15">
-        <v>0.574160447761194</v>
+        <v>0.2922912205567451</v>
       </c>
       <c r="AA15">
         <v>0</v>
       </c>
       <c r="AB15">
-        <v>0.06407444561841215</v>
+        <v>0.0964699917177953</v>
       </c>
       <c r="AC15">
-        <v>-0.06407444561841215</v>
+        <v>-0.0964699917177953</v>
       </c>
       <c r="AD15">
-        <v>311.7</v>
+        <v>627.5</v>
       </c>
       <c r="AE15">
         <v>0</v>
       </c>
       <c r="AF15">
-        <v>311.7</v>
+        <v>627.5</v>
       </c>
       <c r="AG15">
-        <v>112.4</v>
+        <v>107.5</v>
       </c>
       <c r="AH15">
-        <v>0.6308439587128111</v>
+        <v>0.7333177515484398</v>
       </c>
       <c r="AI15">
-        <v>0.5465544450289321</v>
+        <v>0.6886523266022827</v>
       </c>
       <c r="AJ15">
-        <v>0.3812754409769335</v>
+        <v>0.3202263926124516</v>
       </c>
       <c r="AK15">
-        <v>0.3029649595687331</v>
+        <v>0.2747955010224949</v>
       </c>
       <c r="AL15">
         <v>0</v>
@@ -2278,7 +2281,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Al-Arafah Islami Bank Limited (DSE:ALARABANK)</t>
+          <t>The Premier Bank Limited (DSE:PREMIERBAN)</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -2287,10 +2290,10 @@
         </is>
       </c>
       <c r="D16">
-        <v>0.04269999999999999</v>
+        <v>0.202</v>
       </c>
       <c r="E16">
-        <v>-0.005829999999999999</v>
+        <v>0.104</v>
       </c>
       <c r="G16">
         <v>0</v>
@@ -2305,28 +2308,28 @@
         <v>0</v>
       </c>
       <c r="K16">
-        <v>32.7</v>
+        <v>38.4</v>
       </c>
       <c r="L16">
-        <v>0.237300435413643</v>
+        <v>0.2121546961325967</v>
       </c>
       <c r="M16">
-        <v>18.8</v>
+        <v>13.9</v>
       </c>
       <c r="N16">
-        <v>0.05662650602409638</v>
+        <v>0.09366576819407008</v>
       </c>
       <c r="O16">
-        <v>0.5749235474006116</v>
+        <v>0.3619791666666667</v>
       </c>
       <c r="P16">
-        <v>18.8</v>
+        <v>13.9</v>
       </c>
       <c r="Q16">
-        <v>0.05662650602409638</v>
+        <v>0.09366576819407008</v>
       </c>
       <c r="R16">
-        <v>0.5749235474006116</v>
+        <v>0.3619791666666667</v>
       </c>
       <c r="S16">
         <v>0</v>
@@ -2335,55 +2338,55 @@
         <v>0</v>
       </c>
       <c r="U16">
-        <v>616.2</v>
+        <v>624</v>
       </c>
       <c r="V16">
-        <v>1.856024096385542</v>
+        <v>4.204851752021563</v>
       </c>
       <c r="W16">
-        <v>0.1230248306997743</v>
+        <v>0.1568627450980392</v>
       </c>
       <c r="X16">
-        <v>0.1138322280081736</v>
+        <v>0.1974592858349269</v>
       </c>
       <c r="Y16">
-        <v>0.00919260269160066</v>
+        <v>-0.04059654073688773</v>
       </c>
       <c r="Z16">
-        <v>0.5111275964391692</v>
+        <v>0.5055865921787708</v>
       </c>
       <c r="AA16">
         <v>0</v>
       </c>
       <c r="AB16">
-        <v>0.06414972333824481</v>
+        <v>0.09652259987527961</v>
       </c>
       <c r="AC16">
-        <v>-0.06414972333824481</v>
+        <v>-0.09652259987527961</v>
       </c>
       <c r="AD16">
-        <v>595.1</v>
+        <v>429.3</v>
       </c>
       <c r="AE16">
         <v>0</v>
       </c>
       <c r="AF16">
-        <v>595.1</v>
+        <v>429.3</v>
       </c>
       <c r="AG16">
-        <v>-21.10000000000002</v>
+        <v>-194.7</v>
       </c>
       <c r="AH16">
-        <v>0.6418940783087046</v>
+        <v>0.7431192660550459</v>
       </c>
       <c r="AI16">
-        <v>0.6640999888405312</v>
+        <v>0.644014401440144</v>
       </c>
       <c r="AJ16">
-        <v>-0.06786748150530725</v>
+        <v>4.205183585313176</v>
       </c>
       <c r="AK16">
-        <v>-0.07538406573776357</v>
+        <v>-4.570422535211265</v>
       </c>
       <c r="AL16">
         <v>0</v>
@@ -2400,7 +2403,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Trust Bank Limited (DSE:TRUSTBANK)</t>
+          <t>Prime Bank Limited (DSE:PRIMEBANK)</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -2409,10 +2412,10 @@
         </is>
       </c>
       <c r="D17">
-        <v>0.07139999999999999</v>
+        <v>0.0623</v>
       </c>
       <c r="E17">
-        <v>0.031</v>
+        <v>0.00273</v>
       </c>
       <c r="G17">
         <v>0</v>
@@ -2427,28 +2430,28 @@
         <v>0</v>
       </c>
       <c r="K17">
-        <v>23.7</v>
+        <v>34.5</v>
       </c>
       <c r="L17">
-        <v>0.191437802907916</v>
+        <v>0.2342158859470468</v>
       </c>
       <c r="M17">
-        <v>7.58</v>
+        <v>19.3</v>
       </c>
       <c r="N17">
-        <v>0.0274438812454743</v>
+        <v>0.0912961210974456</v>
       </c>
       <c r="O17">
-        <v>0.319831223628692</v>
+        <v>0.5594202898550725</v>
       </c>
       <c r="P17">
-        <v>7.58</v>
+        <v>19.3</v>
       </c>
       <c r="Q17">
-        <v>0.0274438812454743</v>
+        <v>0.0912961210974456</v>
       </c>
       <c r="R17">
-        <v>0.319831223628692</v>
+        <v>0.5594202898550725</v>
       </c>
       <c r="S17">
         <v>0</v>
@@ -2457,55 +2460,55 @@
         <v>0</v>
       </c>
       <c r="U17">
-        <v>266.2</v>
+        <v>110.6</v>
       </c>
       <c r="V17">
-        <v>0.9637943519188994</v>
+        <v>0.5231788079470199</v>
       </c>
       <c r="W17">
-        <v>0.1125890736342043</v>
+        <v>0.1009362200117027</v>
       </c>
       <c r="X17">
-        <v>0.1158652332648687</v>
+        <v>0.2156374103439929</v>
       </c>
       <c r="Y17">
-        <v>-0.003276159630664452</v>
+        <v>-0.1147011903322902</v>
       </c>
       <c r="Z17">
-        <v>0.3613543490951547</v>
+        <v>0.1839410589410589</v>
       </c>
       <c r="AA17">
         <v>0</v>
       </c>
       <c r="AB17">
-        <v>0.06420722949284918</v>
+        <v>0.09667986174549449</v>
       </c>
       <c r="AC17">
-        <v>-0.06420722949284918</v>
+        <v>-0.09667986174549449</v>
       </c>
       <c r="AD17">
-        <v>513.7</v>
+        <v>717.5</v>
       </c>
       <c r="AE17">
         <v>0</v>
       </c>
       <c r="AF17">
-        <v>513.7</v>
+        <v>717.5</v>
       </c>
       <c r="AG17">
-        <v>247.5000000000001</v>
+        <v>606.9</v>
       </c>
       <c r="AH17">
-        <v>0.6503354855044943</v>
+        <v>0.7724189902034665</v>
       </c>
       <c r="AI17">
-        <v>0.6899932840832774</v>
+        <v>0.7012999706773532</v>
       </c>
       <c r="AJ17">
-        <v>0.4725988161160971</v>
+        <v>0.7416595380667237</v>
       </c>
       <c r="AK17">
-        <v>0.5174576625548819</v>
+        <v>0.6650958904109588</v>
       </c>
       <c r="AL17">
         <v>0</v>
@@ -2522,7 +2525,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Eastern Bank Limited (DSE:EBL)</t>
+          <t>Export Import Bank of Bangladesh Limited (DSE:EXIMBANK)</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -2531,10 +2534,10 @@
         </is>
       </c>
       <c r="D18">
-        <v>0.096</v>
+        <v>0.0507</v>
       </c>
       <c r="E18">
-        <v>0.174</v>
+        <v>-0.0483</v>
       </c>
       <c r="G18">
         <v>0</v>
@@ -2549,28 +2552,28 @@
         <v>0</v>
       </c>
       <c r="K18">
-        <v>61.7</v>
+        <v>26.9</v>
       </c>
       <c r="L18">
-        <v>0.3429683157309616</v>
+        <v>0.2021036814425244</v>
       </c>
       <c r="M18">
-        <v>28.6</v>
+        <v>14.4</v>
       </c>
       <c r="N18">
-        <v>0.06643437862950058</v>
+        <v>0.09836065573770492</v>
       </c>
       <c r="O18">
-        <v>0.4635332252836304</v>
+        <v>0.5353159851301116</v>
       </c>
       <c r="P18">
-        <v>28.6</v>
+        <v>14.4</v>
       </c>
       <c r="Q18">
-        <v>0.06643437862950058</v>
+        <v>0.09836065573770492</v>
       </c>
       <c r="R18">
-        <v>0.4635332252836304</v>
+        <v>0.5353159851301116</v>
       </c>
       <c r="S18">
         <v>0</v>
@@ -2579,55 +2582,55 @@
         <v>0</v>
       </c>
       <c r="U18">
-        <v>476.6</v>
+        <v>85.7</v>
       </c>
       <c r="V18">
-        <v>1.107084785133566</v>
+        <v>0.5853825136612022</v>
       </c>
       <c r="W18">
-        <v>0.1798833819241983</v>
+        <v>0.07311769502582223</v>
       </c>
       <c r="X18">
-        <v>0.1172606380530745</v>
+        <v>0.228994202160215</v>
       </c>
       <c r="Y18">
-        <v>0.06262274387112371</v>
+        <v>-0.1558765071343928</v>
       </c>
       <c r="Z18">
-        <v>0.2176385192354222</v>
+        <v>0.1487317018661303</v>
       </c>
       <c r="AA18">
         <v>0</v>
       </c>
       <c r="AB18">
-        <v>0.06424515624590803</v>
+        <v>0.09677431755714666</v>
       </c>
       <c r="AC18">
-        <v>-0.06424515624590803</v>
+        <v>-0.09677431755714666</v>
       </c>
       <c r="AD18">
-        <v>820.6</v>
+        <v>550.8</v>
       </c>
       <c r="AE18">
         <v>0</v>
       </c>
       <c r="AF18">
-        <v>820.6</v>
+        <v>550.8</v>
       </c>
       <c r="AG18">
-        <v>344</v>
+        <v>465.1</v>
       </c>
       <c r="AH18">
-        <v>0.6559028055311327</v>
+        <v>0.7900172117039587</v>
       </c>
       <c r="AI18">
-        <v>0.690392057883224</v>
+        <v>0.6319412574575494</v>
       </c>
       <c r="AJ18">
-        <v>0.4441575209812783</v>
+        <v>0.7605887162714635</v>
       </c>
       <c r="AK18">
-        <v>0.4831460674157304</v>
+        <v>0.5918055732281461</v>
       </c>
       <c r="AL18">
         <v>0</v>
@@ -2644,7 +2647,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Bank Asia Limited (DSE:BANKASIA)</t>
+          <t>Mutual Trust Bank Limited (DSE:MTB)</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -2653,10 +2656,10 @@
         </is>
       </c>
       <c r="D19">
-        <v>0.1</v>
+        <v>0.177</v>
       </c>
       <c r="E19">
-        <v>0.059</v>
+        <v>0.339</v>
       </c>
       <c r="G19">
         <v>0</v>
@@ -2671,28 +2674,28 @@
         <v>0</v>
       </c>
       <c r="K19">
-        <v>29.2</v>
+        <v>42</v>
       </c>
       <c r="L19">
-        <v>0.1863433312061264</v>
+        <v>0.2888583218707015</v>
       </c>
       <c r="M19">
-        <v>26.1</v>
+        <v>4.48</v>
       </c>
       <c r="N19">
-        <v>0.08761329305135952</v>
+        <v>0.03085399449035813</v>
       </c>
       <c r="O19">
-        <v>0.8938356164383562</v>
+        <v>0.1066666666666667</v>
       </c>
       <c r="P19">
-        <v>26.1</v>
+        <v>4.48</v>
       </c>
       <c r="Q19">
-        <v>0.08761329305135952</v>
+        <v>0.03085399449035813</v>
       </c>
       <c r="R19">
-        <v>0.8938356164383562</v>
+        <v>0.1066666666666667</v>
       </c>
       <c r="S19">
         <v>0</v>
@@ -2701,55 +2704,55 @@
         <v>0</v>
       </c>
       <c r="U19">
-        <v>495.9</v>
+        <v>85.8</v>
       </c>
       <c r="V19">
-        <v>1.664652567975831</v>
+        <v>0.5909090909090909</v>
       </c>
       <c r="W19">
-        <v>0.09228824273072062</v>
+        <v>0.1981132075471698</v>
       </c>
       <c r="X19">
-        <v>0.1245347617320997</v>
+        <v>0.2319954465828366</v>
       </c>
       <c r="Y19">
-        <v>-0.03224651900137905</v>
+        <v>-0.03388223903566678</v>
       </c>
       <c r="Z19">
-        <v>0.3854858548585486</v>
+        <v>0.2132590202405398</v>
       </c>
       <c r="AA19">
         <v>0</v>
       </c>
       <c r="AB19">
-        <v>0.06442480635287706</v>
+        <v>0.0967935659461831</v>
       </c>
       <c r="AC19">
-        <v>-0.06442480635287706</v>
+        <v>-0.0967935659461831</v>
       </c>
       <c r="AD19">
-        <v>639.7</v>
+        <v>558.3</v>
       </c>
       <c r="AE19">
         <v>0</v>
       </c>
       <c r="AF19">
-        <v>639.7</v>
+        <v>558.3</v>
       </c>
       <c r="AG19">
-        <v>143.8000000000001</v>
+        <v>472.4999999999999</v>
       </c>
       <c r="AH19">
-        <v>0.682273890784983</v>
+        <v>0.7936034115138592</v>
       </c>
       <c r="AI19">
-        <v>0.6643472842455084</v>
+        <v>0.7208521626856036</v>
       </c>
       <c r="AJ19">
-        <v>0.3255603350690515</v>
+        <v>0.764934434191355</v>
       </c>
       <c r="AK19">
-        <v>0.3079229122055676</v>
+        <v>0.6860752141716276</v>
       </c>
       <c r="AL19">
         <v>0</v>
@@ -2766,7 +2769,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Prime Bank Limited (DSE:PRIMEBANK)</t>
+          <t>The City Bank Limited (DSE:CITYBANK)</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -2775,7 +2778,10 @@
         </is>
       </c>
       <c r="D20">
-        <v>0.15</v>
+        <v>0.103</v>
+      </c>
+      <c r="E20">
+        <v>0.051</v>
       </c>
       <c r="G20">
         <v>0</v>
@@ -2790,28 +2796,28 @@
         <v>0</v>
       </c>
       <c r="K20">
-        <v>38.4</v>
+        <v>54.3</v>
       </c>
       <c r="L20">
-        <v>0.2422712933753943</v>
+        <v>0.2410119840213049</v>
       </c>
       <c r="M20">
-        <v>33.2</v>
+        <v>13.4</v>
       </c>
       <c r="N20">
-        <v>0.1163279607568325</v>
+        <v>0.05265225933202358</v>
       </c>
       <c r="O20">
-        <v>0.8645833333333335</v>
+        <v>0.2467771639042357</v>
       </c>
       <c r="P20">
-        <v>33.2</v>
+        <v>13.4</v>
       </c>
       <c r="Q20">
-        <v>0.1163279607568325</v>
+        <v>0.05265225933202358</v>
       </c>
       <c r="R20">
-        <v>0.8645833333333335</v>
+        <v>0.2467771639042357</v>
       </c>
       <c r="S20">
         <v>0</v>
@@ -2820,55 +2826,55 @@
         <v>0</v>
       </c>
       <c r="U20">
-        <v>174.4</v>
+        <v>330</v>
       </c>
       <c r="V20">
-        <v>0.6110721793973372</v>
+        <v>1.296660117878192</v>
       </c>
       <c r="W20">
-        <v>0.1233140655105973</v>
+        <v>0.1433852653815685</v>
       </c>
       <c r="X20">
-        <v>0.1267053465556053</v>
+        <v>0.2350078166033056</v>
       </c>
       <c r="Y20">
-        <v>-0.003391281045007952</v>
+        <v>-0.0916225512217371</v>
       </c>
       <c r="Z20">
-        <v>0.2472313211667447</v>
+        <v>0.2770536153467781</v>
       </c>
       <c r="AA20">
         <v>0</v>
       </c>
       <c r="AB20">
-        <v>0.06447319855794925</v>
+        <v>0.09681223570168637</v>
       </c>
       <c r="AC20">
-        <v>-0.06447319855794925</v>
+        <v>-0.09681223570168637</v>
       </c>
       <c r="AD20">
-        <v>633.4</v>
+        <v>999.7</v>
       </c>
       <c r="AE20">
         <v>0</v>
       </c>
       <c r="AF20">
-        <v>633.4</v>
+        <v>999.7</v>
       </c>
       <c r="AG20">
-        <v>459</v>
+        <v>669.7</v>
       </c>
       <c r="AH20">
-        <v>0.6893774488463214</v>
+        <v>0.7970818051347472</v>
       </c>
       <c r="AI20">
-        <v>0.6495077932731746</v>
+        <v>0.7508637524410395</v>
       </c>
       <c r="AJ20">
-        <v>0.6166039763567974</v>
+        <v>0.7246267041765851</v>
       </c>
       <c r="AK20">
-        <v>0.5731768231768232</v>
+        <v>0.6687637307769123</v>
       </c>
       <c r="AL20">
         <v>0</v>
@@ -2885,7 +2891,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Southeast Bank Limited (DSE:SOUTHEASTB)</t>
+          <t>Dhaka Bank Limited (DSE:DHAKABANK)</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -2894,10 +2900,10 @@
         </is>
       </c>
       <c r="D21">
-        <v>0.00731</v>
+        <v>0.0916</v>
       </c>
       <c r="E21">
-        <v>0.00634</v>
+        <v>0.103</v>
       </c>
       <c r="G21">
         <v>0</v>
@@ -2912,28 +2918,28 @@
         <v>0</v>
       </c>
       <c r="K21">
-        <v>36.5</v>
+        <v>24.1</v>
       </c>
       <c r="L21">
-        <v>0.3004115226337449</v>
+        <v>0.2159498207885305</v>
       </c>
       <c r="M21">
-        <v>24.3</v>
+        <v>11.3</v>
       </c>
       <c r="N21">
-        <v>0.1125</v>
+        <v>0.09269893355209188</v>
       </c>
       <c r="O21">
-        <v>0.6657534246575343</v>
+        <v>0.4688796680497925</v>
       </c>
       <c r="P21">
-        <v>24.3</v>
+        <v>11.3</v>
       </c>
       <c r="Q21">
-        <v>0.1125</v>
+        <v>0.09269893355209188</v>
       </c>
       <c r="R21">
-        <v>0.6657534246575343</v>
+        <v>0.4688796680497925</v>
       </c>
       <c r="S21">
         <v>0</v>
@@ -2942,55 +2948,55 @@
         <v>0</v>
       </c>
       <c r="U21">
-        <v>304</v>
+        <v>128.2</v>
       </c>
       <c r="V21">
-        <v>1.407407407407407</v>
+        <v>1.051681706316653</v>
       </c>
       <c r="W21">
-        <v>0.09159347553324969</v>
+        <v>0.1000415110004151</v>
       </c>
       <c r="X21">
-        <v>0.1284396873324644</v>
+        <v>0.2549923668174693</v>
       </c>
       <c r="Y21">
-        <v>-0.03684621179921473</v>
+        <v>-0.1549508558170542</v>
       </c>
       <c r="Z21">
-        <v>0.6074999999999998</v>
+        <v>0.1703556708899405</v>
       </c>
       <c r="AA21">
         <v>0</v>
       </c>
       <c r="AB21">
-        <v>0.06451033697365789</v>
+        <v>0.09692176099867167</v>
       </c>
       <c r="AC21">
-        <v>-0.06451033697365789</v>
+        <v>-0.09692176099867167</v>
       </c>
       <c r="AD21">
-        <v>491.8</v>
+        <v>546</v>
       </c>
       <c r="AE21">
         <v>0</v>
       </c>
       <c r="AF21">
-        <v>491.8</v>
+        <v>546</v>
       </c>
       <c r="AG21">
-        <v>187.8</v>
+        <v>417.8</v>
       </c>
       <c r="AH21">
-        <v>0.6948290477536028</v>
+        <v>0.8174876478514748</v>
       </c>
       <c r="AI21">
-        <v>0.5619287020109689</v>
+        <v>0.7172884918549658</v>
       </c>
       <c r="AJ21">
-        <v>0.4650817236255572</v>
+        <v>0.7741337780248285</v>
       </c>
       <c r="AK21">
-        <v>0.328781512605042</v>
+        <v>0.6600315955766193</v>
       </c>
       <c r="AL21">
         <v>0</v>
@@ -3016,10 +3022,10 @@
         </is>
       </c>
       <c r="D22">
-        <v>0.117</v>
+        <v>0.156</v>
       </c>
       <c r="E22">
-        <v>0.132</v>
+        <v>0.249</v>
       </c>
       <c r="G22">
         <v>0</v>
@@ -3034,28 +3040,28 @@
         <v>0</v>
       </c>
       <c r="K22">
-        <v>33.2</v>
+        <v>33.4</v>
       </c>
       <c r="L22">
-        <v>0.2326559215136651</v>
+        <v>0.2191601049868766</v>
       </c>
       <c r="M22">
-        <v>5.59</v>
+        <v>3.56</v>
       </c>
       <c r="N22">
-        <v>0.03711819389110226</v>
+        <v>0.03570712136409228</v>
       </c>
       <c r="O22">
-        <v>0.1683734939759036</v>
+        <v>0.1065868263473054</v>
       </c>
       <c r="P22">
-        <v>5.59</v>
+        <v>3.56</v>
       </c>
       <c r="Q22">
-        <v>0.03711819389110226</v>
+        <v>0.03570712136409228</v>
       </c>
       <c r="R22">
-        <v>0.1683734939759036</v>
+        <v>0.1065868263473054</v>
       </c>
       <c r="S22">
         <v>0</v>
@@ -3064,55 +3070,55 @@
         <v>0</v>
       </c>
       <c r="U22">
-        <v>46.3</v>
+        <v>45.2</v>
       </c>
       <c r="V22">
-        <v>0.3074369189907039</v>
+        <v>0.4533600802407222</v>
       </c>
       <c r="W22">
-        <v>0.1689567430025445</v>
+        <v>0.1510628674807779</v>
       </c>
       <c r="X22">
-        <v>0.1344482619058278</v>
+        <v>0.273122360570509</v>
       </c>
       <c r="Y22">
-        <v>0.03450848109671678</v>
+        <v>-0.1220594930897311</v>
       </c>
       <c r="Z22">
-        <v>0.293440263212009</v>
+        <v>0.2782545188972065</v>
       </c>
       <c r="AA22">
         <v>0</v>
       </c>
       <c r="AB22">
-        <v>0.06462949840118232</v>
+        <v>0.09700365889794203</v>
       </c>
       <c r="AC22">
-        <v>-0.06462949840118232</v>
+        <v>-0.09700365889794203</v>
       </c>
       <c r="AD22">
-        <v>372.9</v>
+        <v>496.4</v>
       </c>
       <c r="AE22">
         <v>0</v>
       </c>
       <c r="AF22">
-        <v>372.9</v>
+        <v>496.4</v>
       </c>
       <c r="AG22">
-        <v>326.6</v>
+        <v>451.2</v>
       </c>
       <c r="AH22">
-        <v>0.7123209169054441</v>
+        <v>0.832746183526254</v>
       </c>
       <c r="AI22">
-        <v>0.6229535583027064</v>
+        <v>0.6993519301211609</v>
       </c>
       <c r="AJ22">
-        <v>0.684409052808047</v>
+        <v>0.8190234162279906</v>
       </c>
       <c r="AK22">
-        <v>0.5913452833604925</v>
+        <v>0.6789046042732471</v>
       </c>
       <c r="AL22">
         <v>0</v>
@@ -3129,7 +3135,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>The City Bank Limited (DSE:CITYBANK)</t>
+          <t>United Commercial Bank Limited (DSE:UCB)</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -3138,10 +3144,10 @@
         </is>
       </c>
       <c r="D23">
-        <v>0.101</v>
+        <v>0.08779999999999999</v>
       </c>
       <c r="E23">
-        <v>0.0357</v>
+        <v>-0.0697</v>
       </c>
       <c r="G23">
         <v>0</v>
@@ -3156,85 +3162,82 @@
         <v>0</v>
       </c>
       <c r="K23">
-        <v>52.4</v>
+        <v>22.1</v>
       </c>
       <c r="L23">
-        <v>0.2261545101424255</v>
+        <v>0.09464668094218416</v>
       </c>
       <c r="M23">
-        <v>21.2</v>
+        <v>-0</v>
       </c>
       <c r="N23">
-        <v>0.06207906295754026</v>
+        <v>-0</v>
       </c>
       <c r="O23">
-        <v>0.4045801526717557</v>
+        <v>-0</v>
       </c>
       <c r="P23">
-        <v>21.2</v>
+        <v>-0</v>
       </c>
       <c r="Q23">
-        <v>0.06207906295754026</v>
+        <v>-0</v>
       </c>
       <c r="R23">
-        <v>0.4045801526717557</v>
+        <v>-0</v>
       </c>
       <c r="S23">
         <v>0</v>
       </c>
-      <c r="T23">
-        <v>0</v>
-      </c>
       <c r="U23">
-        <v>412.8</v>
+        <v>223.8</v>
       </c>
       <c r="V23">
-        <v>1.208784773060029</v>
+        <v>1.258717660292463</v>
       </c>
       <c r="W23">
-        <v>0.1625310173697271</v>
+        <v>0.05060682390657202</v>
       </c>
       <c r="X23">
-        <v>0.1345995627101998</v>
+        <v>0.3189490161532329</v>
       </c>
       <c r="Y23">
-        <v>0.02793145465952723</v>
+        <v>-0.2683421922466609</v>
       </c>
       <c r="Z23">
-        <v>0.3051092968132736</v>
+        <v>0.2040905515252163</v>
       </c>
       <c r="AA23">
         <v>0</v>
       </c>
       <c r="AB23">
-        <v>0.0646323229182106</v>
+        <v>0.09716026838604841</v>
       </c>
       <c r="AC23">
-        <v>-0.0646323229182106</v>
+        <v>-0.09716026838604841</v>
       </c>
       <c r="AD23">
-        <v>847.3</v>
+        <v>1109.9</v>
       </c>
       <c r="AE23">
         <v>0</v>
       </c>
       <c r="AF23">
-        <v>847.3</v>
+        <v>1109.9</v>
       </c>
       <c r="AG23">
-        <v>434.4999999999999</v>
+        <v>886.1000000000001</v>
       </c>
       <c r="AH23">
-        <v>0.712735531628533</v>
+        <v>0.8619243612642696</v>
       </c>
       <c r="AI23">
-        <v>0.6911092985318107</v>
+        <v>0.7406245829440812</v>
       </c>
       <c r="AJ23">
-        <v>0.559922680412371</v>
+        <v>0.8328790299840211</v>
       </c>
       <c r="AK23">
-        <v>0.5343089030988687</v>
+        <v>0.6950894257922812</v>
       </c>
       <c r="AL23">
         <v>0</v>
@@ -3251,7 +3254,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>The Premier Bank Limited (DSE:PREMIERBAN)</t>
+          <t>NRB Commercial Bank Limited (DSE:NRBCBANK)</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -3260,10 +3263,10 @@
         </is>
       </c>
       <c r="D24">
-        <v>0.207</v>
+        <v>0.217</v>
       </c>
       <c r="E24">
-        <v>0.229</v>
+        <v>0.147</v>
       </c>
       <c r="G24">
         <v>0</v>
@@ -3278,28 +3281,28 @@
         <v>0</v>
       </c>
       <c r="K24">
-        <v>34.5</v>
+        <v>17.9</v>
       </c>
       <c r="L24">
-        <v>0.2019906323185011</v>
+        <v>0.2220843672456576</v>
       </c>
       <c r="M24">
-        <v>14.3</v>
+        <v>5.89</v>
       </c>
       <c r="N24">
-        <v>0.07848518111964875</v>
+        <v>0.04340456890198968</v>
       </c>
       <c r="O24">
-        <v>0.4144927536231884</v>
+        <v>0.329050279329609</v>
       </c>
       <c r="P24">
-        <v>14.3</v>
+        <v>5.89</v>
       </c>
       <c r="Q24">
-        <v>0.07848518111964875</v>
+        <v>0.04340456890198968</v>
       </c>
       <c r="R24">
-        <v>0.4144927536231884</v>
+        <v>0.329050279329609</v>
       </c>
       <c r="S24">
         <v>0</v>
@@ -3308,55 +3311,55 @@
         <v>0</v>
       </c>
       <c r="U24">
-        <v>643.3</v>
+        <v>62.7</v>
       </c>
       <c r="V24">
-        <v>3.530735455543359</v>
+        <v>0.4620486366985999</v>
       </c>
       <c r="W24">
-        <v>0.1462484103433658</v>
+        <v>0.1274928774928775</v>
       </c>
       <c r="X24">
-        <v>0.1451497211078037</v>
+        <v>0.1293390498235124</v>
       </c>
       <c r="Y24">
-        <v>0.001098689235562139</v>
+        <v>-0.001846172330634915</v>
       </c>
       <c r="Z24">
-        <v>5.693333333333333</v>
+        <v>0.4766410408042577</v>
       </c>
       <c r="AA24">
         <v>0</v>
       </c>
       <c r="AB24">
-        <v>0.06481103199228797</v>
+        <v>0.09785508618214127</v>
       </c>
       <c r="AC24">
-        <v>-0.06481103199228797</v>
+        <v>-0.09785508618214127</v>
       </c>
       <c r="AD24">
-        <v>515.8</v>
+        <v>137.7</v>
       </c>
       <c r="AE24">
         <v>0</v>
       </c>
       <c r="AF24">
-        <v>515.8</v>
+        <v>137.7</v>
       </c>
       <c r="AG24">
-        <v>-127.5</v>
+        <v>74.99999999999999</v>
       </c>
       <c r="AH24">
-        <v>0.7389684813753581</v>
+        <v>0.5036576444769568</v>
       </c>
       <c r="AI24">
-        <v>0.6709157127991675</v>
+        <v>0.5255725190839694</v>
       </c>
       <c r="AJ24">
-        <v>-2.330895795246801</v>
+        <v>0.3559563360227812</v>
       </c>
       <c r="AK24">
-        <v>-1.01593625498008</v>
+        <v>0.376317109884596</v>
       </c>
       <c r="AL24">
         <v>0</v>
@@ -3373,7 +3376,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Export Import Bank of Bangladesh Limited (DSE:EXIMBANK)</t>
+          <t>South Bangla Agriculture and Commerce Bank Limited (DSE:SBACBANK)</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -3381,12 +3384,6 @@
           <t>Bank (Money Center)</t>
         </is>
       </c>
-      <c r="D25">
-        <v>0.0224</v>
-      </c>
-      <c r="E25">
-        <v>-0.0339</v>
-      </c>
       <c r="G25">
         <v>0</v>
       </c>
@@ -3400,28 +3397,28 @@
         <v>0</v>
       </c>
       <c r="K25">
-        <v>29.5</v>
+        <v>4.82</v>
       </c>
       <c r="L25">
-        <v>0.2234848484848485</v>
+        <v>0.106401766004415</v>
       </c>
       <c r="M25">
-        <v>12.5</v>
+        <v>4.7</v>
       </c>
       <c r="N25">
-        <v>0.0580046403712297</v>
+        <v>0.0558858501783591</v>
       </c>
       <c r="O25">
-        <v>0.423728813559322</v>
+        <v>0.975103734439834</v>
       </c>
       <c r="P25">
-        <v>12.5</v>
+        <v>4.7</v>
       </c>
       <c r="Q25">
-        <v>0.0580046403712297</v>
+        <v>0.0558858501783591</v>
       </c>
       <c r="R25">
-        <v>0.423728813559322</v>
+        <v>0.975103734439834</v>
       </c>
       <c r="S25">
         <v>0</v>
@@ -3430,55 +3427,55 @@
         <v>0</v>
       </c>
       <c r="U25">
-        <v>83.5</v>
+        <v>34.7</v>
       </c>
       <c r="V25">
-        <v>0.3874709976798144</v>
+        <v>0.4126040428061832</v>
       </c>
       <c r="W25">
-        <v>0.08397381155707373</v>
+        <v>0.03618618618618619</v>
       </c>
       <c r="X25">
-        <v>0.1452097828354518</v>
+        <v>0.1233703812360858</v>
       </c>
       <c r="Y25">
-        <v>-0.0612359712783781</v>
+        <v>-0.08718419504989963</v>
       </c>
       <c r="Z25">
-        <v>0.1900647948164147</v>
+        <v>0.4773445732349844</v>
       </c>
       <c r="AA25">
         <v>0</v>
       </c>
       <c r="AB25">
-        <v>0.06481195598971204</v>
+        <v>0.09856733668593165</v>
       </c>
       <c r="AC25">
-        <v>-0.06481195598971204</v>
+        <v>-0.09856733668593165</v>
       </c>
       <c r="AD25">
-        <v>610.5</v>
+        <v>71.5</v>
       </c>
       <c r="AE25">
         <v>0</v>
       </c>
       <c r="AF25">
-        <v>610.5</v>
+        <v>71.5</v>
       </c>
       <c r="AG25">
-        <v>527</v>
+        <v>36.8</v>
       </c>
       <c r="AH25">
-        <v>0.7391041162227603</v>
+        <v>0.4595115681233933</v>
       </c>
       <c r="AI25">
-        <v>0.6239779231398201</v>
+        <v>0.3970016657412549</v>
       </c>
       <c r="AJ25">
-        <v>0.7097643097643098</v>
+        <v>0.304383788254756</v>
       </c>
       <c r="AK25">
-        <v>0.5888926136998548</v>
+        <v>0.2530949105914718</v>
       </c>
       <c r="AL25">
         <v>0</v>
@@ -3495,7 +3492,7 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Mutual Trust Bank Limited (DSE:MTB)</t>
+          <t>International Finance Investment and Commerce Bank Limited (DSE:IFIC)</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -3504,10 +3501,10 @@
         </is>
       </c>
       <c r="D26">
-        <v>0.08169999999999999</v>
+        <v>0.113</v>
       </c>
       <c r="E26">
-        <v>-0.131</v>
+        <v>0.0329</v>
       </c>
       <c r="G26">
         <v>0</v>
@@ -3522,10 +3519,10 @@
         <v>0</v>
       </c>
       <c r="K26">
-        <v>8.26</v>
+        <v>20.7</v>
       </c>
       <c r="L26">
-        <v>0.07213973799126637</v>
+        <v>0.169255928045789</v>
       </c>
       <c r="M26">
         <v>-0</v>
@@ -3549,55 +3546,55 @@
         <v>0</v>
       </c>
       <c r="U26">
-        <v>100</v>
+        <v>237.4</v>
       </c>
       <c r="V26">
-        <v>0.5356186395286556</v>
+        <v>1.188783174762143</v>
       </c>
       <c r="W26">
-        <v>0.0406496062992126</v>
+        <v>0.05882352941176471</v>
       </c>
       <c r="X26">
-        <v>0.1518143966997698</v>
+        <v>0.1512896255881976</v>
       </c>
       <c r="Y26">
-        <v>-0.1111647904005572</v>
+        <v>-0.09246609617643288</v>
       </c>
       <c r="Z26">
-        <v>0.2147009188074255</v>
+        <v>0.2977842707572438</v>
       </c>
       <c r="AA26">
         <v>0</v>
       </c>
       <c r="AB26">
-        <v>0.06490802046337758</v>
+        <v>0.09906637530407397</v>
       </c>
       <c r="AC26">
-        <v>-0.06490802046337758</v>
+        <v>-0.09906637530407397</v>
       </c>
       <c r="AD26">
-        <v>569.8</v>
+        <v>323.5</v>
       </c>
       <c r="AE26">
         <v>0</v>
       </c>
       <c r="AF26">
-        <v>569.8</v>
+        <v>323.5</v>
       </c>
       <c r="AG26">
-        <v>469.8</v>
+        <v>86.09999999999999</v>
       </c>
       <c r="AH26">
-        <v>0.7532055518836748</v>
+        <v>0.6183103975535168</v>
       </c>
       <c r="AI26">
-        <v>0.7288309030442568</v>
+        <v>0.5039725813989718</v>
       </c>
       <c r="AJ26">
-        <v>0.7156130997715155</v>
+        <v>0.301259622113366</v>
       </c>
       <c r="AK26">
-        <v>0.689058374889997</v>
+        <v>0.2128553770086526</v>
       </c>
       <c r="AL26">
         <v>0</v>
@@ -3614,7 +3611,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Dhaka Bank Limited (DSE:DHAKABANK)</t>
+          <t>AB Bank Limited (DSE:ABBANK)</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -3623,10 +3620,10 @@
         </is>
       </c>
       <c r="D27">
-        <v>0.103</v>
+        <v>0.07389999999999999</v>
       </c>
       <c r="E27">
-        <v>0.119</v>
+        <v>0.0106</v>
       </c>
       <c r="G27">
         <v>0</v>
@@ -3641,28 +3638,28 @@
         <v>0</v>
       </c>
       <c r="K27">
-        <v>27.6</v>
+        <v>7.94</v>
       </c>
       <c r="L27">
-        <v>0.2506811989100818</v>
+        <v>0.08546824542518837</v>
       </c>
       <c r="M27">
-        <v>6.33</v>
+        <v>4.31</v>
       </c>
       <c r="N27">
-        <v>0.04062901155327343</v>
+        <v>0.0519903498190591</v>
       </c>
       <c r="O27">
-        <v>0.2293478260869565</v>
+        <v>0.5428211586901762</v>
       </c>
       <c r="P27">
-        <v>6.33</v>
+        <v>4.31</v>
       </c>
       <c r="Q27">
-        <v>0.04062901155327343</v>
+        <v>0.0519903498190591</v>
       </c>
       <c r="R27">
-        <v>0.2293478260869565</v>
+        <v>0.5428211586901762</v>
       </c>
       <c r="S27">
         <v>0</v>
@@ -3671,55 +3668,55 @@
         <v>0</v>
       </c>
       <c r="U27">
-        <v>250.6</v>
+        <v>101</v>
       </c>
       <c r="V27">
-        <v>1.608472400513479</v>
+        <v>1.218335343787696</v>
       </c>
       <c r="W27">
-        <v>0.1252837040399455</v>
+        <v>0.02593076420640105</v>
       </c>
       <c r="X27">
-        <v>0.1884566595665615</v>
+        <v>0.1909761672036192</v>
       </c>
       <c r="Y27">
-        <v>-0.06317295552661592</v>
+        <v>-0.1650454029972181</v>
       </c>
       <c r="Z27">
-        <v>0.2213955358938267</v>
+        <v>0.1328281384043466</v>
       </c>
       <c r="AA27">
         <v>0</v>
       </c>
       <c r="AB27">
-        <v>0.06529587276698562</v>
+        <v>0.1002543540205364</v>
       </c>
       <c r="AC27">
-        <v>-0.06529587276698562</v>
+        <v>-0.1002543540205364</v>
       </c>
       <c r="AD27">
-        <v>664.8</v>
+        <v>225</v>
       </c>
       <c r="AE27">
         <v>0</v>
       </c>
       <c r="AF27">
-        <v>664.8</v>
+        <v>225</v>
       </c>
       <c r="AG27">
-        <v>414.1999999999999</v>
+        <v>124</v>
       </c>
       <c r="AH27">
-        <v>0.810138922739459</v>
+        <v>0.7307567392010393</v>
       </c>
       <c r="AI27">
-        <v>0.7340178867174562</v>
+        <v>0.4703177257525084</v>
       </c>
       <c r="AJ27">
-        <v>0.7266666666666666</v>
+        <v>0.5993233446109232</v>
       </c>
       <c r="AK27">
-        <v>0.632269882460693</v>
+        <v>0.3285638579756227</v>
       </c>
       <c r="AL27">
         <v>0</v>
@@ -3736,7 +3733,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>United Commercial Bank Limited (DSE:UCB)</t>
+          <t>Shahjalal Islami Bank Limited (DSE:SHAHJABANK)</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -3745,10 +3742,10 @@
         </is>
       </c>
       <c r="D28">
-        <v>0.0689</v>
+        <v>0.156</v>
       </c>
       <c r="E28">
-        <v>-0.0142</v>
+        <v>0.147</v>
       </c>
       <c r="G28">
         <v>0</v>
@@ -3763,28 +3760,28 @@
         <v>0</v>
       </c>
       <c r="K28">
-        <v>38.7</v>
+        <v>36.4</v>
       </c>
       <c r="L28">
-        <v>0.1536323938070663</v>
+        <v>0.2708333333333333</v>
       </c>
       <c r="M28">
-        <v>14</v>
+        <v>13.1</v>
       </c>
       <c r="N28">
-        <v>0.06105538595726123</v>
+        <v>0.06629554655870445</v>
       </c>
       <c r="O28">
-        <v>0.3617571059431524</v>
+        <v>0.3598901098901099</v>
       </c>
       <c r="P28">
-        <v>14</v>
+        <v>13.1</v>
       </c>
       <c r="Q28">
-        <v>0.06105538595726123</v>
+        <v>0.06629554655870445</v>
       </c>
       <c r="R28">
-        <v>0.3617571059431524</v>
+        <v>0.3598901098901099</v>
       </c>
       <c r="S28">
         <v>0</v>
@@ -3793,55 +3790,55 @@
         <v>0</v>
       </c>
       <c r="U28">
-        <v>339.3</v>
+        <v>117.7</v>
       </c>
       <c r="V28">
-        <v>1.479720889664195</v>
+        <v>0.5956477732793523</v>
       </c>
       <c r="W28">
-        <v>0.09361393323657476</v>
+        <v>0.155955441302485</v>
       </c>
       <c r="X28">
-        <v>0.1974359774743126</v>
+        <v>0.2014188288258651</v>
       </c>
       <c r="Y28">
-        <v>-0.1038220442377379</v>
+        <v>-0.04546338752338011</v>
       </c>
       <c r="Z28">
-        <v>0.2929410396557739</v>
+        <v>0.23712067748765</v>
       </c>
       <c r="AA28">
         <v>0</v>
       </c>
       <c r="AB28">
-        <v>0.06536507903524016</v>
+        <v>0.1023830665066036</v>
       </c>
       <c r="AC28">
-        <v>-0.06536507903524016</v>
+        <v>-0.1023830665066036</v>
       </c>
       <c r="AD28">
-        <v>1046.7</v>
+        <v>593.2</v>
       </c>
       <c r="AE28">
         <v>0</v>
       </c>
       <c r="AF28">
-        <v>1046.7</v>
+        <v>593.2</v>
       </c>
       <c r="AG28">
-        <v>707.4000000000001</v>
+        <v>475.5000000000001</v>
       </c>
       <c r="AH28">
-        <v>0.8202978056426332</v>
+        <v>0.750126454223571</v>
       </c>
       <c r="AI28">
-        <v>0.7056087366859917</v>
+        <v>0.728120780655456</v>
       </c>
       <c r="AJ28">
-        <v>0.7552044411230918</v>
+        <v>0.7064329222998069</v>
       </c>
       <c r="AK28">
-        <v>0.6183025959269295</v>
+        <v>0.6822094691535151</v>
       </c>
       <c r="AL28">
         <v>0</v>
@@ -3858,7 +3855,7 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>South Bangla Agriculture and Commerce Bank Limited (DSE:SBACBANK)</t>
+          <t>Al-Arafah Islami Bank Limited (DSE:ALARABANK)</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -3866,6 +3863,12 @@
           <t>Bank (Money Center)</t>
         </is>
       </c>
+      <c r="D29">
+        <v>0.0374</v>
+      </c>
+      <c r="E29">
+        <v>-0.0759</v>
+      </c>
       <c r="G29">
         <v>0</v>
       </c>
@@ -3879,28 +3882,28 @@
         <v>0</v>
       </c>
       <c r="K29">
-        <v>8.91</v>
+        <v>22.5</v>
       </c>
       <c r="L29">
-        <v>0.225</v>
+        <v>0.1596877217885025</v>
       </c>
       <c r="M29">
-        <v>3.923</v>
+        <v>17.1</v>
       </c>
       <c r="N29">
-        <v>0.02806151645207439</v>
+        <v>0.06996726677577741</v>
       </c>
       <c r="O29">
-        <v>0.4402918069584736</v>
+        <v>0.76</v>
       </c>
       <c r="P29">
-        <v>3.923</v>
+        <v>17.1</v>
       </c>
       <c r="Q29">
-        <v>0.02806151645207439</v>
+        <v>0.06996726677577741</v>
       </c>
       <c r="R29">
-        <v>0.4402918069584736</v>
+        <v>0.76</v>
       </c>
       <c r="S29">
         <v>0</v>
@@ -3909,55 +3912,55 @@
         <v>0</v>
       </c>
       <c r="U29">
-        <v>170.4</v>
+        <v>605.5</v>
       </c>
       <c r="V29">
-        <v>1.218884120171674</v>
+        <v>2.477495908346972</v>
       </c>
       <c r="W29">
-        <v>0.08374060150375939</v>
+        <v>0.08143322475570032</v>
       </c>
       <c r="X29">
-        <v>0.0882727896482422</v>
+        <v>0.2082462927398155</v>
       </c>
       <c r="Y29">
-        <v>-0.004532188144482807</v>
+        <v>-0.1268130679841152</v>
       </c>
       <c r="Z29">
-        <v>1.171597633136095</v>
+        <v>0.9337309476474481</v>
       </c>
       <c r="AA29">
         <v>0</v>
       </c>
       <c r="AB29">
-        <v>0.06560015307262737</v>
+        <v>0.1025304487600801</v>
       </c>
       <c r="AC29">
-        <v>-0.06560015307262737</v>
+        <v>-0.1025304487600801</v>
       </c>
       <c r="AD29">
-        <v>132.1</v>
+        <v>779.7</v>
       </c>
       <c r="AE29">
         <v>0</v>
       </c>
       <c r="AF29">
-        <v>132.1</v>
+        <v>779.7</v>
       </c>
       <c r="AG29">
-        <v>-38.30000000000001</v>
+        <v>174.2</v>
       </c>
       <c r="AH29">
-        <v>0.4858403824935638</v>
+        <v>0.7613514305243628</v>
       </c>
       <c r="AI29">
-        <v>0.4979268752355824</v>
+        <v>0.740315229775921</v>
       </c>
       <c r="AJ29">
-        <v>-0.3773399014778326</v>
+        <v>0.4161490683229814</v>
       </c>
       <c r="AK29">
-        <v>-0.403582718651212</v>
+        <v>0.3890998436452983</v>
       </c>
       <c r="AL29">
         <v>0</v>
@@ -3983,10 +3986,10 @@
         </is>
       </c>
       <c r="D30">
-        <v>0.107</v>
+        <v>0.0866</v>
       </c>
       <c r="E30">
-        <v>0.124</v>
+        <v>0.006750000000000001</v>
       </c>
       <c r="G30">
         <v>0</v>
@@ -4001,28 +4004,28 @@
         <v>0</v>
       </c>
       <c r="K30">
-        <v>67.59999999999999</v>
+        <v>52.2</v>
       </c>
       <c r="L30">
-        <v>0.1966831539132965</v>
+        <v>0.1578947368421053</v>
       </c>
       <c r="M30">
-        <v>26.6</v>
+        <v>10.4</v>
       </c>
       <c r="N30">
-        <v>0.02947695035460993</v>
+        <v>0.01856148491879351</v>
       </c>
       <c r="O30">
-        <v>0.3934911242603551</v>
+        <v>0.1992337164750958</v>
       </c>
       <c r="P30">
-        <v>26.6</v>
+        <v>10.4</v>
       </c>
       <c r="Q30">
-        <v>0.02947695035460993</v>
+        <v>0.01856148491879351</v>
       </c>
       <c r="R30">
-        <v>0.3934911242603551</v>
+        <v>0.1992337164750958</v>
       </c>
       <c r="S30">
         <v>0</v>
@@ -4031,179 +4034,60 @@
         <v>0</v>
       </c>
       <c r="U30">
-        <v>724.6</v>
+        <v>545.4</v>
       </c>
       <c r="V30">
-        <v>0.8029698581560284</v>
+        <v>0.9734071033374978</v>
       </c>
       <c r="W30">
-        <v>0.1279333838001514</v>
+        <v>0.09031141868512112</v>
       </c>
       <c r="X30">
-        <v>0.07424044008067268</v>
+        <v>0.1414211389350766</v>
       </c>
       <c r="Y30">
-        <v>0.05369294371947872</v>
+        <v>-0.05110972024995551</v>
       </c>
       <c r="Z30">
-        <v>0.8736654804270464</v>
+        <v>1.2271714922049</v>
       </c>
       <c r="AA30">
         <v>0</v>
       </c>
       <c r="AB30">
-        <v>0.067067040075259</v>
+        <v>0.1099529033286276</v>
       </c>
       <c r="AC30">
-        <v>-0.067067040075259</v>
+        <v>-0.1099529033286276</v>
       </c>
       <c r="AD30">
-        <v>432.8</v>
+        <v>755.2</v>
       </c>
       <c r="AE30">
         <v>0</v>
       </c>
       <c r="AF30">
-        <v>432.8</v>
+        <v>755.2</v>
       </c>
       <c r="AG30">
-        <v>-291.8</v>
+        <v>209.8000000000001</v>
       </c>
       <c r="AH30">
-        <v>0.3241461953265428</v>
+        <v>0.5740782972253896</v>
       </c>
       <c r="AI30">
-        <v>0.4043726058114547</v>
+        <v>0.4901668072953853</v>
       </c>
       <c r="AJ30">
-        <v>-0.4778905994104161</v>
+        <v>0.2724321516686146</v>
       </c>
       <c r="AK30">
-        <v>-0.8440844663002603</v>
+        <v>0.2107907163669246</v>
       </c>
       <c r="AL30">
         <v>0</v>
       </c>
       <c r="AM30">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" t="inlineStr">
-        <is>
-          <t>Bangladesh</t>
-        </is>
-      </c>
-      <c r="B31" t="inlineStr">
-        <is>
-          <t>AB Bank Limited (DSE:ABBANK)</t>
-        </is>
-      </c>
-      <c r="C31" t="inlineStr">
-        <is>
-          <t>Bank (Money Center)</t>
-        </is>
-      </c>
-      <c r="D31">
-        <v>-0.0384</v>
-      </c>
-      <c r="E31">
-        <v>-0.212</v>
-      </c>
-      <c r="G31">
-        <v>0</v>
-      </c>
-      <c r="H31">
-        <v>0</v>
-      </c>
-      <c r="I31">
-        <v>0</v>
-      </c>
-      <c r="J31">
-        <v>0</v>
-      </c>
-      <c r="K31">
-        <v>6.24</v>
-      </c>
-      <c r="L31">
-        <v>0.07281213535589265</v>
-      </c>
-      <c r="M31">
-        <v>-0</v>
-      </c>
-      <c r="N31">
-        <v>-0</v>
-      </c>
-      <c r="O31">
-        <v>-0</v>
-      </c>
-      <c r="P31">
-        <v>-0</v>
-      </c>
-      <c r="Q31">
-        <v>-0</v>
-      </c>
-      <c r="R31">
-        <v>-0</v>
-      </c>
-      <c r="S31">
-        <v>0</v>
-      </c>
-      <c r="U31">
-        <v>88.2</v>
-      </c>
-      <c r="V31">
-        <v>0.6666666666666666</v>
-      </c>
-      <c r="W31">
-        <v>0.0214065180102916</v>
-      </c>
-      <c r="X31">
-        <v>0.1695088052229842</v>
-      </c>
-      <c r="Y31">
-        <v>-0.1481022872126926</v>
-      </c>
-      <c r="Z31">
-        <v>0.1394629780309194</v>
-      </c>
-      <c r="AA31">
-        <v>0</v>
-      </c>
-      <c r="AB31">
-        <v>0.0675657499833533</v>
-      </c>
-      <c r="AC31">
-        <v>-0.0675657499833533</v>
-      </c>
-      <c r="AD31">
-        <v>481.4</v>
-      </c>
-      <c r="AE31">
-        <v>0</v>
-      </c>
-      <c r="AF31">
-        <v>481.4</v>
-      </c>
-      <c r="AG31">
-        <v>393.2</v>
-      </c>
-      <c r="AH31">
-        <v>0.7844223562000977</v>
-      </c>
-      <c r="AI31">
-        <v>0.611068799187611</v>
-      </c>
-      <c r="AJ31">
-        <v>0.7482397716460514</v>
-      </c>
-      <c r="AK31">
-        <v>0.5620354488279017</v>
-      </c>
-      <c r="AL31">
-        <v>0</v>
-      </c>
-      <c r="AM31">
         <v>0</v>
       </c>
     </row>

--- a/research/traditional_assets/database/data/bangladesh/bangladesh_bank_money_center.xlsx
+++ b/research/traditional_assets/database/data/bangladesh/bangladesh_bank_money_center.xlsx
@@ -351,7 +351,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AQ30"/>
+  <dimension ref="A1:AQ31"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -579,7 +579,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>28</t>
+          <t>29</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -588,10 +588,10 @@
         </is>
       </c>
       <c r="D2">
-        <v>0.0794</v>
+        <v>0.09375</v>
       </c>
       <c r="E2">
-        <v>0.04704999999999999</v>
+        <v>0.109</v>
       </c>
       <c r="G2">
         <v>0</v>
@@ -606,28 +606,28 @@
         <v>0</v>
       </c>
       <c r="K2">
-        <v>792.47</v>
+        <v>410.6</v>
       </c>
       <c r="L2">
-        <v>0.1855945104100799</v>
+        <v>0.1075432163436354</v>
       </c>
       <c r="M2">
-        <v>267.53</v>
+        <v>221.0512</v>
       </c>
       <c r="N2">
-        <v>0.04518324607329843</v>
+        <v>0.04166453680143248</v>
       </c>
       <c r="O2">
-        <v>0.3375900665009401</v>
+        <v>0.5383614223088165</v>
       </c>
       <c r="P2">
-        <v>267.53</v>
+        <v>221.0512</v>
       </c>
       <c r="Q2">
-        <v>0.04518324607329843</v>
+        <v>0.04166453680143248</v>
       </c>
       <c r="R2">
-        <v>0.3375900665009401</v>
+        <v>0.5383614223088165</v>
       </c>
       <c r="S2">
         <v>0</v>
@@ -636,55 +636,55 @@
         <v>0</v>
       </c>
       <c r="U2">
-        <v>7609.3</v>
+        <v>5593.1</v>
       </c>
       <c r="V2">
-        <v>1.285137645667962</v>
+        <v>1.054207897464895</v>
       </c>
       <c r="W2">
-        <v>0.09913406761412877</v>
+        <v>0.1041486603284356</v>
       </c>
       <c r="X2">
-        <v>0.1768210610502926</v>
+        <v>0.1478889422349866</v>
       </c>
       <c r="Y2">
-        <v>-0.07768699343616384</v>
+        <v>-0.04374028190655102</v>
       </c>
       <c r="Z2">
-        <v>0.3020949038862908</v>
+        <v>0.2588351739239493</v>
       </c>
       <c r="AA2">
         <v>0</v>
       </c>
       <c r="AB2">
-        <v>0.09660123081038705</v>
+        <v>0.09333421013511942</v>
       </c>
       <c r="AC2">
-        <v>-0.09660123081038705</v>
+        <v>-0.09333421013511942</v>
       </c>
       <c r="AD2">
-        <v>13497.2</v>
+        <v>11384.7</v>
       </c>
       <c r="AE2">
         <v>0</v>
       </c>
       <c r="AF2">
-        <v>13497.2</v>
+        <v>11384.7</v>
       </c>
       <c r="AG2">
-        <v>5887.900000000001</v>
+        <v>5791.6</v>
       </c>
       <c r="AH2">
-        <v>0.6950798735207177</v>
+        <v>0.6821188481863609</v>
       </c>
       <c r="AI2">
-        <v>0.6135816050987843</v>
+        <v>0.6025436108053179</v>
       </c>
       <c r="AJ2">
-        <v>0.498598514679606</v>
+        <v>0.5219021185715187</v>
       </c>
       <c r="AK2">
-        <v>0.40922011940423</v>
+        <v>0.4354160871493764</v>
       </c>
       <c r="AL2">
         <v>0</v>
@@ -701,7 +701,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Uttara Bank Limited (DSE:UTTARABANK)</t>
+          <t>Rupali Bank PLC. (DSE:RUPALIBANK)</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -710,10 +710,10 @@
         </is>
       </c>
       <c r="D3">
-        <v>0.06900000000000001</v>
+        <v>0.09230000000000001</v>
       </c>
       <c r="E3">
-        <v>0.102</v>
+        <v>0.0374</v>
       </c>
       <c r="G3">
         <v>0</v>
@@ -728,85 +728,76 @@
         <v>0</v>
       </c>
       <c r="K3">
-        <v>25</v>
+        <v>5.68</v>
       </c>
       <c r="L3">
-        <v>0.2289377289377289</v>
+        <v>0.04522292993630573</v>
       </c>
       <c r="M3">
-        <v>7.6</v>
+        <v>-0</v>
       </c>
       <c r="N3">
-        <v>0.05209047292666209</v>
+        <v>-0</v>
       </c>
       <c r="O3">
-        <v>0.304</v>
+        <v>-0</v>
       </c>
       <c r="P3">
-        <v>7.6</v>
+        <v>-0</v>
       </c>
       <c r="Q3">
-        <v>0.05209047292666209</v>
+        <v>-0</v>
       </c>
       <c r="R3">
-        <v>0.304</v>
+        <v>-0</v>
       </c>
       <c r="S3">
         <v>0</v>
       </c>
-      <c r="T3">
-        <v>0</v>
-      </c>
       <c r="U3">
-        <v>128.1</v>
+        <v>0</v>
       </c>
       <c r="V3">
-        <v>0.8779986291980808</v>
+        <v>0</v>
       </c>
       <c r="W3">
-        <v>0.1147315282239559</v>
+        <v>0.03343143025309005</v>
       </c>
       <c r="X3">
-        <v>0.09698392476578604</v>
+        <v>0.0828224625095878</v>
       </c>
       <c r="Y3">
-        <v>0.01774760345816989</v>
+        <v>-0.04939103225649775</v>
       </c>
       <c r="Z3">
-        <v>2.785714285714286</v>
+        <v>10.55462184873949</v>
       </c>
       <c r="AA3">
         <v>0</v>
       </c>
       <c r="AB3">
-        <v>0.093120560684196</v>
+        <v>0.0828224625095878</v>
       </c>
       <c r="AC3">
-        <v>-0.093120560684196</v>
+        <v>-0.0828224625095878</v>
       </c>
       <c r="AD3">
-        <v>17.9</v>
+        <v>0</v>
       </c>
       <c r="AE3">
         <v>0</v>
       </c>
       <c r="AF3">
-        <v>17.9</v>
+        <v>0</v>
       </c>
       <c r="AG3">
-        <v>-110.2</v>
+        <v>0</v>
       </c>
       <c r="AH3">
-        <v>0.1092796092796093</v>
-      </c>
-      <c r="AI3">
-        <v>0.0838800374882849</v>
+        <v>0</v>
       </c>
       <c r="AJ3">
-        <v>-3.086834733893556</v>
-      </c>
-      <c r="AK3">
-        <v>-1.291910902696366</v>
+        <v>0</v>
       </c>
       <c r="AL3">
         <v>0</v>
@@ -823,7 +814,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>National Bank Limited (DSE:NBL)</t>
+          <t>Uttara Bank PLC. (DSE:UTTARABANK)</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -832,7 +823,10 @@
         </is>
       </c>
       <c r="D4">
-        <v>-0.146</v>
+        <v>0.0516</v>
+      </c>
+      <c r="E4">
+        <v>0.132</v>
       </c>
       <c r="G4">
         <v>0</v>
@@ -847,82 +841,85 @@
         <v>0</v>
       </c>
       <c r="K4">
-        <v>-24.1</v>
+        <v>24.9</v>
       </c>
       <c r="L4">
-        <v>-0.3990066225165563</v>
+        <v>0.2385057471264368</v>
       </c>
       <c r="M4">
-        <v>-0</v>
+        <v>7.91</v>
       </c>
       <c r="N4">
-        <v>-0</v>
+        <v>0.05301608579088472</v>
       </c>
       <c r="O4">
-        <v>0</v>
+        <v>0.3176706827309237</v>
       </c>
       <c r="P4">
-        <v>-0</v>
+        <v>7.91</v>
       </c>
       <c r="Q4">
-        <v>-0</v>
+        <v>0.05301608579088472</v>
       </c>
       <c r="R4">
-        <v>0</v>
+        <v>0.3176706827309237</v>
       </c>
       <c r="S4">
         <v>0</v>
       </c>
+      <c r="T4">
+        <v>0</v>
+      </c>
       <c r="U4">
-        <v>44.8</v>
+        <v>121.2</v>
       </c>
       <c r="V4">
-        <v>0.1723739899961524</v>
+        <v>0.8123324396782843</v>
       </c>
       <c r="W4">
-        <v>-0.03855383138697809</v>
+        <v>0.1273657289002557</v>
       </c>
       <c r="X4">
-        <v>0.1151420024541229</v>
+        <v>0.08872949802863569</v>
       </c>
       <c r="Y4">
-        <v>-0.153695833841101</v>
+        <v>0.03863623087162005</v>
       </c>
       <c r="Z4">
-        <v>0.07496586818915228</v>
+        <v>1.223915592028136</v>
       </c>
       <c r="AA4">
         <v>0</v>
       </c>
       <c r="AB4">
-        <v>0.0945949590042228</v>
+        <v>0.08505064670482426</v>
       </c>
       <c r="AC4">
-        <v>-0.0945949590042228</v>
+        <v>-0.08505064670482426</v>
       </c>
       <c r="AD4">
-        <v>162</v>
+        <v>28.6</v>
       </c>
       <c r="AE4">
         <v>0</v>
       </c>
       <c r="AF4">
-        <v>162</v>
+        <v>28.6</v>
       </c>
       <c r="AG4">
-        <v>117.2</v>
+        <v>-92.59999999999999</v>
       </c>
       <c r="AH4">
-        <v>0.3839772457928419</v>
+        <v>0.1608548931383577</v>
       </c>
       <c r="AI4">
-        <v>0.2328255245760276</v>
+        <v>0.1274509803921569</v>
       </c>
       <c r="AJ4">
-        <v>0.3107928931317953</v>
+        <v>-1.636042402826855</v>
       </c>
       <c r="AK4">
-        <v>0.1800307219662058</v>
+        <v>-0.8972868217054262</v>
       </c>
       <c r="AL4">
         <v>0</v>
@@ -939,7 +936,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Social Islami Bank Limited (DSE:SIBL)</t>
+          <t>National Bank Limited (DSE:NBL)</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -947,104 +944,80 @@
           <t>Bank (Money Center)</t>
         </is>
       </c>
-      <c r="D5">
-        <v>0.0454</v>
-      </c>
-      <c r="E5">
-        <v>-0.0097</v>
-      </c>
-      <c r="G5">
-        <v>0</v>
-      </c>
-      <c r="H5">
-        <v>0</v>
-      </c>
-      <c r="I5">
-        <v>0</v>
-      </c>
-      <c r="J5">
-        <v>0</v>
-      </c>
       <c r="K5">
-        <v>21.4</v>
-      </c>
-      <c r="L5">
-        <v>0.1975992613111727</v>
+        <v>-342.1</v>
       </c>
       <c r="M5">
-        <v>7.81</v>
+        <v>-0</v>
       </c>
       <c r="N5">
-        <v>0.06313662085691188</v>
+        <v>-0</v>
       </c>
       <c r="O5">
-        <v>0.3649532710280374</v>
+        <v>0</v>
       </c>
       <c r="P5">
-        <v>7.81</v>
+        <v>-0</v>
       </c>
       <c r="Q5">
-        <v>0.06313662085691188</v>
+        <v>-0</v>
       </c>
       <c r="R5">
-        <v>0.3649532710280374</v>
+        <v>0</v>
       </c>
       <c r="S5">
         <v>0</v>
       </c>
-      <c r="T5">
-        <v>0</v>
-      </c>
       <c r="U5">
-        <v>190.4</v>
+        <v>52.2</v>
       </c>
       <c r="V5">
-        <v>1.539207760711399</v>
+        <v>0.2141977841608535</v>
       </c>
       <c r="W5">
-        <v>0.09857208659603869</v>
+        <v>-0.6408767328587487</v>
       </c>
       <c r="X5">
-        <v>0.1224710781251746</v>
+        <v>0.0949868967541329</v>
       </c>
       <c r="Y5">
-        <v>-0.02389899152913592</v>
+        <v>-0.7358636296128815</v>
       </c>
       <c r="Z5">
-        <v>0.8561264822134389</v>
+        <v>0</v>
       </c>
       <c r="AA5">
         <v>0</v>
       </c>
       <c r="AB5">
-        <v>0.09496097370654256</v>
+        <v>0.08674295584901456</v>
       </c>
       <c r="AC5">
-        <v>-0.09496097370654256</v>
+        <v>-0.08674295584901456</v>
       </c>
       <c r="AD5">
-        <v>102.1</v>
+        <v>96.2</v>
       </c>
       <c r="AE5">
         <v>0</v>
       </c>
       <c r="AF5">
-        <v>102.1</v>
+        <v>96.2</v>
       </c>
       <c r="AG5">
-        <v>-88.30000000000001</v>
+        <v>44</v>
       </c>
       <c r="AH5">
-        <v>0.4521700620017715</v>
+        <v>0.2830244189467491</v>
       </c>
       <c r="AI5">
-        <v>0.341929002009377</v>
+        <v>0.2287752675386445</v>
       </c>
       <c r="AJ5">
-        <v>-2.494350282485877</v>
+        <v>0.1529370872436566</v>
       </c>
       <c r="AK5">
-        <v>-0.8160813308687618</v>
+        <v>0.1194678251425468</v>
       </c>
       <c r="AL5">
         <v>0</v>
@@ -1061,7 +1034,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Dutch-Bangla Bank Limited (DSE:DUTCHBANGL)</t>
+          <t>South Bangla Agriculture and Commerce Bank Limited (DSE:SBACBANK)</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -1069,12 +1042,6 @@
           <t>Bank (Money Center)</t>
         </is>
       </c>
-      <c r="D6">
-        <v>0.104</v>
-      </c>
-      <c r="E6">
-        <v>0.195</v>
-      </c>
       <c r="G6">
         <v>0</v>
       </c>
@@ -1088,28 +1055,28 @@
         <v>0</v>
       </c>
       <c r="K6">
-        <v>55.6</v>
+        <v>4.48</v>
       </c>
       <c r="L6">
-        <v>0.2052417866371355</v>
+        <v>0.1240997229916898</v>
       </c>
       <c r="M6">
-        <v>11</v>
+        <v>3.24</v>
       </c>
       <c r="N6">
-        <v>0.02596789423984891</v>
+        <v>0.04106463878326996</v>
       </c>
       <c r="O6">
-        <v>0.197841726618705</v>
+        <v>0.7232142857142857</v>
       </c>
       <c r="P6">
-        <v>11</v>
+        <v>3.24</v>
       </c>
       <c r="Q6">
-        <v>0.02596789423984891</v>
+        <v>0.04106463878326996</v>
       </c>
       <c r="R6">
-        <v>0.197841726618705</v>
+        <v>0.7232142857142857</v>
       </c>
       <c r="S6">
         <v>0</v>
@@ -1118,55 +1085,55 @@
         <v>0</v>
       </c>
       <c r="U6">
-        <v>383</v>
+        <v>79.40000000000001</v>
       </c>
       <c r="V6">
-        <v>0.9041548630783758</v>
+        <v>1.006337135614702</v>
       </c>
       <c r="W6">
-        <v>0.1335896203748198</v>
+        <v>0.04125230202578269</v>
       </c>
       <c r="X6">
-        <v>0.1322294543405071</v>
+        <v>0.1002026869351095</v>
       </c>
       <c r="Y6">
-        <v>0.00136016603431266</v>
+        <v>-0.05895038490932678</v>
       </c>
       <c r="Z6">
-        <v>0.5329529805233129</v>
+        <v>0.2482806052269602</v>
       </c>
       <c r="AA6">
         <v>0</v>
       </c>
       <c r="AB6">
-        <v>0.0953386889801916</v>
+        <v>0.08995863184381572</v>
       </c>
       <c r="AC6">
-        <v>-0.0953386889801916</v>
+        <v>-0.08995863184381572</v>
       </c>
       <c r="AD6">
-        <v>463.6</v>
+        <v>44.5</v>
       </c>
       <c r="AE6">
         <v>0</v>
       </c>
       <c r="AF6">
-        <v>463.6</v>
+        <v>44.5</v>
       </c>
       <c r="AG6">
-        <v>80.60000000000002</v>
+        <v>-34.90000000000001</v>
       </c>
       <c r="AH6">
-        <v>0.5225428313796213</v>
+        <v>0.3606158833063209</v>
       </c>
       <c r="AI6">
-        <v>0.5396345012222094</v>
+        <v>0.3062629043358568</v>
       </c>
       <c r="AJ6">
-        <v>0.1598571995239984</v>
+        <v>-0.7931818181818183</v>
       </c>
       <c r="AK6">
-        <v>0.1692921655114472</v>
+        <v>-0.5295902883156299</v>
       </c>
       <c r="AL6">
         <v>0</v>
@@ -1192,10 +1159,10 @@
         </is>
       </c>
       <c r="D7">
-        <v>0.0926</v>
+        <v>0.124</v>
       </c>
       <c r="E7">
-        <v>0.0431</v>
+        <v>0.225</v>
       </c>
       <c r="G7">
         <v>0</v>
@@ -1210,28 +1177,28 @@
         <v>0</v>
       </c>
       <c r="K7">
-        <v>26.6</v>
+        <v>24.8</v>
       </c>
       <c r="L7">
-        <v>0.2079749804534793</v>
+        <v>0.2117847993168233</v>
       </c>
       <c r="M7">
-        <v>8.779999999999999</v>
+        <v>7.07</v>
       </c>
       <c r="N7">
-        <v>0.03323239969719909</v>
+        <v>0.02856565656565657</v>
       </c>
       <c r="O7">
-        <v>0.3300751879699247</v>
+        <v>0.2850806451612903</v>
       </c>
       <c r="P7">
-        <v>8.779999999999999</v>
+        <v>7.07</v>
       </c>
       <c r="Q7">
-        <v>0.03323239969719909</v>
+        <v>0.02856565656565657</v>
       </c>
       <c r="R7">
-        <v>0.3300751879699247</v>
+        <v>0.2850806451612903</v>
       </c>
       <c r="S7">
         <v>0</v>
@@ -1240,55 +1207,55 @@
         <v>0</v>
       </c>
       <c r="U7">
-        <v>212.6</v>
+        <v>347.5</v>
       </c>
       <c r="V7">
-        <v>0.8046934140802423</v>
+        <v>1.404040404040404</v>
       </c>
       <c r="W7">
-        <v>0.1162587412587413</v>
+        <v>0.12344449975112</v>
       </c>
       <c r="X7">
-        <v>0.1443175862524778</v>
+        <v>0.1252298787178137</v>
       </c>
       <c r="Y7">
-        <v>-0.02805884499373658</v>
+        <v>-0.001785378966693785</v>
       </c>
       <c r="Z7">
-        <v>0.2685282385051438</v>
+        <v>0.3203830369357045</v>
       </c>
       <c r="AA7">
         <v>0</v>
       </c>
       <c r="AB7">
-        <v>0.09569049581737207</v>
+        <v>0.09084497269471541</v>
       </c>
       <c r="AC7">
-        <v>-0.09569049581737207</v>
+        <v>-0.09084497269471541</v>
       </c>
       <c r="AD7">
-        <v>377.2</v>
+        <v>340.6</v>
       </c>
       <c r="AE7">
         <v>0</v>
       </c>
       <c r="AF7">
-        <v>377.2</v>
+        <v>340.6</v>
       </c>
       <c r="AG7">
-        <v>164.6</v>
+        <v>-6.899999999999977</v>
       </c>
       <c r="AH7">
-        <v>0.5880885562831306</v>
+        <v>0.5791532052372046</v>
       </c>
       <c r="AI7">
-        <v>0.6522566142140758</v>
+        <v>0.6321455085374909</v>
       </c>
       <c r="AJ7">
-        <v>0.3838619402985075</v>
+        <v>-0.0286783042394014</v>
       </c>
       <c r="AK7">
-        <v>0.4500957068635494</v>
+        <v>-0.03606900156821734</v>
       </c>
       <c r="AL7">
         <v>0</v>
@@ -1305,7 +1272,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Jamuna Bank Limited (DSE:JAMUNABANK)</t>
+          <t>Bank Asia Limited (DSE:BANKASIA)</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -1314,10 +1281,10 @@
         </is>
       </c>
       <c r="D8">
-        <v>0.0779</v>
+        <v>0.09519999999999999</v>
       </c>
       <c r="E8">
-        <v>0.0416</v>
+        <v>0.0672</v>
       </c>
       <c r="G8">
         <v>0</v>
@@ -1332,28 +1299,28 @@
         <v>0</v>
       </c>
       <c r="K8">
-        <v>26.3</v>
+        <v>34.1</v>
       </c>
       <c r="L8">
-        <v>0.2281006071118821</v>
+        <v>0.2148708254568368</v>
       </c>
       <c r="M8">
-        <v>13</v>
+        <v>18.1</v>
       </c>
       <c r="N8">
-        <v>0.08376288659793815</v>
+        <v>0.08430367955286447</v>
       </c>
       <c r="O8">
-        <v>0.4942965779467681</v>
+        <v>0.530791788856305</v>
       </c>
       <c r="P8">
-        <v>13</v>
+        <v>18.1</v>
       </c>
       <c r="Q8">
-        <v>0.08376288659793815</v>
+        <v>0.08430367955286447</v>
       </c>
       <c r="R8">
-        <v>0.4942965779467681</v>
+        <v>0.530791788856305</v>
       </c>
       <c r="S8">
         <v>0</v>
@@ -1362,55 +1329,55 @@
         <v>0</v>
       </c>
       <c r="U8">
-        <v>33.7</v>
+        <v>261</v>
       </c>
       <c r="V8">
-        <v>0.217139175257732</v>
+        <v>1.215649743828598</v>
       </c>
       <c r="W8">
-        <v>0.0909405255878285</v>
+        <v>0.1201973916108565</v>
       </c>
       <c r="X8">
-        <v>0.1518240728003333</v>
+        <v>0.1328423960410919</v>
       </c>
       <c r="Y8">
-        <v>-0.06088354721250483</v>
+        <v>-0.01264500443023539</v>
       </c>
       <c r="Z8">
-        <v>0.2181233446840712</v>
+        <v>0.4056748466257668</v>
       </c>
       <c r="AA8">
         <v>0</v>
       </c>
       <c r="AB8">
-        <v>0.09586416468941464</v>
+        <v>0.09139396487275087</v>
       </c>
       <c r="AC8">
-        <v>-0.09586416468941464</v>
+        <v>-0.09139396487275087</v>
       </c>
       <c r="AD8">
-        <v>253.7</v>
+        <v>348.5</v>
       </c>
       <c r="AE8">
         <v>0</v>
       </c>
       <c r="AF8">
-        <v>253.7</v>
+        <v>348.5</v>
       </c>
       <c r="AG8">
-        <v>220</v>
+        <v>87.5</v>
       </c>
       <c r="AH8">
-        <v>0.6204450966006358</v>
+        <v>0.6187855113636364</v>
       </c>
       <c r="AI8">
-        <v>0.5410535295372148</v>
+        <v>0.556087442157332</v>
       </c>
       <c r="AJ8">
-        <v>0.5863539445628998</v>
+        <v>0.2895433487756453</v>
       </c>
       <c r="AK8">
-        <v>0.5055147058823529</v>
+        <v>0.2392671588733935</v>
       </c>
       <c r="AL8">
         <v>0</v>
@@ -1427,7 +1394,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Islami Bank Bangladesh Limited (DSE:ISLAMIBANK)</t>
+          <t>Social Islami Bank PLC. (DSE:SIBL)</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -1436,10 +1403,10 @@
         </is>
       </c>
       <c r="D9">
-        <v>0.07490000000000001</v>
+        <v>0.0472</v>
       </c>
       <c r="E9">
-        <v>0.0611</v>
+        <v>0.123</v>
       </c>
       <c r="G9">
         <v>0</v>
@@ -1454,28 +1421,28 @@
         <v>0</v>
       </c>
       <c r="K9">
-        <v>48.5</v>
+        <v>23.1</v>
       </c>
       <c r="L9">
-        <v>0.1155036913550846</v>
+        <v>0.2179245283018868</v>
       </c>
       <c r="M9">
-        <v>16</v>
+        <v>8.390000000000001</v>
       </c>
       <c r="N9">
-        <v>0.03096574414553899</v>
+        <v>0.0724525043177893</v>
       </c>
       <c r="O9">
-        <v>0.3298969072164948</v>
+        <v>0.3632034632034632</v>
       </c>
       <c r="P9">
-        <v>16</v>
+        <v>8.390000000000001</v>
       </c>
       <c r="Q9">
-        <v>0.03096574414553899</v>
+        <v>0.0724525043177893</v>
       </c>
       <c r="R9">
-        <v>0.3298969072164948</v>
+        <v>0.3632034632034632</v>
       </c>
       <c r="S9">
         <v>0</v>
@@ -1484,55 +1451,55 @@
         <v>0</v>
       </c>
       <c r="U9">
-        <v>1814.2</v>
+        <v>166.4</v>
       </c>
       <c r="V9">
-        <v>3.511128314302303</v>
+        <v>1.436960276338515</v>
       </c>
       <c r="W9">
-        <v>0.06297883391767303</v>
+        <v>0.117557251908397</v>
       </c>
       <c r="X9">
-        <v>0.1606595926875909</v>
+        <v>0.1425112953129589</v>
       </c>
       <c r="Y9">
-        <v>-0.09768075876991783</v>
+        <v>-0.02495404340456199</v>
       </c>
       <c r="Z9">
-        <v>0.8717043803197008</v>
+        <v>0.9796672828096117</v>
       </c>
       <c r="AA9">
         <v>0</v>
       </c>
       <c r="AB9">
-        <v>0.096036582691678</v>
+        <v>0.09195811254726657</v>
       </c>
       <c r="AC9">
-        <v>-0.096036582691678</v>
+        <v>-0.09195811254726657</v>
       </c>
       <c r="AD9">
-        <v>970.5</v>
+        <v>224.3</v>
       </c>
       <c r="AE9">
         <v>0</v>
       </c>
       <c r="AF9">
-        <v>970.5</v>
+        <v>224.3</v>
       </c>
       <c r="AG9">
-        <v>-843.7</v>
+        <v>57.90000000000001</v>
       </c>
       <c r="AH9">
-        <v>0.6525685852608929</v>
+        <v>0.6595119082622758</v>
       </c>
       <c r="AI9">
-        <v>0.5895037356496386</v>
+        <v>0.5363462458153992</v>
       </c>
       <c r="AJ9">
-        <v>2.580122324159022</v>
+        <v>0.3333333333333334</v>
       </c>
       <c r="AK9">
-        <v>5.025014889815364</v>
+        <v>0.2299444003177125</v>
       </c>
       <c r="AL9">
         <v>0</v>
@@ -1549,7 +1516,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Southeast Bank Limited (DSE:SOUTHEASTB)</t>
+          <t>Standard Bank Limited (DSE:STANDBANKL)</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1558,10 +1525,10 @@
         </is>
       </c>
       <c r="D10">
-        <v>0.00932</v>
+        <v>0.0388</v>
       </c>
       <c r="E10">
-        <v>-0.09789999999999999</v>
+        <v>0.0958</v>
       </c>
       <c r="G10">
         <v>0</v>
@@ -1576,28 +1543,28 @@
         <v>0</v>
       </c>
       <c r="K10">
-        <v>15</v>
+        <v>10.5</v>
       </c>
       <c r="L10">
-        <v>0.1364877161055505</v>
+        <v>0.1810344827586207</v>
       </c>
       <c r="M10">
-        <v>9.44</v>
+        <v>2.47</v>
       </c>
       <c r="N10">
-        <v>0.05690174804098854</v>
+        <v>0.02892271662763466</v>
       </c>
       <c r="O10">
-        <v>0.6293333333333333</v>
+        <v>0.2352380952380952</v>
       </c>
       <c r="P10">
-        <v>9.44</v>
+        <v>2.47</v>
       </c>
       <c r="Q10">
-        <v>0.05690174804098854</v>
+        <v>0.02892271662763466</v>
       </c>
       <c r="R10">
-        <v>0.6293333333333333</v>
+        <v>0.2352380952380952</v>
       </c>
       <c r="S10">
         <v>0</v>
@@ -1606,55 +1573,55 @@
         <v>0</v>
       </c>
       <c r="U10">
-        <v>295</v>
+        <v>169.1</v>
       </c>
       <c r="V10">
-        <v>1.778179626280892</v>
+        <v>1.980093676814988</v>
       </c>
       <c r="W10">
-        <v>0.03913383772501956</v>
+        <v>0.06143943826799297</v>
       </c>
       <c r="X10">
-        <v>0.1629542480237514</v>
+        <v>0.1441652381377019</v>
       </c>
       <c r="Y10">
-        <v>-0.1238204102987319</v>
+        <v>-0.08272579986970893</v>
       </c>
       <c r="Z10">
-        <v>0.1924356504990369</v>
+        <v>0.2972834443874935</v>
       </c>
       <c r="AA10">
         <v>0</v>
       </c>
       <c r="AB10">
-        <v>0.09607668966786923</v>
+        <v>0.09204275804014425</v>
       </c>
       <c r="AC10">
-        <v>-0.09607668966786923</v>
+        <v>-0.09204275804014425</v>
       </c>
       <c r="AD10">
-        <v>322.1</v>
+        <v>170</v>
       </c>
       <c r="AE10">
         <v>0</v>
       </c>
       <c r="AF10">
-        <v>322.1</v>
+        <v>170</v>
       </c>
       <c r="AG10">
-        <v>27.10000000000002</v>
+        <v>0.9000000000000057</v>
       </c>
       <c r="AH10">
-        <v>0.6600409836065574</v>
+        <v>0.6656225528582616</v>
       </c>
       <c r="AI10">
-        <v>0.4997672614429791</v>
+        <v>0.5132850241545894</v>
       </c>
       <c r="AJ10">
-        <v>0.1404145077720208</v>
+        <v>0.01042873696407886</v>
       </c>
       <c r="AK10">
-        <v>0.07753934191702438</v>
+        <v>0.005552128315854446</v>
       </c>
       <c r="AL10">
         <v>0</v>
@@ -1671,7 +1638,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>National Credit and Commerce Bank Limited (DSE:NCCBANK)</t>
+          <t>Eastern Bank PLC. (DSE:EBL)</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1680,10 +1647,10 @@
         </is>
       </c>
       <c r="D11">
-        <v>0.0675</v>
+        <v>0.112</v>
       </c>
       <c r="E11">
-        <v>0.0188</v>
+        <v>0.23</v>
       </c>
       <c r="G11">
         <v>0</v>
@@ -1698,28 +1665,28 @@
         <v>0</v>
       </c>
       <c r="K11">
-        <v>26.1</v>
+        <v>50.1</v>
       </c>
       <c r="L11">
-        <v>0.2427906976744186</v>
+        <v>0.2998204667863555</v>
       </c>
       <c r="M11">
-        <v>11.2</v>
+        <v>12.2</v>
       </c>
       <c r="N11">
-        <v>0.07892882311486962</v>
+        <v>0.03770086526576019</v>
       </c>
       <c r="O11">
-        <v>0.4291187739463601</v>
+        <v>0.2435129740518962</v>
       </c>
       <c r="P11">
-        <v>11.2</v>
+        <v>12.2</v>
       </c>
       <c r="Q11">
-        <v>0.07892882311486962</v>
+        <v>0.03770086526576019</v>
       </c>
       <c r="R11">
-        <v>0.4291187739463601</v>
+        <v>0.2435129740518962</v>
       </c>
       <c r="S11">
         <v>0</v>
@@ -1728,55 +1695,55 @@
         <v>0</v>
       </c>
       <c r="U11">
-        <v>73.09999999999999</v>
+        <v>223.2</v>
       </c>
       <c r="V11">
-        <v>0.5151515151515151</v>
+        <v>0.6897404202719406</v>
       </c>
       <c r="W11">
-        <v>0.1009280742459397</v>
+        <v>0.1467486818980668</v>
       </c>
       <c r="X11">
-        <v>0.1719251795303436</v>
+        <v>0.1524720927804739</v>
       </c>
       <c r="Y11">
-        <v>-0.07099710528440391</v>
+        <v>-0.005723410882407104</v>
       </c>
       <c r="Z11">
-        <v>0.2897574123989219</v>
+        <v>0.19018893694514</v>
       </c>
       <c r="AA11">
         <v>0</v>
       </c>
       <c r="AB11">
-        <v>0.09621821517692285</v>
+        <v>0.092425736265807</v>
       </c>
       <c r="AC11">
-        <v>-0.09621821517692285</v>
+        <v>-0.092425736265807</v>
       </c>
       <c r="AD11">
-        <v>310.6</v>
+        <v>731.4</v>
       </c>
       <c r="AE11">
         <v>0</v>
       </c>
       <c r="AF11">
-        <v>310.6</v>
+        <v>731.4</v>
       </c>
       <c r="AG11">
-        <v>237.5</v>
+        <v>508.2</v>
       </c>
       <c r="AH11">
-        <v>0.6864088397790056</v>
+        <v>0.6932701421800948</v>
       </c>
       <c r="AI11">
-        <v>0.5730627306273063</v>
+        <v>0.676470588235294</v>
       </c>
       <c r="AJ11">
-        <v>0.6259884027411703</v>
+        <v>0.6109641740803078</v>
       </c>
       <c r="AK11">
-        <v>0.5065045851994029</v>
+        <v>0.5923076923076923</v>
       </c>
       <c r="AL11">
         <v>0</v>
@@ -1793,7 +1760,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Pubali Bank Limited (DSE:PUBALIBANK)</t>
+          <t>National Credit and Commerce Bank PLC. (DSE:NCCBANK)</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1802,10 +1769,10 @@
         </is>
       </c>
       <c r="D12">
-        <v>0.0794</v>
+        <v>0.0716</v>
       </c>
       <c r="E12">
-        <v>0.215</v>
+        <v>0.0369</v>
       </c>
       <c r="G12">
         <v>0</v>
@@ -1820,28 +1787,28 @@
         <v>0</v>
       </c>
       <c r="K12">
-        <v>49.2</v>
+        <v>24.1</v>
       </c>
       <c r="L12">
-        <v>0.2575916230366492</v>
+        <v>0.2339805825242719</v>
       </c>
       <c r="M12">
-        <v>14.3</v>
+        <v>5.41</v>
       </c>
       <c r="N12">
-        <v>0.05437262357414449</v>
+        <v>0.04079939668174962</v>
       </c>
       <c r="O12">
-        <v>0.290650406504065</v>
+        <v>0.2244813278008299</v>
       </c>
       <c r="P12">
-        <v>14.3</v>
+        <v>5.41</v>
       </c>
       <c r="Q12">
-        <v>0.05437262357414449</v>
+        <v>0.04079939668174962</v>
       </c>
       <c r="R12">
-        <v>0.290650406504065</v>
+        <v>0.2244813278008299</v>
       </c>
       <c r="S12">
         <v>0</v>
@@ -1850,55 +1817,55 @@
         <v>0</v>
       </c>
       <c r="U12">
-        <v>150.9</v>
+        <v>113.3</v>
       </c>
       <c r="V12">
-        <v>0.5737642585551331</v>
+        <v>0.8544494720965309</v>
       </c>
       <c r="W12">
-        <v>0.09969604863221886</v>
+        <v>0.1041486603284356</v>
       </c>
       <c r="X12">
-        <v>0.1765353070777265</v>
+        <v>0.1594434589091939</v>
       </c>
       <c r="Y12">
-        <v>-0.07683925844550764</v>
+        <v>-0.05529479858075825</v>
       </c>
       <c r="Z12">
-        <v>0.3026941362916006</v>
+        <v>0.2196630411601621</v>
       </c>
       <c r="AA12">
         <v>0</v>
       </c>
       <c r="AB12">
-        <v>0.09628273200744154</v>
+        <v>0.09270143705963561</v>
       </c>
       <c r="AC12">
-        <v>-0.09628273200744154</v>
+        <v>-0.09270143705963561</v>
       </c>
       <c r="AD12">
-        <v>609.1</v>
+        <v>329.7</v>
       </c>
       <c r="AE12">
         <v>0</v>
       </c>
       <c r="AF12">
-        <v>609.1</v>
+        <v>329.7</v>
       </c>
       <c r="AG12">
-        <v>458.2</v>
+        <v>216.4</v>
       </c>
       <c r="AH12">
-        <v>0.6984290792340329</v>
+        <v>0.7131732641142116</v>
       </c>
       <c r="AI12">
-        <v>0.5902131782945736</v>
+        <v>0.5956639566395664</v>
       </c>
       <c r="AJ12">
-        <v>0.6353300055463117</v>
+        <v>0.6200573065902578</v>
       </c>
       <c r="AK12">
-        <v>0.5200317784587448</v>
+        <v>0.4915947296683326</v>
       </c>
       <c r="AL12">
         <v>0</v>
@@ -1915,7 +1882,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Eastern Bank Limited (DSE:EBL)</t>
+          <t>IFIC Bank PLC (DSE:IFIC)</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1924,10 +1891,10 @@
         </is>
       </c>
       <c r="D13">
-        <v>0.103</v>
+        <v>0.145</v>
       </c>
       <c r="E13">
-        <v>0.0877</v>
+        <v>0.109</v>
       </c>
       <c r="G13">
         <v>0</v>
@@ -1942,28 +1909,28 @@
         <v>0</v>
       </c>
       <c r="K13">
-        <v>46.2</v>
+        <v>27.7</v>
       </c>
       <c r="L13">
-        <v>0.2711267605633803</v>
+        <v>0.2165754495699765</v>
       </c>
       <c r="M13">
-        <v>11.8</v>
+        <v>3.6612</v>
       </c>
       <c r="N13">
-        <v>0.03555287737270263</v>
+        <v>0.01958908507223114</v>
       </c>
       <c r="O13">
-        <v>0.2554112554112554</v>
+        <v>0.132173285198556</v>
       </c>
       <c r="P13">
-        <v>11.8</v>
+        <v>3.6612</v>
       </c>
       <c r="Q13">
-        <v>0.03555287737270263</v>
+        <v>0.01958908507223114</v>
       </c>
       <c r="R13">
-        <v>0.2554112554112554</v>
+        <v>0.132173285198556</v>
       </c>
       <c r="S13">
         <v>0</v>
@@ -1972,55 +1939,55 @@
         <v>0</v>
       </c>
       <c r="U13">
-        <v>236.7</v>
+        <v>163.1</v>
       </c>
       <c r="V13">
-        <v>0.7131666164507382</v>
+        <v>0.8726591760299625</v>
       </c>
       <c r="W13">
-        <v>0.1255434782608696</v>
+        <v>0.08699748743718594</v>
       </c>
       <c r="X13">
-        <v>0.1771068150228587</v>
+        <v>0.1140503816081493</v>
       </c>
       <c r="Y13">
-        <v>-0.05156333676198915</v>
+        <v>-0.02705289417096338</v>
       </c>
       <c r="Z13">
-        <v>0.2393258426966293</v>
+        <v>0.3161928306551298</v>
       </c>
       <c r="AA13">
         <v>0</v>
       </c>
       <c r="AB13">
-        <v>0.09629038707821198</v>
+        <v>0.09278261647667727</v>
       </c>
       <c r="AC13">
-        <v>-0.09629038707821198</v>
+        <v>-0.09278261647667727</v>
       </c>
       <c r="AD13">
-        <v>773.9</v>
+        <v>189.4</v>
       </c>
       <c r="AE13">
         <v>0</v>
       </c>
       <c r="AF13">
-        <v>773.9</v>
+        <v>189.4</v>
       </c>
       <c r="AG13">
-        <v>537.2</v>
+        <v>26.30000000000001</v>
       </c>
       <c r="AH13">
-        <v>0.6998553083740279</v>
+        <v>0.5033218176986447</v>
       </c>
       <c r="AI13">
-        <v>0.6938940195463105</v>
+        <v>0.3769904458598726</v>
       </c>
       <c r="AJ13">
-        <v>0.618110689218732</v>
+        <v>0.1233583489681051</v>
       </c>
       <c r="AK13">
-        <v>0.6114272706578648</v>
+        <v>0.07751252578838788</v>
       </c>
       <c r="AL13">
         <v>0</v>
@@ -2037,7 +2004,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Standard Bank Limited (DSE:STANDBANKL)</t>
+          <t>Dhaka Bank PLC. (DSE:DHAKABANK)</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -2046,10 +2013,10 @@
         </is>
       </c>
       <c r="D14">
-        <v>0.046</v>
+        <v>0.0664</v>
       </c>
       <c r="E14">
-        <v>-0.0741</v>
+        <v>0.0146</v>
       </c>
       <c r="G14">
         <v>0</v>
@@ -2064,28 +2031,28 @@
         <v>0</v>
       </c>
       <c r="K14">
-        <v>7.71</v>
+        <v>15.2</v>
       </c>
       <c r="L14">
-        <v>0.1166414523449319</v>
+        <v>0.1578400830737279</v>
       </c>
       <c r="M14">
-        <v>3.16</v>
+        <v>5.18</v>
       </c>
       <c r="N14">
-        <v>0.03476347634763476</v>
+        <v>0.04516129032258064</v>
       </c>
       <c r="O14">
-        <v>0.4098573281452659</v>
+        <v>0.3407894736842105</v>
       </c>
       <c r="P14">
-        <v>3.16</v>
+        <v>5.18</v>
       </c>
       <c r="Q14">
-        <v>0.03476347634763476</v>
+        <v>0.04516129032258064</v>
       </c>
       <c r="R14">
-        <v>0.4098573281452659</v>
+        <v>0.3407894736842105</v>
       </c>
       <c r="S14">
         <v>0</v>
@@ -2094,55 +2061,55 @@
         <v>0</v>
       </c>
       <c r="U14">
-        <v>189.1</v>
+        <v>254</v>
       </c>
       <c r="V14">
-        <v>2.08030803080308</v>
+        <v>2.214472537053182</v>
       </c>
       <c r="W14">
-        <v>0.03893939393939394</v>
+        <v>0.07063197026022305</v>
       </c>
       <c r="X14">
-        <v>0.177643916370802</v>
+        <v>0.1634484319898764</v>
       </c>
       <c r="Y14">
-        <v>-0.138704522431408</v>
+        <v>-0.09281646172965335</v>
       </c>
       <c r="Z14">
-        <v>0.4154619736015084</v>
+        <v>0.1521327014218009</v>
       </c>
       <c r="AA14">
         <v>0</v>
       </c>
       <c r="AB14">
-        <v>0.09629751558211171</v>
+        <v>0.09284422395236797</v>
       </c>
       <c r="AC14">
-        <v>-0.09629751558211171</v>
+        <v>-0.09284422395236797</v>
       </c>
       <c r="AD14">
-        <v>213.3</v>
+        <v>300.1</v>
       </c>
       <c r="AE14">
         <v>0</v>
       </c>
       <c r="AF14">
-        <v>213.3</v>
+        <v>300.1</v>
       </c>
       <c r="AG14">
-        <v>24.20000000000002</v>
+        <v>46.10000000000002</v>
       </c>
       <c r="AH14">
-        <v>0.7011834319526626</v>
+        <v>0.7234811957569913</v>
       </c>
       <c r="AI14">
-        <v>0.5551795939614783</v>
+        <v>0.5921468034727704</v>
       </c>
       <c r="AJ14">
-        <v>0.2102519548218941</v>
+        <v>0.2866915422885573</v>
       </c>
       <c r="AK14">
-        <v>0.1240389543823681</v>
+        <v>0.1823575949367089</v>
       </c>
       <c r="AL14">
         <v>0</v>
@@ -2159,7 +2126,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Bank Asia Limited (DSE:BANKASIA)</t>
+          <t>One Bank PLC. (DSE:ONEBANKPLC)</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -2168,10 +2135,10 @@
         </is>
       </c>
       <c r="D15">
-        <v>0.06950000000000001</v>
+        <v>0.0215</v>
       </c>
       <c r="E15">
-        <v>0.0555</v>
+        <v>-0.0269</v>
       </c>
       <c r="G15">
         <v>0</v>
@@ -2186,85 +2153,82 @@
         <v>0</v>
       </c>
       <c r="K15">
-        <v>30.8</v>
+        <v>10.2</v>
       </c>
       <c r="L15">
-        <v>0.2256410256410256</v>
+        <v>0.1378378378378378</v>
       </c>
       <c r="M15">
-        <v>17.6</v>
+        <v>-0</v>
       </c>
       <c r="N15">
-        <v>0.077125328659071</v>
+        <v>-0</v>
       </c>
       <c r="O15">
-        <v>0.5714285714285715</v>
+        <v>-0</v>
       </c>
       <c r="P15">
-        <v>17.6</v>
+        <v>-0</v>
       </c>
       <c r="Q15">
-        <v>0.077125328659071</v>
+        <v>-0</v>
       </c>
       <c r="R15">
-        <v>0.5714285714285715</v>
+        <v>-0</v>
       </c>
       <c r="S15">
         <v>0</v>
       </c>
-      <c r="T15">
-        <v>0</v>
-      </c>
       <c r="U15">
-        <v>520</v>
+        <v>121.9</v>
       </c>
       <c r="V15">
-        <v>2.278702892199825</v>
+        <v>1.366591928251121</v>
       </c>
       <c r="W15">
-        <v>0.0952970297029703</v>
+        <v>0.05573770491803278</v>
       </c>
       <c r="X15">
-        <v>0.1922698440882776</v>
+        <v>0.170398538432529</v>
       </c>
       <c r="Y15">
-        <v>-0.09697281438530733</v>
+        <v>-0.1146608335144962</v>
       </c>
       <c r="Z15">
-        <v>0.2922912205567451</v>
+        <v>0.1949420442571128</v>
       </c>
       <c r="AA15">
         <v>0</v>
       </c>
       <c r="AB15">
-        <v>0.0964699917177953</v>
+        <v>0.09306908349176726</v>
       </c>
       <c r="AC15">
-        <v>-0.0964699917177953</v>
+        <v>-0.09306908349176726</v>
       </c>
       <c r="AD15">
-        <v>627.5</v>
+        <v>253.5</v>
       </c>
       <c r="AE15">
         <v>0</v>
       </c>
       <c r="AF15">
-        <v>627.5</v>
+        <v>253.5</v>
       </c>
       <c r="AG15">
-        <v>107.5</v>
+        <v>131.6</v>
       </c>
       <c r="AH15">
-        <v>0.7333177515484398</v>
+        <v>0.7397140355996499</v>
       </c>
       <c r="AI15">
-        <v>0.6886523266022827</v>
+        <v>0.5927051671732523</v>
       </c>
       <c r="AJ15">
-        <v>0.3202263926124516</v>
+        <v>0.5960144927536232</v>
       </c>
       <c r="AK15">
-        <v>0.2747955010224949</v>
+        <v>0.4303466317854808</v>
       </c>
       <c r="AL15">
         <v>0</v>
@@ -2281,7 +2245,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>The Premier Bank Limited (DSE:PREMIERBAN)</t>
+          <t>Pubali Bank PLC. (DSE:PUBALIBANK)</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -2290,10 +2254,10 @@
         </is>
       </c>
       <c r="D16">
-        <v>0.202</v>
+        <v>0.175</v>
       </c>
       <c r="E16">
-        <v>0.104</v>
+        <v>0.399</v>
       </c>
       <c r="G16">
         <v>0</v>
@@ -2308,28 +2272,28 @@
         <v>0</v>
       </c>
       <c r="K16">
-        <v>38.4</v>
+        <v>59.2</v>
       </c>
       <c r="L16">
-        <v>0.2121546961325967</v>
+        <v>0.2367053178728509</v>
       </c>
       <c r="M16">
-        <v>13.9</v>
+        <v>11.3</v>
       </c>
       <c r="N16">
-        <v>0.09366576819407008</v>
+        <v>0.0461789946873723</v>
       </c>
       <c r="O16">
-        <v>0.3619791666666667</v>
+        <v>0.1908783783783784</v>
       </c>
       <c r="P16">
-        <v>13.9</v>
+        <v>11.3</v>
       </c>
       <c r="Q16">
-        <v>0.09366576819407008</v>
+        <v>0.0461789946873723</v>
       </c>
       <c r="R16">
-        <v>0.3619791666666667</v>
+        <v>0.1908783783783784</v>
       </c>
       <c r="S16">
         <v>0</v>
@@ -2338,55 +2302,55 @@
         <v>0</v>
       </c>
       <c r="U16">
-        <v>624</v>
+        <v>167.8</v>
       </c>
       <c r="V16">
-        <v>4.204851752021563</v>
+        <v>0.6857376379239887</v>
       </c>
       <c r="W16">
-        <v>0.1568627450980392</v>
+        <v>0.1399858122487586</v>
       </c>
       <c r="X16">
-        <v>0.1974592858349269</v>
+        <v>0.1709375500149863</v>
       </c>
       <c r="Y16">
-        <v>-0.04059654073688773</v>
+        <v>-0.0309517377662277</v>
       </c>
       <c r="Z16">
-        <v>0.5055865921787708</v>
+        <v>0.2838497332879355</v>
       </c>
       <c r="AA16">
         <v>0</v>
       </c>
       <c r="AB16">
-        <v>0.09652259987527961</v>
+        <v>0.09308542421517949</v>
       </c>
       <c r="AC16">
-        <v>-0.09652259987527961</v>
+        <v>-0.09308542421517949</v>
       </c>
       <c r="AD16">
-        <v>429.3</v>
+        <v>699.7</v>
       </c>
       <c r="AE16">
         <v>0</v>
       </c>
       <c r="AF16">
-        <v>429.3</v>
+        <v>699.7</v>
       </c>
       <c r="AG16">
-        <v>-194.7</v>
+        <v>531.9000000000001</v>
       </c>
       <c r="AH16">
-        <v>0.7431192660550459</v>
+        <v>0.7408936891147818</v>
       </c>
       <c r="AI16">
-        <v>0.644014401440144</v>
+        <v>0.6205214615111743</v>
       </c>
       <c r="AJ16">
-        <v>4.205183585313176</v>
+        <v>0.68490857584342</v>
       </c>
       <c r="AK16">
-        <v>-4.570422535211265</v>
+        <v>0.5541779537403626</v>
       </c>
       <c r="AL16">
         <v>0</v>
@@ -2403,7 +2367,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Prime Bank Limited (DSE:PRIMEBANK)</t>
+          <t>City Bank PLC. (DSE:CITYBANK)</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -2412,10 +2376,10 @@
         </is>
       </c>
       <c r="D17">
-        <v>0.0623</v>
+        <v>0.103</v>
       </c>
       <c r="E17">
-        <v>0.00273</v>
+        <v>0.119</v>
       </c>
       <c r="G17">
         <v>0</v>
@@ -2430,28 +2394,28 @@
         <v>0</v>
       </c>
       <c r="K17">
-        <v>34.5</v>
+        <v>47.9</v>
       </c>
       <c r="L17">
-        <v>0.2342158859470468</v>
+        <v>0.2174307762142533</v>
       </c>
       <c r="M17">
-        <v>19.3</v>
+        <v>11</v>
       </c>
       <c r="N17">
-        <v>0.0912961210974456</v>
+        <v>0.04602510460251046</v>
       </c>
       <c r="O17">
-        <v>0.5594202898550725</v>
+        <v>0.2296450939457202</v>
       </c>
       <c r="P17">
-        <v>19.3</v>
+        <v>11</v>
       </c>
       <c r="Q17">
-        <v>0.0912961210974456</v>
+        <v>0.04602510460251046</v>
       </c>
       <c r="R17">
-        <v>0.5594202898550725</v>
+        <v>0.2296450939457202</v>
       </c>
       <c r="S17">
         <v>0</v>
@@ -2460,55 +2424,55 @@
         <v>0</v>
       </c>
       <c r="U17">
-        <v>110.6</v>
+        <v>412.9</v>
       </c>
       <c r="V17">
-        <v>0.5231788079470199</v>
+        <v>1.727615062761506</v>
       </c>
       <c r="W17">
-        <v>0.1009362200117027</v>
+        <v>0.1444075972264094</v>
       </c>
       <c r="X17">
-        <v>0.2156374103439929</v>
+        <v>0.1797952902812308</v>
       </c>
       <c r="Y17">
-        <v>-0.1147011903322902</v>
+        <v>-0.0353876930548214</v>
       </c>
       <c r="Z17">
-        <v>0.1839410589410589</v>
+        <v>0.2199920111843419</v>
       </c>
       <c r="AA17">
         <v>0</v>
       </c>
       <c r="AB17">
-        <v>0.09667986174549449</v>
+        <v>0.09333421013511942</v>
       </c>
       <c r="AC17">
-        <v>-0.09667986174549449</v>
+        <v>-0.09333421013511942</v>
       </c>
       <c r="AD17">
-        <v>717.5</v>
+        <v>752.1</v>
       </c>
       <c r="AE17">
         <v>0</v>
       </c>
       <c r="AF17">
-        <v>717.5</v>
+        <v>752.1</v>
       </c>
       <c r="AG17">
-        <v>606.9</v>
+        <v>339.2</v>
       </c>
       <c r="AH17">
-        <v>0.7724189902034665</v>
+        <v>0.7588537988094037</v>
       </c>
       <c r="AI17">
-        <v>0.7012999706773532</v>
+        <v>0.6971635150166853</v>
       </c>
       <c r="AJ17">
-        <v>0.7416595380667237</v>
+        <v>0.5866482186094777</v>
       </c>
       <c r="AK17">
-        <v>0.6650958904109588</v>
+        <v>0.5093857936627121</v>
       </c>
       <c r="AL17">
         <v>0</v>
@@ -2525,7 +2489,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Export Import Bank of Bangladesh Limited (DSE:EXIMBANK)</t>
+          <t>Mutual Trust Bank PLC. (DSE:MTB)</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -2534,10 +2498,10 @@
         </is>
       </c>
       <c r="D18">
-        <v>0.0507</v>
+        <v>0.0999</v>
       </c>
       <c r="E18">
-        <v>-0.0483</v>
+        <v>-0.0507</v>
       </c>
       <c r="G18">
         <v>0</v>
@@ -2552,85 +2516,82 @@
         <v>0</v>
       </c>
       <c r="K18">
-        <v>26.9</v>
+        <v>18.6</v>
       </c>
       <c r="L18">
-        <v>0.2021036814425244</v>
+        <v>0.161598609904431</v>
       </c>
       <c r="M18">
-        <v>14.4</v>
+        <v>-0</v>
       </c>
       <c r="N18">
-        <v>0.09836065573770492</v>
+        <v>-0</v>
       </c>
       <c r="O18">
-        <v>0.5353159851301116</v>
+        <v>-0</v>
       </c>
       <c r="P18">
-        <v>14.4</v>
+        <v>-0</v>
       </c>
       <c r="Q18">
-        <v>0.09836065573770492</v>
+        <v>-0</v>
       </c>
       <c r="R18">
-        <v>0.5353159851301116</v>
+        <v>-0</v>
       </c>
       <c r="S18">
         <v>0</v>
       </c>
-      <c r="T18">
-        <v>0</v>
-      </c>
       <c r="U18">
-        <v>85.7</v>
+        <v>110.4</v>
       </c>
       <c r="V18">
-        <v>0.5853825136612022</v>
+        <v>0.7948164146868251</v>
       </c>
       <c r="W18">
-        <v>0.07311769502582223</v>
+        <v>0.08603145235892692</v>
       </c>
       <c r="X18">
-        <v>0.228994202160215</v>
+        <v>0.1880263228798726</v>
       </c>
       <c r="Y18">
-        <v>-0.1558765071343928</v>
+        <v>-0.1019948705209457</v>
       </c>
       <c r="Z18">
-        <v>0.1487317018661303</v>
+        <v>0.1671264701611732</v>
       </c>
       <c r="AA18">
         <v>0</v>
       </c>
       <c r="AB18">
-        <v>0.09677431755714666</v>
+        <v>0.09353634913691712</v>
       </c>
       <c r="AC18">
-        <v>-0.09677431755714666</v>
+        <v>-0.09353634913691712</v>
       </c>
       <c r="AD18">
-        <v>550.8</v>
+        <v>474.2</v>
       </c>
       <c r="AE18">
         <v>0</v>
       </c>
       <c r="AF18">
-        <v>550.8</v>
+        <v>474.2</v>
       </c>
       <c r="AG18">
-        <v>465.1</v>
+        <v>363.8</v>
       </c>
       <c r="AH18">
-        <v>0.7900172117039587</v>
+        <v>0.7734464198336323</v>
       </c>
       <c r="AI18">
-        <v>0.6319412574575494</v>
+        <v>0.6908508158508159</v>
       </c>
       <c r="AJ18">
-        <v>0.7605887162714635</v>
+        <v>0.723692062860553</v>
       </c>
       <c r="AK18">
-        <v>0.5918055732281461</v>
+        <v>0.6315972222222221</v>
       </c>
       <c r="AL18">
         <v>0</v>
@@ -2647,7 +2608,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Mutual Trust Bank Limited (DSE:MTB)</t>
+          <t>NRBC Bank PLC. (DSE:NRBCBANK)</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -2656,10 +2617,10 @@
         </is>
       </c>
       <c r="D19">
-        <v>0.177</v>
+        <v>0.183</v>
       </c>
       <c r="E19">
-        <v>0.339</v>
+        <v>0.145</v>
       </c>
       <c r="G19">
         <v>0</v>
@@ -2674,28 +2635,28 @@
         <v>0</v>
       </c>
       <c r="K19">
-        <v>42</v>
+        <v>15.4</v>
       </c>
       <c r="L19">
-        <v>0.2888583218707015</v>
+        <v>0.2308845577211394</v>
       </c>
       <c r="M19">
-        <v>4.48</v>
+        <v>5.41</v>
       </c>
       <c r="N19">
-        <v>0.03085399449035813</v>
+        <v>0.04263199369582348</v>
       </c>
       <c r="O19">
-        <v>0.1066666666666667</v>
+        <v>0.3512987012987013</v>
       </c>
       <c r="P19">
-        <v>4.48</v>
+        <v>5.41</v>
       </c>
       <c r="Q19">
-        <v>0.03085399449035813</v>
+        <v>0.04263199369582348</v>
       </c>
       <c r="R19">
-        <v>0.1066666666666667</v>
+        <v>0.3512987012987013</v>
       </c>
       <c r="S19">
         <v>0</v>
@@ -2704,55 +2665,55 @@
         <v>0</v>
       </c>
       <c r="U19">
-        <v>85.8</v>
+        <v>58.7</v>
       </c>
       <c r="V19">
-        <v>0.5909090909090909</v>
+        <v>0.4625689519306541</v>
       </c>
       <c r="W19">
-        <v>0.1981132075471698</v>
+        <v>0.1238938053097345</v>
       </c>
       <c r="X19">
-        <v>0.2319954465828366</v>
+        <v>0.123375857839539</v>
       </c>
       <c r="Y19">
-        <v>-0.03388223903566678</v>
+        <v>0.0005179474701954845</v>
       </c>
       <c r="Z19">
-        <v>0.2132590202405398</v>
+        <v>0.3346713497240341</v>
       </c>
       <c r="AA19">
         <v>0</v>
       </c>
       <c r="AB19">
-        <v>0.0967935659461831</v>
+        <v>0.09406688566092355</v>
       </c>
       <c r="AC19">
-        <v>-0.0967935659461831</v>
+        <v>-0.09406688566092355</v>
       </c>
       <c r="AD19">
-        <v>558.3</v>
+        <v>167</v>
       </c>
       <c r="AE19">
         <v>0</v>
       </c>
       <c r="AF19">
-        <v>558.3</v>
+        <v>167</v>
       </c>
       <c r="AG19">
-        <v>472.4999999999999</v>
+        <v>108.3</v>
       </c>
       <c r="AH19">
-        <v>0.7936034115138592</v>
+        <v>0.5682204831575366</v>
       </c>
       <c r="AI19">
-        <v>0.7208521626856036</v>
+        <v>0.5736860185503263</v>
       </c>
       <c r="AJ19">
-        <v>0.764934434191355</v>
+        <v>0.4604591836734694</v>
       </c>
       <c r="AK19">
-        <v>0.6860752141716276</v>
+        <v>0.4660068846815835</v>
       </c>
       <c r="AL19">
         <v>0</v>
@@ -2769,7 +2730,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>The City Bank Limited (DSE:CITYBANK)</t>
+          <t>Jamuna Bank PLC. (DSE:JAMUNABANK)</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -2778,10 +2739,10 @@
         </is>
       </c>
       <c r="D20">
-        <v>0.103</v>
+        <v>0.0327</v>
       </c>
       <c r="E20">
-        <v>0.051</v>
+        <v>-0.0574</v>
       </c>
       <c r="G20">
         <v>0</v>
@@ -2796,28 +2757,28 @@
         <v>0</v>
       </c>
       <c r="K20">
-        <v>54.3</v>
+        <v>17.1</v>
       </c>
       <c r="L20">
-        <v>0.2410119840213049</v>
+        <v>0.1696428571428572</v>
       </c>
       <c r="M20">
-        <v>13.4</v>
+        <v>11.9</v>
       </c>
       <c r="N20">
-        <v>0.05265225933202358</v>
+        <v>0.07682375726275016</v>
       </c>
       <c r="O20">
-        <v>0.2467771639042357</v>
+        <v>0.695906432748538</v>
       </c>
       <c r="P20">
-        <v>13.4</v>
+        <v>11.9</v>
       </c>
       <c r="Q20">
-        <v>0.05265225933202358</v>
+        <v>0.07682375726275016</v>
       </c>
       <c r="R20">
-        <v>0.2467771639042357</v>
+        <v>0.695906432748538</v>
       </c>
       <c r="S20">
         <v>0</v>
@@ -2826,55 +2787,55 @@
         <v>0</v>
       </c>
       <c r="U20">
-        <v>330</v>
+        <v>39.4</v>
       </c>
       <c r="V20">
-        <v>1.296660117878192</v>
+        <v>0.2543576500968366</v>
       </c>
       <c r="W20">
-        <v>0.1433852653815685</v>
+        <v>0.07946096654275094</v>
       </c>
       <c r="X20">
-        <v>0.2350078166033056</v>
+        <v>0.1359393007474313</v>
       </c>
       <c r="Y20">
-        <v>-0.0916225512217371</v>
+        <v>-0.05647833420468033</v>
       </c>
       <c r="Z20">
-        <v>0.2770536153467781</v>
+        <v>0.2316176470588235</v>
       </c>
       <c r="AA20">
         <v>0</v>
       </c>
       <c r="AB20">
-        <v>0.09681223570168637</v>
+        <v>0.09534585614566826</v>
       </c>
       <c r="AC20">
-        <v>-0.09681223570168637</v>
+        <v>-0.09534585614566826</v>
       </c>
       <c r="AD20">
-        <v>999.7</v>
+        <v>267</v>
       </c>
       <c r="AE20">
         <v>0</v>
       </c>
       <c r="AF20">
-        <v>999.7</v>
+        <v>267</v>
       </c>
       <c r="AG20">
-        <v>669.7</v>
+        <v>227.6</v>
       </c>
       <c r="AH20">
-        <v>0.7970818051347472</v>
+        <v>0.6328513865844987</v>
       </c>
       <c r="AI20">
-        <v>0.7508637524410395</v>
+        <v>0.583989501312336</v>
       </c>
       <c r="AJ20">
-        <v>0.7246267041765851</v>
+        <v>0.5950326797385621</v>
       </c>
       <c r="AK20">
-        <v>0.6687637307769123</v>
+        <v>0.5447582575394926</v>
       </c>
       <c r="AL20">
         <v>0</v>
@@ -2891,7 +2852,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Dhaka Bank Limited (DSE:DHAKABANK)</t>
+          <t>Union Bank PLC. (DSE:UNIONBANK)</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -2899,12 +2860,6 @@
           <t>Bank (Money Center)</t>
         </is>
       </c>
-      <c r="D21">
-        <v>0.0916</v>
-      </c>
-      <c r="E21">
-        <v>0.103</v>
-      </c>
       <c r="G21">
         <v>0</v>
       </c>
@@ -2918,28 +2873,28 @@
         <v>0</v>
       </c>
       <c r="K21">
-        <v>24.1</v>
+        <v>14.1</v>
       </c>
       <c r="L21">
-        <v>0.2159498207885305</v>
+        <v>0.2165898617511521</v>
       </c>
       <c r="M21">
-        <v>11.3</v>
+        <v>8.890000000000001</v>
       </c>
       <c r="N21">
-        <v>0.09269893355209188</v>
+        <v>0.1057074910820452</v>
       </c>
       <c r="O21">
-        <v>0.4688796680497925</v>
+        <v>0.6304964539007093</v>
       </c>
       <c r="P21">
-        <v>11.3</v>
+        <v>8.890000000000001</v>
       </c>
       <c r="Q21">
-        <v>0.09269893355209188</v>
+        <v>0.1057074910820452</v>
       </c>
       <c r="R21">
-        <v>0.4688796680497925</v>
+        <v>0.6304964539007093</v>
       </c>
       <c r="S21">
         <v>0</v>
@@ -2948,55 +2903,55 @@
         <v>0</v>
       </c>
       <c r="U21">
-        <v>128.2</v>
+        <v>120.4</v>
       </c>
       <c r="V21">
-        <v>1.051681706316653</v>
+        <v>1.431629013079667</v>
       </c>
       <c r="W21">
-        <v>0.1000415110004151</v>
+        <v>0.09406270847231488</v>
       </c>
       <c r="X21">
-        <v>0.2549923668174693</v>
+        <v>0.1404233159525728</v>
       </c>
       <c r="Y21">
-        <v>-0.1549508558170542</v>
+        <v>-0.04636060748025791</v>
       </c>
       <c r="Z21">
-        <v>0.1703556708899405</v>
+        <v>0.6542713567839196</v>
       </c>
       <c r="AA21">
         <v>0</v>
       </c>
       <c r="AB21">
-        <v>0.09692176099867167</v>
+        <v>0.09571432057303939</v>
       </c>
       <c r="AC21">
-        <v>-0.09692176099867167</v>
+        <v>-0.09571432057303939</v>
       </c>
       <c r="AD21">
-        <v>546</v>
+        <v>157.2</v>
       </c>
       <c r="AE21">
         <v>0</v>
       </c>
       <c r="AF21">
-        <v>546</v>
+        <v>157.2</v>
       </c>
       <c r="AG21">
-        <v>417.8</v>
+        <v>36.79999999999998</v>
       </c>
       <c r="AH21">
-        <v>0.8174876478514748</v>
+        <v>0.6514711976792374</v>
       </c>
       <c r="AI21">
-        <v>0.7172884918549658</v>
+        <v>0.5179571663920922</v>
       </c>
       <c r="AJ21">
-        <v>0.7741337780248285</v>
+        <v>0.3043837882547559</v>
       </c>
       <c r="AK21">
-        <v>0.6600315955766193</v>
+        <v>0.2009830693610048</v>
       </c>
       <c r="AL21">
         <v>0</v>
@@ -3013,7 +2968,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>First Security Islami Bank Limited (DSE:FIRSTSBANK)</t>
+          <t>Shahjalal Islami Bank PLC. (DSE:SHAHJABANK)</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -3022,10 +2977,10 @@
         </is>
       </c>
       <c r="D22">
-        <v>0.156</v>
+        <v>0.148</v>
       </c>
       <c r="E22">
-        <v>0.249</v>
+        <v>0.218</v>
       </c>
       <c r="G22">
         <v>0</v>
@@ -3040,28 +2995,28 @@
         <v>0</v>
       </c>
       <c r="K22">
-        <v>33.4</v>
+        <v>33.3</v>
       </c>
       <c r="L22">
-        <v>0.2191601049868766</v>
+        <v>0.2694174757281553</v>
       </c>
       <c r="M22">
-        <v>3.56</v>
+        <v>12.1</v>
       </c>
       <c r="N22">
-        <v>0.03570712136409228</v>
+        <v>0.06515885837372105</v>
       </c>
       <c r="O22">
-        <v>0.1065868263473054</v>
+        <v>0.3633633633633634</v>
       </c>
       <c r="P22">
-        <v>3.56</v>
+        <v>12.1</v>
       </c>
       <c r="Q22">
-        <v>0.03570712136409228</v>
+        <v>0.06515885837372105</v>
       </c>
       <c r="R22">
-        <v>0.1065868263473054</v>
+        <v>0.3633633633633634</v>
       </c>
       <c r="S22">
         <v>0</v>
@@ -3070,55 +3025,55 @@
         <v>0</v>
       </c>
       <c r="U22">
-        <v>45.2</v>
+        <v>99</v>
       </c>
       <c r="V22">
-        <v>0.4533600802407222</v>
+        <v>0.5331179321486269</v>
       </c>
       <c r="W22">
-        <v>0.1510628674807779</v>
+        <v>0.1519853947968964</v>
       </c>
       <c r="X22">
-        <v>0.273122360570509</v>
+        <v>0.1478889422349866</v>
       </c>
       <c r="Y22">
-        <v>-0.1220594930897311</v>
+        <v>0.004096452561909741</v>
       </c>
       <c r="Z22">
-        <v>0.2782545188972065</v>
+        <v>0.1779441405125252</v>
       </c>
       <c r="AA22">
         <v>0</v>
       </c>
       <c r="AB22">
-        <v>0.09700365889794203</v>
+        <v>0.09625133655333859</v>
       </c>
       <c r="AC22">
-        <v>-0.09700365889794203</v>
+        <v>-0.09625133655333859</v>
       </c>
       <c r="AD22">
-        <v>496.4</v>
+        <v>392.1</v>
       </c>
       <c r="AE22">
         <v>0</v>
       </c>
       <c r="AF22">
-        <v>496.4</v>
+        <v>392.1</v>
       </c>
       <c r="AG22">
-        <v>451.2</v>
+        <v>293.1</v>
       </c>
       <c r="AH22">
-        <v>0.832746183526254</v>
+        <v>0.6786085150571133</v>
       </c>
       <c r="AI22">
-        <v>0.6993519301211609</v>
+        <v>0.6399543006365268</v>
       </c>
       <c r="AJ22">
-        <v>0.8190234162279906</v>
+        <v>0.612155388471178</v>
       </c>
       <c r="AK22">
-        <v>0.6789046042732471</v>
+        <v>0.5705664784893907</v>
       </c>
       <c r="AL22">
         <v>0</v>
@@ -3135,7 +3090,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>United Commercial Bank Limited (DSE:UCB)</t>
+          <t>AB Bank PLC. (DSE:ABBANK)</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -3144,10 +3099,7 @@
         </is>
       </c>
       <c r="D23">
-        <v>0.08779999999999999</v>
-      </c>
-      <c r="E23">
-        <v>-0.0697</v>
+        <v>0.0799</v>
       </c>
       <c r="G23">
         <v>0</v>
@@ -3162,82 +3114,85 @@
         <v>0</v>
       </c>
       <c r="K23">
-        <v>22.1</v>
+        <v>6.74</v>
       </c>
       <c r="L23">
-        <v>0.09464668094218416</v>
+        <v>0.07846332945285216</v>
       </c>
       <c r="M23">
-        <v>-0</v>
+        <v>4.84</v>
       </c>
       <c r="N23">
-        <v>-0</v>
+        <v>0.06229086229086229</v>
       </c>
       <c r="O23">
-        <v>-0</v>
+        <v>0.7181008902077151</v>
       </c>
       <c r="P23">
-        <v>-0</v>
+        <v>4.84</v>
       </c>
       <c r="Q23">
-        <v>-0</v>
+        <v>0.06229086229086229</v>
       </c>
       <c r="R23">
-        <v>-0</v>
+        <v>0.7181008902077151</v>
       </c>
       <c r="S23">
         <v>0</v>
       </c>
+      <c r="T23">
+        <v>0</v>
+      </c>
       <c r="U23">
-        <v>223.8</v>
+        <v>125.9</v>
       </c>
       <c r="V23">
-        <v>1.258717660292463</v>
+        <v>1.62033462033462</v>
       </c>
       <c r="W23">
-        <v>0.05060682390657202</v>
+        <v>0.02660876431109356</v>
       </c>
       <c r="X23">
-        <v>0.3189490161532329</v>
+        <v>0.1518703068602115</v>
       </c>
       <c r="Y23">
-        <v>-0.2683421922466609</v>
+        <v>-0.1252615425491179</v>
       </c>
       <c r="Z23">
-        <v>0.2040905515252163</v>
+        <v>0.2276702888947787</v>
       </c>
       <c r="AA23">
         <v>0</v>
       </c>
       <c r="AB23">
-        <v>0.09716026838604841</v>
+        <v>0.09650489584854885</v>
       </c>
       <c r="AC23">
-        <v>-0.09716026838604841</v>
+        <v>-0.09650489584854885</v>
       </c>
       <c r="AD23">
-        <v>1109.9</v>
+        <v>174.1</v>
       </c>
       <c r="AE23">
         <v>0</v>
       </c>
       <c r="AF23">
-        <v>1109.9</v>
+        <v>174.1</v>
       </c>
       <c r="AG23">
-        <v>886.1000000000001</v>
+        <v>48.19999999999999</v>
       </c>
       <c r="AH23">
-        <v>0.8619243612642696</v>
+        <v>0.6914217633042097</v>
       </c>
       <c r="AI23">
-        <v>0.7406245829440812</v>
+        <v>0.425464320625611</v>
       </c>
       <c r="AJ23">
-        <v>0.8328790299840211</v>
+        <v>0.3828435266084193</v>
       </c>
       <c r="AK23">
-        <v>0.6950894257922812</v>
+        <v>0.1701376632545005</v>
       </c>
       <c r="AL23">
         <v>0</v>
@@ -3254,7 +3209,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>NRB Commercial Bank Limited (DSE:NRBCBANK)</t>
+          <t>Export Import Bank of Bangladesh Limited (DSE:EXIMBANK)</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -3263,10 +3218,10 @@
         </is>
       </c>
       <c r="D24">
-        <v>0.217</v>
+        <v>0.106</v>
       </c>
       <c r="E24">
-        <v>0.147</v>
+        <v>0.171</v>
       </c>
       <c r="G24">
         <v>0</v>
@@ -3281,28 +3236,28 @@
         <v>0</v>
       </c>
       <c r="K24">
-        <v>17.9</v>
+        <v>34.1</v>
       </c>
       <c r="L24">
-        <v>0.2220843672456576</v>
+        <v>0.2655763239875389</v>
       </c>
       <c r="M24">
-        <v>5.89</v>
+        <v>13.2</v>
       </c>
       <c r="N24">
-        <v>0.04340456890198968</v>
+        <v>0.0961398397669337</v>
       </c>
       <c r="O24">
-        <v>0.329050279329609</v>
+        <v>0.3870967741935484</v>
       </c>
       <c r="P24">
-        <v>5.89</v>
+        <v>13.2</v>
       </c>
       <c r="Q24">
-        <v>0.04340456890198968</v>
+        <v>0.0961398397669337</v>
       </c>
       <c r="R24">
-        <v>0.329050279329609</v>
+        <v>0.3870967741935484</v>
       </c>
       <c r="S24">
         <v>0</v>
@@ -3311,55 +3266,55 @@
         <v>0</v>
       </c>
       <c r="U24">
-        <v>62.7</v>
+        <v>22.7</v>
       </c>
       <c r="V24">
-        <v>0.4620486366985999</v>
+        <v>0.1653313911143481</v>
       </c>
       <c r="W24">
-        <v>0.1274928774928775</v>
+        <v>0.1062967581047382</v>
       </c>
       <c r="X24">
-        <v>0.1293390498235124</v>
+        <v>0.1637109318607808</v>
       </c>
       <c r="Y24">
-        <v>-0.001846172330634915</v>
+        <v>-0.05741417375604269</v>
       </c>
       <c r="Z24">
-        <v>0.4766410408042577</v>
+        <v>0.1633795648301311</v>
       </c>
       <c r="AA24">
         <v>0</v>
       </c>
       <c r="AB24">
-        <v>0.09785508618214127</v>
+        <v>0.09715217368987458</v>
       </c>
       <c r="AC24">
-        <v>-0.09785508618214127</v>
+        <v>-0.09715217368987458</v>
       </c>
       <c r="AD24">
-        <v>137.7</v>
+        <v>360.4</v>
       </c>
       <c r="AE24">
         <v>0</v>
       </c>
       <c r="AF24">
-        <v>137.7</v>
+        <v>360.4</v>
       </c>
       <c r="AG24">
-        <v>74.99999999999999</v>
+        <v>337.7</v>
       </c>
       <c r="AH24">
-        <v>0.5036576444769568</v>
+        <v>0.7241310026120152</v>
       </c>
       <c r="AI24">
-        <v>0.5255725190839694</v>
+        <v>0.549725442342892</v>
       </c>
       <c r="AJ24">
-        <v>0.3559563360227812</v>
+        <v>0.7109473684210527</v>
       </c>
       <c r="AK24">
-        <v>0.376317109884596</v>
+        <v>0.5335756043608785</v>
       </c>
       <c r="AL24">
         <v>0</v>
@@ -3376,7 +3331,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>South Bangla Agriculture and Commerce Bank Limited (DSE:SBACBANK)</t>
+          <t>Southeast Bank PLC. (DSE:SOUTHEASTB)</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -3384,6 +3339,12 @@
           <t>Bank (Money Center)</t>
         </is>
       </c>
+      <c r="D25">
+        <v>0.0372</v>
+      </c>
+      <c r="E25">
+        <v>0.00688</v>
+      </c>
       <c r="G25">
         <v>0</v>
       </c>
@@ -3397,28 +3358,28 @@
         <v>0</v>
       </c>
       <c r="K25">
-        <v>4.82</v>
+        <v>12</v>
       </c>
       <c r="L25">
-        <v>0.106401766004415</v>
+        <v>0.1264488935721812</v>
       </c>
       <c r="M25">
-        <v>4.7</v>
+        <v>6.74</v>
       </c>
       <c r="N25">
-        <v>0.0558858501783591</v>
+        <v>0.04323284156510584</v>
       </c>
       <c r="O25">
-        <v>0.975103734439834</v>
+        <v>0.5616666666666666</v>
       </c>
       <c r="P25">
-        <v>4.7</v>
+        <v>6.74</v>
       </c>
       <c r="Q25">
-        <v>0.0558858501783591</v>
+        <v>0.04323284156510584</v>
       </c>
       <c r="R25">
-        <v>0.975103734439834</v>
+        <v>0.5616666666666666</v>
       </c>
       <c r="S25">
         <v>0</v>
@@ -3427,55 +3388,55 @@
         <v>0</v>
       </c>
       <c r="U25">
-        <v>34.7</v>
+        <v>340.3</v>
       </c>
       <c r="V25">
-        <v>0.4126040428061832</v>
+        <v>2.182809493264914</v>
       </c>
       <c r="W25">
-        <v>0.03618618618618619</v>
+        <v>0.03723239218119764</v>
       </c>
       <c r="X25">
-        <v>0.1233703812360858</v>
+        <v>0.1676991256342311</v>
       </c>
       <c r="Y25">
-        <v>-0.08718419504989963</v>
+        <v>-0.1304667334530335</v>
       </c>
       <c r="Z25">
-        <v>0.4773445732349844</v>
+        <v>0.2716084716657126</v>
       </c>
       <c r="AA25">
         <v>0</v>
       </c>
       <c r="AB25">
-        <v>0.09856733668593165</v>
+        <v>0.09734036287510843</v>
       </c>
       <c r="AC25">
-        <v>-0.09856733668593165</v>
+        <v>-0.09734036287510843</v>
       </c>
       <c r="AD25">
-        <v>71.5</v>
+        <v>429.4</v>
       </c>
       <c r="AE25">
         <v>0</v>
       </c>
       <c r="AF25">
-        <v>71.5</v>
+        <v>429.4</v>
       </c>
       <c r="AG25">
-        <v>36.8</v>
+        <v>89.09999999999997</v>
       </c>
       <c r="AH25">
-        <v>0.4595115681233933</v>
+        <v>0.7336408679309756</v>
       </c>
       <c r="AI25">
-        <v>0.3970016657412549</v>
+        <v>0.5882997670913823</v>
       </c>
       <c r="AJ25">
-        <v>0.304383788254756</v>
+        <v>0.363673469387755</v>
       </c>
       <c r="AK25">
-        <v>0.2530949105914718</v>
+        <v>0.2286960985626283</v>
       </c>
       <c r="AL25">
         <v>0</v>
@@ -3492,7 +3453,7 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>International Finance Investment and Commerce Bank Limited (DSE:IFIC)</t>
+          <t>Al-Arafah Islami Bank PLC. (DSE:ALARABANK)</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -3501,10 +3462,10 @@
         </is>
       </c>
       <c r="D26">
-        <v>0.113</v>
+        <v>0.08539999999999999</v>
       </c>
       <c r="E26">
-        <v>0.0329</v>
+        <v>-0.00329</v>
       </c>
       <c r="G26">
         <v>0</v>
@@ -3519,82 +3480,85 @@
         <v>0</v>
       </c>
       <c r="K26">
-        <v>20.7</v>
+        <v>18.9</v>
       </c>
       <c r="L26">
-        <v>0.169255928045789</v>
+        <v>0.1483516483516483</v>
       </c>
       <c r="M26">
-        <v>-0</v>
+        <v>12</v>
       </c>
       <c r="N26">
-        <v>-0</v>
+        <v>0.05063291139240506</v>
       </c>
       <c r="O26">
-        <v>-0</v>
+        <v>0.634920634920635</v>
       </c>
       <c r="P26">
-        <v>-0</v>
+        <v>12</v>
       </c>
       <c r="Q26">
-        <v>-0</v>
+        <v>0.05063291139240506</v>
       </c>
       <c r="R26">
-        <v>-0</v>
+        <v>0.634920634920635</v>
       </c>
       <c r="S26">
         <v>0</v>
       </c>
+      <c r="T26">
+        <v>0</v>
+      </c>
       <c r="U26">
-        <v>237.4</v>
+        <v>621.7</v>
       </c>
       <c r="V26">
-        <v>1.188783174762143</v>
+        <v>2.623206751054853</v>
       </c>
       <c r="W26">
-        <v>0.05882352941176471</v>
+        <v>0.07971320118093631</v>
       </c>
       <c r="X26">
-        <v>0.1512896255881976</v>
+        <v>0.1693925421602987</v>
       </c>
       <c r="Y26">
-        <v>-0.09246609617643288</v>
+        <v>-0.08967934097936239</v>
       </c>
       <c r="Z26">
-        <v>0.2977842707572438</v>
+        <v>0.3105045088959298</v>
       </c>
       <c r="AA26">
         <v>0</v>
       </c>
       <c r="AB26">
-        <v>0.09906637530407397</v>
+        <v>0.09741640182380007</v>
       </c>
       <c r="AC26">
-        <v>-0.09906637530407397</v>
+        <v>-0.09741640182380007</v>
       </c>
       <c r="AD26">
-        <v>323.5</v>
+        <v>665.8</v>
       </c>
       <c r="AE26">
         <v>0</v>
       </c>
       <c r="AF26">
-        <v>323.5</v>
+        <v>665.8</v>
       </c>
       <c r="AG26">
-        <v>86.09999999999999</v>
+        <v>44.09999999999991</v>
       </c>
       <c r="AH26">
-        <v>0.6183103975535168</v>
+        <v>0.7374833850243686</v>
       </c>
       <c r="AI26">
-        <v>0.5039725813989718</v>
+        <v>0.7387107511372462</v>
       </c>
       <c r="AJ26">
-        <v>0.301259622113366</v>
+        <v>0.1568836712913551</v>
       </c>
       <c r="AK26">
-        <v>0.2128553770086526</v>
+        <v>0.1577253218884117</v>
       </c>
       <c r="AL26">
         <v>0</v>
@@ -3611,7 +3575,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>AB Bank Limited (DSE:ABBANK)</t>
+          <t>Dutch-Bangla Bank PLC. (DSE:DUTCHBANGL)</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -3620,10 +3584,10 @@
         </is>
       </c>
       <c r="D27">
-        <v>0.07389999999999999</v>
+        <v>0.0626</v>
       </c>
       <c r="E27">
-        <v>0.0106</v>
+        <v>0.136</v>
       </c>
       <c r="G27">
         <v>0</v>
@@ -3638,28 +3602,28 @@
         <v>0</v>
       </c>
       <c r="K27">
-        <v>7.94</v>
+        <v>52.7</v>
       </c>
       <c r="L27">
-        <v>0.08546824542518837</v>
+        <v>0.204978607545702</v>
       </c>
       <c r="M27">
-        <v>4.31</v>
+        <v>11.1</v>
       </c>
       <c r="N27">
-        <v>0.0519903498190591</v>
+        <v>0.02754342431761787</v>
       </c>
       <c r="O27">
-        <v>0.5428211586901762</v>
+        <v>0.2106261859582542</v>
       </c>
       <c r="P27">
-        <v>4.31</v>
+        <v>11.1</v>
       </c>
       <c r="Q27">
-        <v>0.0519903498190591</v>
+        <v>0.02754342431761787</v>
       </c>
       <c r="R27">
-        <v>0.5428211586901762</v>
+        <v>0.2106261859582542</v>
       </c>
       <c r="S27">
         <v>0</v>
@@ -3668,55 +3632,55 @@
         <v>0</v>
       </c>
       <c r="U27">
-        <v>101</v>
+        <v>382.6</v>
       </c>
       <c r="V27">
-        <v>1.218335343787696</v>
+        <v>0.9493796526054591</v>
       </c>
       <c r="W27">
-        <v>0.02593076420640105</v>
+        <v>0.1332490518331226</v>
       </c>
       <c r="X27">
-        <v>0.1909761672036192</v>
+        <v>0.1060068978521062</v>
       </c>
       <c r="Y27">
-        <v>-0.1650454029972181</v>
+        <v>0.02724215398101645</v>
       </c>
       <c r="Z27">
-        <v>0.1328281384043466</v>
+        <v>0.5400126023944549</v>
       </c>
       <c r="AA27">
         <v>0</v>
       </c>
       <c r="AB27">
-        <v>0.1002543540205364</v>
+        <v>0.09772968340253969</v>
       </c>
       <c r="AC27">
-        <v>-0.1002543540205364</v>
+        <v>-0.09772968340253969</v>
       </c>
       <c r="AD27">
-        <v>225</v>
+        <v>303.2</v>
       </c>
       <c r="AE27">
         <v>0</v>
       </c>
       <c r="AF27">
-        <v>225</v>
+        <v>303.2</v>
       </c>
       <c r="AG27">
-        <v>124</v>
+        <v>-79.40000000000003</v>
       </c>
       <c r="AH27">
-        <v>0.7307567392010393</v>
+        <v>0.4293401302747097</v>
       </c>
       <c r="AI27">
-        <v>0.4703177257525084</v>
+        <v>0.4289149809025322</v>
       </c>
       <c r="AJ27">
-        <v>0.5993233446109232</v>
+        <v>-0.2453646477132263</v>
       </c>
       <c r="AK27">
-        <v>0.3285638579756227</v>
+        <v>-0.2448350292938639</v>
       </c>
       <c r="AL27">
         <v>0</v>
@@ -3733,7 +3697,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Shahjalal Islami Bank Limited (DSE:SHAHJABANK)</t>
+          <t>Prime Bank PLC. (DSE:PRIMEBANK)</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -3742,10 +3706,10 @@
         </is>
       </c>
       <c r="D28">
-        <v>0.156</v>
+        <v>0.07829999999999999</v>
       </c>
       <c r="E28">
-        <v>0.147</v>
+        <v>0.347</v>
       </c>
       <c r="G28">
         <v>0</v>
@@ -3760,28 +3724,28 @@
         <v>0</v>
       </c>
       <c r="K28">
-        <v>36.4</v>
+        <v>42.3</v>
       </c>
       <c r="L28">
-        <v>0.2708333333333333</v>
+        <v>0.3017118402282454</v>
       </c>
       <c r="M28">
-        <v>13.1</v>
+        <v>18</v>
       </c>
       <c r="N28">
-        <v>0.06629554655870445</v>
+        <v>0.08341056533827618</v>
       </c>
       <c r="O28">
-        <v>0.3598901098901099</v>
+        <v>0.425531914893617</v>
       </c>
       <c r="P28">
-        <v>13.1</v>
+        <v>18</v>
       </c>
       <c r="Q28">
-        <v>0.06629554655870445</v>
+        <v>0.08341056533827618</v>
       </c>
       <c r="R28">
-        <v>0.3598901098901099</v>
+        <v>0.425531914893617</v>
       </c>
       <c r="S28">
         <v>0</v>
@@ -3790,55 +3754,55 @@
         <v>0</v>
       </c>
       <c r="U28">
-        <v>117.7</v>
+        <v>90.3</v>
       </c>
       <c r="V28">
-        <v>0.5956477732793523</v>
+        <v>0.4184430027803521</v>
       </c>
       <c r="W28">
-        <v>0.155955441302485</v>
+        <v>0.1384162303664921</v>
       </c>
       <c r="X28">
-        <v>0.2014188288258651</v>
+        <v>0.1946758286756308</v>
       </c>
       <c r="Y28">
-        <v>-0.04546338752338011</v>
+        <v>-0.05625959830913868</v>
       </c>
       <c r="Z28">
-        <v>0.23712067748765</v>
+        <v>0.1536438356164384</v>
       </c>
       <c r="AA28">
         <v>0</v>
       </c>
       <c r="AB28">
-        <v>0.1023830665066036</v>
+        <v>0.09833702250424345</v>
       </c>
       <c r="AC28">
-        <v>-0.1023830665066036</v>
+        <v>-0.09833702250424345</v>
       </c>
       <c r="AD28">
-        <v>593.2</v>
+        <v>783.3</v>
       </c>
       <c r="AE28">
         <v>0</v>
       </c>
       <c r="AF28">
-        <v>593.2</v>
+        <v>783.3</v>
       </c>
       <c r="AG28">
-        <v>475.5000000000001</v>
+        <v>693</v>
       </c>
       <c r="AH28">
-        <v>0.750126454223571</v>
+        <v>0.7840056050445401</v>
       </c>
       <c r="AI28">
-        <v>0.728120780655456</v>
+        <v>0.7190196438406461</v>
       </c>
       <c r="AJ28">
-        <v>0.7064329222998069</v>
+        <v>0.7625440140845071</v>
       </c>
       <c r="AK28">
-        <v>0.6822094691535151</v>
+        <v>0.6936242618356521</v>
       </c>
       <c r="AL28">
         <v>0</v>
@@ -3855,7 +3819,7 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Al-Arafah Islami Bank Limited (DSE:ALARABANK)</t>
+          <t>United Commercial Bank PLC (DSE:UCB)</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -3864,10 +3828,10 @@
         </is>
       </c>
       <c r="D29">
-        <v>0.0374</v>
+        <v>0.112</v>
       </c>
       <c r="E29">
-        <v>-0.0759</v>
+        <v>0.0964</v>
       </c>
       <c r="G29">
         <v>0</v>
@@ -3882,28 +3846,28 @@
         <v>0</v>
       </c>
       <c r="K29">
-        <v>22.5</v>
+        <v>28.4</v>
       </c>
       <c r="L29">
-        <v>0.1596877217885025</v>
+        <v>0.1174038859032658</v>
       </c>
       <c r="M29">
-        <v>17.1</v>
+        <v>6.39</v>
       </c>
       <c r="N29">
-        <v>0.06996726677577741</v>
+        <v>0.03828639904134212</v>
       </c>
       <c r="O29">
-        <v>0.76</v>
+        <v>0.225</v>
       </c>
       <c r="P29">
-        <v>17.1</v>
+        <v>6.39</v>
       </c>
       <c r="Q29">
-        <v>0.06996726677577741</v>
+        <v>0.03828639904134212</v>
       </c>
       <c r="R29">
-        <v>0.76</v>
+        <v>0.225</v>
       </c>
       <c r="S29">
         <v>0</v>
@@ -3912,55 +3876,55 @@
         <v>0</v>
       </c>
       <c r="U29">
-        <v>605.5</v>
+        <v>275.2</v>
       </c>
       <c r="V29">
-        <v>2.477495908346972</v>
+        <v>1.648891551827441</v>
       </c>
       <c r="W29">
-        <v>0.08143322475570032</v>
+        <v>0.07306405968613326</v>
       </c>
       <c r="X29">
-        <v>0.2082462927398155</v>
+        <v>0.1957642133902373</v>
       </c>
       <c r="Y29">
-        <v>-0.1268130679841152</v>
+        <v>-0.122700153704104</v>
       </c>
       <c r="Z29">
-        <v>0.9337309476474481</v>
+        <v>0.1897552557263884</v>
       </c>
       <c r="AA29">
         <v>0</v>
       </c>
       <c r="AB29">
-        <v>0.1025304487600801</v>
+        <v>0.09836938297090576</v>
       </c>
       <c r="AC29">
-        <v>-0.1025304487600801</v>
+        <v>-0.09836938297090576</v>
       </c>
       <c r="AD29">
-        <v>779.7</v>
+        <v>611.7</v>
       </c>
       <c r="AE29">
         <v>0</v>
       </c>
       <c r="AF29">
-        <v>779.7</v>
+        <v>611.7</v>
       </c>
       <c r="AG29">
-        <v>174.2</v>
+        <v>336.5000000000001</v>
       </c>
       <c r="AH29">
-        <v>0.7613514305243628</v>
+        <v>0.7856408939121501</v>
       </c>
       <c r="AI29">
-        <v>0.740315229775921</v>
+        <v>0.6218359255870692</v>
       </c>
       <c r="AJ29">
-        <v>0.4161490683229814</v>
+        <v>0.6684545093365117</v>
       </c>
       <c r="AK29">
-        <v>0.3890998436452983</v>
+        <v>0.4749470712773466</v>
       </c>
       <c r="AL29">
         <v>0</v>
@@ -3977,7 +3941,7 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>BRAC Bank Limited (DSE:BRACBANK)</t>
+          <t>First Security Islami Bank PLC (DSE:FIRSTSBANK)</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -3986,10 +3950,10 @@
         </is>
       </c>
       <c r="D30">
-        <v>0.0866</v>
+        <v>0.15</v>
       </c>
       <c r="E30">
-        <v>0.006750000000000001</v>
+        <v>0.251</v>
       </c>
       <c r="G30">
         <v>0</v>
@@ -4004,28 +3968,28 @@
         <v>0</v>
       </c>
       <c r="K30">
-        <v>52.2</v>
+        <v>29.1</v>
       </c>
       <c r="L30">
-        <v>0.1578947368421053</v>
+        <v>0.2004132231404959</v>
       </c>
       <c r="M30">
-        <v>10.4</v>
+        <v>4.45</v>
       </c>
       <c r="N30">
-        <v>0.01856148491879351</v>
+        <v>0.04764453961456103</v>
       </c>
       <c r="O30">
-        <v>0.1992337164750958</v>
+        <v>0.1529209621993127</v>
       </c>
       <c r="P30">
-        <v>10.4</v>
+        <v>4.45</v>
       </c>
       <c r="Q30">
-        <v>0.01856148491879351</v>
+        <v>0.04764453961456103</v>
       </c>
       <c r="R30">
-        <v>0.1992337164750958</v>
+        <v>0.1529209621993127</v>
       </c>
       <c r="S30">
         <v>0</v>
@@ -4034,60 +3998,182 @@
         <v>0</v>
       </c>
       <c r="U30">
-        <v>545.4</v>
+        <v>57.4</v>
       </c>
       <c r="V30">
-        <v>0.9734071033374978</v>
+        <v>0.6145610278372591</v>
       </c>
       <c r="W30">
-        <v>0.09031141868512112</v>
+        <v>0.1387696709585122</v>
       </c>
       <c r="X30">
-        <v>0.1414211389350766</v>
+        <v>0.4356526015398579</v>
       </c>
       <c r="Y30">
-        <v>-0.05110972024995551</v>
+        <v>-0.2968829305813457</v>
       </c>
       <c r="Z30">
-        <v>1.2271714922049</v>
+        <v>0.2197004085338176</v>
       </c>
       <c r="AA30">
         <v>0</v>
       </c>
       <c r="AB30">
-        <v>0.1099529033286276</v>
+        <v>0.1010217947022278</v>
       </c>
       <c r="AC30">
-        <v>-0.1099529033286276</v>
+        <v>-0.1010217947022278</v>
       </c>
       <c r="AD30">
-        <v>755.2</v>
+        <v>1069.4</v>
       </c>
       <c r="AE30">
         <v>0</v>
       </c>
       <c r="AF30">
-        <v>755.2</v>
+        <v>1069.4</v>
       </c>
       <c r="AG30">
-        <v>209.8000000000001</v>
+        <v>1012</v>
       </c>
       <c r="AH30">
-        <v>0.5740782972253896</v>
+        <v>0.9196766425868592</v>
       </c>
       <c r="AI30">
-        <v>0.4901668072953853</v>
+        <v>0.8295066708035992</v>
       </c>
       <c r="AJ30">
-        <v>0.2724321516686146</v>
+        <v>0.9155056992943731</v>
       </c>
       <c r="AK30">
-        <v>0.2107907163669246</v>
+        <v>0.8215619418736808</v>
       </c>
       <c r="AL30">
         <v>0</v>
       </c>
       <c r="AM30">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>Bangladesh</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>BRAC Bank PLC. (DSE:BRACBANK)</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>Bank (Money Center)</t>
+        </is>
+      </c>
+      <c r="D31">
+        <v>0.112</v>
+      </c>
+      <c r="E31">
+        <v>0.0672</v>
+      </c>
+      <c r="G31">
+        <v>0</v>
+      </c>
+      <c r="H31">
+        <v>0</v>
+      </c>
+      <c r="I31">
+        <v>0</v>
+      </c>
+      <c r="J31">
+        <v>0</v>
+      </c>
+      <c r="K31">
+        <v>68</v>
+      </c>
+      <c r="L31">
+        <v>0.1784308580425085</v>
+      </c>
+      <c r="M31">
+        <v>10.1</v>
+      </c>
+      <c r="N31">
+        <v>0.01923076923076923</v>
+      </c>
+      <c r="O31">
+        <v>0.1485294117647059</v>
+      </c>
+      <c r="P31">
+        <v>10.1</v>
+      </c>
+      <c r="Q31">
+        <v>0.01923076923076923</v>
+      </c>
+      <c r="R31">
+        <v>0.1485294117647059</v>
+      </c>
+      <c r="S31">
+        <v>0</v>
+      </c>
+      <c r="T31">
+        <v>0</v>
+      </c>
+      <c r="U31">
+        <v>596.1</v>
+      </c>
+      <c r="V31">
+        <v>1.134996191926885</v>
+      </c>
+      <c r="W31">
+        <v>0.1153911420329204</v>
+      </c>
+      <c r="X31">
+        <v>0.1427464889237717</v>
+      </c>
+      <c r="Y31">
+        <v>-0.02735534689085131</v>
+      </c>
+      <c r="Z31">
+        <v>0.4851686823679185</v>
+      </c>
+      <c r="AA31">
+        <v>0</v>
+      </c>
+      <c r="AB31">
+        <v>0.1035984306897147</v>
+      </c>
+      <c r="AC31">
+        <v>-0.1035984306897147</v>
+      </c>
+      <c r="AD31">
+        <v>1021.3</v>
+      </c>
+      <c r="AE31">
+        <v>0</v>
+      </c>
+      <c r="AF31">
+        <v>1021.3</v>
+      </c>
+      <c r="AG31">
+        <v>425.1999999999999</v>
+      </c>
+      <c r="AH31">
+        <v>0.6603944390559328</v>
+      </c>
+      <c r="AI31">
+        <v>0.5689059714795009</v>
+      </c>
+      <c r="AJ31">
+        <v>0.4473905723905723</v>
+      </c>
+      <c r="AK31">
+        <v>0.3545992827954298</v>
+      </c>
+      <c r="AL31">
+        <v>0</v>
+      </c>
+      <c r="AM31">
         <v>0</v>
       </c>
     </row>

--- a/research/traditional_assets/database/data/bangladesh/bangladesh_bank_money_center.xlsx
+++ b/research/traditional_assets/database/data/bangladesh/bangladesh_bank_money_center.xlsx
@@ -351,7 +351,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AQ4"/>
+  <dimension ref="A1:AQ35"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -579,7 +579,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>33</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -588,10 +588,13 @@
         </is>
       </c>
       <c r="D2">
-        <v>0.1133</v>
+        <v>0.09630000000000001</v>
       </c>
       <c r="E2">
-        <v>0.11335</v>
+        <v>0.04969999999999999</v>
+      </c>
+      <c r="F2">
+        <v>0.135</v>
       </c>
       <c r="G2">
         <v>0</v>
@@ -606,28 +609,28 @@
         <v>0</v>
       </c>
       <c r="K2">
-        <v>144.6</v>
+        <v>643.47</v>
       </c>
       <c r="L2">
-        <v>0.1946164199192463</v>
+        <v>0.1407969016673231</v>
       </c>
       <c r="M2">
-        <v>24.2</v>
+        <v>298.66</v>
       </c>
       <c r="N2">
-        <v>0.02249697871153667</v>
+        <v>0.05481609279788562</v>
       </c>
       <c r="O2">
-        <v>0.1673582295988935</v>
+        <v>0.46413974233453</v>
       </c>
       <c r="P2">
-        <v>24.2</v>
+        <v>298.66</v>
       </c>
       <c r="Q2">
-        <v>0.02249697871153667</v>
+        <v>0.05481609279788562</v>
       </c>
       <c r="R2">
-        <v>0.1673582295988935</v>
+        <v>0.46413974233453</v>
       </c>
       <c r="S2">
         <v>0</v>
@@ -636,55 +639,55 @@
         <v>0</v>
       </c>
       <c r="U2">
-        <v>792.5</v>
+        <v>7241.7</v>
       </c>
       <c r="V2">
-        <v>0.7367295714418518</v>
+        <v>1.32914250055062</v>
       </c>
       <c r="W2">
-        <v>0.1432100376398437</v>
+        <v>0.1008784773060029</v>
       </c>
       <c r="X2">
-        <v>0.1281919055536881</v>
+        <v>0.1643793464370381</v>
       </c>
       <c r="Y2">
-        <v>0.0150181320861556</v>
+        <v>-0.06350086913103518</v>
       </c>
       <c r="Z2">
-        <v>0.5607123990642217</v>
+        <v>0.3160865084689495</v>
       </c>
       <c r="AA2">
         <v>0</v>
       </c>
       <c r="AB2">
-        <v>0.1074371278732116</v>
+        <v>0.1037510953913832</v>
       </c>
       <c r="AC2">
-        <v>-0.1074371278732116</v>
+        <v>-0.1037510953913832</v>
       </c>
       <c r="AD2">
-        <v>1330.5</v>
+        <v>13833.1</v>
       </c>
       <c r="AE2">
         <v>0</v>
       </c>
       <c r="AF2">
-        <v>1330.5</v>
+        <v>13833.1</v>
       </c>
       <c r="AG2">
-        <v>538</v>
+        <v>6591.400000000001</v>
       </c>
       <c r="AH2">
-        <v>0.5529465547336049</v>
+        <v>0.7174286232917564</v>
       </c>
       <c r="AI2">
-        <v>0.5217442453237128</v>
+        <v>0.6263374038404941</v>
       </c>
       <c r="AJ2">
-        <v>0.3333953027204561</v>
+        <v>0.5474675659064104</v>
       </c>
       <c r="AK2">
-        <v>0.3060992262175694</v>
+        <v>0.4440447318782</v>
       </c>
       <c r="AL2">
         <v>0</v>
@@ -701,7 +704,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Dutch-Bangla Bank PLC. (DSE:DUTCHBANGL)</t>
+          <t>Uttara Bank PLC. (DSE:UTTARABANK)</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -710,10 +713,10 @@
         </is>
       </c>
       <c r="D3">
-        <v>0.0736</v>
+        <v>0.0949</v>
       </c>
       <c r="E3">
-        <v>0.04969999999999999</v>
+        <v>0.182</v>
       </c>
       <c r="G3">
         <v>0</v>
@@ -728,28 +731,28 @@
         <v>0</v>
       </c>
       <c r="K3">
-        <v>52.2</v>
+        <v>36.5</v>
       </c>
       <c r="L3">
-        <v>0.1832865168539326</v>
+        <v>0.2910685805422648</v>
       </c>
       <c r="M3">
-        <v>10.7</v>
+        <v>10.3</v>
       </c>
       <c r="N3">
-        <v>0.03044096728307254</v>
+        <v>0.06666666666666667</v>
       </c>
       <c r="O3">
-        <v>0.2049808429118774</v>
+        <v>0.2821917808219178</v>
       </c>
       <c r="P3">
-        <v>10.7</v>
+        <v>10.3</v>
       </c>
       <c r="Q3">
-        <v>0.03044096728307254</v>
+        <v>0.06666666666666667</v>
       </c>
       <c r="R3">
-        <v>0.2049808429118774</v>
+        <v>0.2821917808219178</v>
       </c>
       <c r="S3">
         <v>0</v>
@@ -758,55 +761,55 @@
         <v>0</v>
       </c>
       <c r="U3">
-        <v>367.7</v>
+        <v>142.4</v>
       </c>
       <c r="V3">
-        <v>1.046088193456614</v>
+        <v>0.9216828478964402</v>
       </c>
       <c r="W3">
-        <v>0.1293039385682438</v>
+        <v>0.186414708886619</v>
       </c>
       <c r="X3">
-        <v>0.1185370218234382</v>
+        <v>0.09579402469002586</v>
       </c>
       <c r="Y3">
-        <v>0.01076691674480557</v>
+        <v>0.09062068419659312</v>
       </c>
       <c r="Z3">
-        <v>0.878199198273204</v>
+        <v>1.215116279069767</v>
       </c>
       <c r="AA3">
         <v>0</v>
       </c>
       <c r="AB3">
-        <v>0.106113406179289</v>
+        <v>0.09387522156601094</v>
       </c>
       <c r="AC3">
-        <v>-0.106113406179289</v>
+        <v>-0.09387522156601094</v>
       </c>
       <c r="AD3">
-        <v>292.7</v>
+        <v>19.4</v>
       </c>
       <c r="AE3">
         <v>0</v>
       </c>
       <c r="AF3">
-        <v>292.7</v>
+        <v>19.4</v>
       </c>
       <c r="AG3">
-        <v>-75</v>
+        <v>-123</v>
       </c>
       <c r="AH3">
-        <v>0.4543619993790748</v>
+        <v>0.1115583668775158</v>
       </c>
       <c r="AI3">
-        <v>0.416180861652211</v>
+        <v>0.08568904593639576</v>
       </c>
       <c r="AJ3">
-        <v>-0.27124773960217</v>
+        <v>-3.904761904761905</v>
       </c>
       <c r="AK3">
-        <v>-0.2234803337306317</v>
+        <v>-1.464285714285714</v>
       </c>
       <c r="AL3">
         <v>0</v>
@@ -823,117 +826,3842 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
+          <t>Midland Bank PLC. (DSE:MIDLANDBNK)</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Bank (Money Center)</t>
+        </is>
+      </c>
+      <c r="G4">
+        <v>0</v>
+      </c>
+      <c r="H4">
+        <v>0</v>
+      </c>
+      <c r="I4">
+        <v>0</v>
+      </c>
+      <c r="J4">
+        <v>0</v>
+      </c>
+      <c r="K4">
+        <v>9.23</v>
+      </c>
+      <c r="L4">
+        <v>0.3431226765799257</v>
+      </c>
+      <c r="M4">
+        <v>2.67</v>
+      </c>
+      <c r="N4">
+        <v>0.01601679664067187</v>
+      </c>
+      <c r="O4">
+        <v>0.2892741061755146</v>
+      </c>
+      <c r="P4">
+        <v>2.67</v>
+      </c>
+      <c r="Q4">
+        <v>0.01601679664067187</v>
+      </c>
+      <c r="R4">
+        <v>0.2892741061755146</v>
+      </c>
+      <c r="S4">
+        <v>0</v>
+      </c>
+      <c r="T4">
+        <v>0</v>
+      </c>
+      <c r="U4">
+        <v>33.5</v>
+      </c>
+      <c r="V4">
+        <v>0.2009598080383923</v>
+      </c>
+      <c r="W4">
+        <v>0.1209698558322412</v>
+      </c>
+      <c r="X4">
+        <v>0.1030628894948253</v>
+      </c>
+      <c r="Y4">
+        <v>0.01790696633741591</v>
+      </c>
+      <c r="Z4">
+        <v>0.2266217354675653</v>
+      </c>
+      <c r="AA4">
+        <v>0</v>
+      </c>
+      <c r="AB4">
+        <v>0.09669859715332249</v>
+      </c>
+      <c r="AC4">
+        <v>-0.09669859715332249</v>
+      </c>
+      <c r="AD4">
+        <v>58.6</v>
+      </c>
+      <c r="AE4">
+        <v>0</v>
+      </c>
+      <c r="AF4">
+        <v>58.6</v>
+      </c>
+      <c r="AG4">
+        <v>25.1</v>
+      </c>
+      <c r="AH4">
+        <v>0.2600976475810031</v>
+      </c>
+      <c r="AI4">
+        <v>0.4327917282127031</v>
+      </c>
+      <c r="AJ4">
+        <v>0.1308654848800834</v>
+      </c>
+      <c r="AK4">
+        <v>0.2463199214916585</v>
+      </c>
+      <c r="AL4">
+        <v>0</v>
+      </c>
+      <c r="AM4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Bangladesh</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>SBAC Bank PLC. (DSE:SBACBANK)</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Bank (Money Center)</t>
+        </is>
+      </c>
+      <c r="G5">
+        <v>0</v>
+      </c>
+      <c r="H5">
+        <v>0</v>
+      </c>
+      <c r="I5">
+        <v>0</v>
+      </c>
+      <c r="J5">
+        <v>0</v>
+      </c>
+      <c r="K5">
+        <v>6.96</v>
+      </c>
+      <c r="L5">
+        <v>0.1714285714285714</v>
+      </c>
+      <c r="M5">
+        <v>1.15</v>
+      </c>
+      <c r="N5">
+        <v>0.02198852772466539</v>
+      </c>
+      <c r="O5">
+        <v>0.1652298850574712</v>
+      </c>
+      <c r="P5">
+        <v>1.15</v>
+      </c>
+      <c r="Q5">
+        <v>0.02198852772466539</v>
+      </c>
+      <c r="R5">
+        <v>0.1652298850574712</v>
+      </c>
+      <c r="S5">
+        <v>0</v>
+      </c>
+      <c r="T5">
+        <v>0</v>
+      </c>
+      <c r="U5">
+        <v>78.3</v>
+      </c>
+      <c r="V5">
+        <v>1.497131931166348</v>
+      </c>
+      <c r="W5">
+        <v>0.06904761904761905</v>
+      </c>
+      <c r="X5">
+        <v>0.1126057503591027</v>
+      </c>
+      <c r="Y5">
+        <v>-0.04355813131148362</v>
+      </c>
+      <c r="Z5">
+        <v>0.6160849772382397</v>
+      </c>
+      <c r="AA5">
+        <v>0</v>
+      </c>
+      <c r="AB5">
+        <v>0.09854168700353479</v>
+      </c>
+      <c r="AC5">
+        <v>-0.09854168700353479</v>
+      </c>
+      <c r="AD5">
+        <v>33.9</v>
+      </c>
+      <c r="AE5">
+        <v>0</v>
+      </c>
+      <c r="AF5">
+        <v>33.9</v>
+      </c>
+      <c r="AG5">
+        <v>-44.4</v>
+      </c>
+      <c r="AH5">
+        <v>0.3932714617169374</v>
+      </c>
+      <c r="AI5">
+        <v>0.2568181818181818</v>
+      </c>
+      <c r="AJ5">
+        <v>-5.620253164556963</v>
+      </c>
+      <c r="AK5">
+        <v>-0.8268156424581006</v>
+      </c>
+      <c r="AL5">
+        <v>0</v>
+      </c>
+      <c r="AM5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Bangladesh</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Jamuna Bank PLC. (DSE:JAMUNABANK)</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Bank (Money Center)</t>
+        </is>
+      </c>
+      <c r="D6">
+        <v>0.1</v>
+      </c>
+      <c r="E6">
+        <v>0.0198</v>
+      </c>
+      <c r="G6">
+        <v>0</v>
+      </c>
+      <c r="H6">
+        <v>0</v>
+      </c>
+      <c r="I6">
+        <v>0</v>
+      </c>
+      <c r="J6">
+        <v>0</v>
+      </c>
+      <c r="K6">
+        <v>26.5</v>
+      </c>
+      <c r="L6">
+        <v>0.1970260223048327</v>
+      </c>
+      <c r="M6">
+        <v>11.9</v>
+      </c>
+      <c r="N6">
+        <v>0.08240997229916898</v>
+      </c>
+      <c r="O6">
+        <v>0.4490566037735849</v>
+      </c>
+      <c r="P6">
+        <v>11.9</v>
+      </c>
+      <c r="Q6">
+        <v>0.08240997229916898</v>
+      </c>
+      <c r="R6">
+        <v>0.4490566037735849</v>
+      </c>
+      <c r="S6">
+        <v>0</v>
+      </c>
+      <c r="T6">
+        <v>0</v>
+      </c>
+      <c r="U6">
+        <v>41.8</v>
+      </c>
+      <c r="V6">
+        <v>0.2894736842105263</v>
+      </c>
+      <c r="W6">
+        <v>0.1393270241850684</v>
+      </c>
+      <c r="X6">
+        <v>0.1284008249448458</v>
+      </c>
+      <c r="Y6">
+        <v>0.01092619924022262</v>
+      </c>
+      <c r="Z6">
+        <v>0.3219243657252274</v>
+      </c>
+      <c r="AA6">
+        <v>0</v>
+      </c>
+      <c r="AB6">
+        <v>0.09964032807692805</v>
+      </c>
+      <c r="AC6">
+        <v>-0.09964032807692805</v>
+      </c>
+      <c r="AD6">
+        <v>164.5</v>
+      </c>
+      <c r="AE6">
+        <v>0</v>
+      </c>
+      <c r="AF6">
+        <v>164.5</v>
+      </c>
+      <c r="AG6">
+        <v>122.7</v>
+      </c>
+      <c r="AH6">
+        <v>0.5325348009064422</v>
+      </c>
+      <c r="AI6">
+        <v>0.4596255937412685</v>
+      </c>
+      <c r="AJ6">
+        <v>0.4593785099213777</v>
+      </c>
+      <c r="AK6">
+        <v>0.3881683011705157</v>
+      </c>
+      <c r="AL6">
+        <v>0</v>
+      </c>
+      <c r="AM6">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Bangladesh</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>NRB Bank PLC. (DSE:NRBBANK)</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Bank (Money Center)</t>
+        </is>
+      </c>
+      <c r="G7">
+        <v>0</v>
+      </c>
+      <c r="H7">
+        <v>0</v>
+      </c>
+      <c r="I7">
+        <v>0</v>
+      </c>
+      <c r="J7">
+        <v>0</v>
+      </c>
+      <c r="K7">
+        <v>6.89</v>
+      </c>
+      <c r="L7">
+        <v>0.2384083044982699</v>
+      </c>
+      <c r="M7">
+        <v>4.05</v>
+      </c>
+      <c r="N7">
+        <v>0.05752840909090908</v>
+      </c>
+      <c r="O7">
+        <v>0.5878084179970973</v>
+      </c>
+      <c r="P7">
+        <v>4.05</v>
+      </c>
+      <c r="Q7">
+        <v>0.05752840909090908</v>
+      </c>
+      <c r="R7">
+        <v>0.5878084179970973</v>
+      </c>
+      <c r="S7">
+        <v>0</v>
+      </c>
+      <c r="T7">
+        <v>0</v>
+      </c>
+      <c r="U7">
+        <v>92.8</v>
+      </c>
+      <c r="V7">
+        <v>1.318181818181818</v>
+      </c>
+      <c r="W7">
+        <v>0.1008784773060029</v>
+      </c>
+      <c r="X7">
+        <v>0.1171147446018022</v>
+      </c>
+      <c r="Y7">
+        <v>-0.01623626729579931</v>
+      </c>
+      <c r="Z7">
+        <v>0.4459876543209876</v>
+      </c>
+      <c r="AA7">
+        <v>0</v>
+      </c>
+      <c r="AB7">
+        <v>0.1001338108136201</v>
+      </c>
+      <c r="AC7">
+        <v>-0.1001338108136201</v>
+      </c>
+      <c r="AD7">
+        <v>55.5</v>
+      </c>
+      <c r="AE7">
+        <v>0</v>
+      </c>
+      <c r="AF7">
+        <v>55.5</v>
+      </c>
+      <c r="AG7">
+        <v>-37.3</v>
+      </c>
+      <c r="AH7">
+        <v>0.4408260524225576</v>
+      </c>
+      <c r="AI7">
+        <v>0.4285714285714285</v>
+      </c>
+      <c r="AJ7">
+        <v>-1.126888217522658</v>
+      </c>
+      <c r="AK7">
+        <v>-1.016348773841962</v>
+      </c>
+      <c r="AL7">
+        <v>0</v>
+      </c>
+      <c r="AM7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Bangladesh</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>National Bank Limited (DSE:NBL)</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Bank (Money Center)</t>
+        </is>
+      </c>
+      <c r="K8">
+        <v>-178.7</v>
+      </c>
+      <c r="M8">
+        <v>-0</v>
+      </c>
+      <c r="N8">
+        <v>-0</v>
+      </c>
+      <c r="O8">
+        <v>0</v>
+      </c>
+      <c r="P8">
+        <v>-0</v>
+      </c>
+      <c r="Q8">
+        <v>-0</v>
+      </c>
+      <c r="R8">
+        <v>0</v>
+      </c>
+      <c r="S8">
+        <v>0</v>
+      </c>
+      <c r="U8">
+        <v>22.3</v>
+      </c>
+      <c r="V8">
+        <v>0.169195751138088</v>
+      </c>
+      <c r="W8">
+        <v>-0.5510329941412272</v>
+      </c>
+      <c r="X8">
+        <v>0.149696818825398</v>
+      </c>
+      <c r="Y8">
+        <v>-0.7007298129666253</v>
+      </c>
+      <c r="Z8">
+        <v>0</v>
+      </c>
+      <c r="AA8">
+        <v>0</v>
+      </c>
+      <c r="AB8">
+        <v>0.1012762292953052</v>
+      </c>
+      <c r="AC8">
+        <v>-0.1012762292953052</v>
+      </c>
+      <c r="AD8">
+        <v>237.4</v>
+      </c>
+      <c r="AE8">
+        <v>0</v>
+      </c>
+      <c r="AF8">
+        <v>237.4</v>
+      </c>
+      <c r="AG8">
+        <v>215.1</v>
+      </c>
+      <c r="AH8">
+        <v>0.6430119176598049</v>
+      </c>
+      <c r="AI8">
+        <v>0.8257391304347826</v>
+      </c>
+      <c r="AJ8">
+        <v>0.6200634188526953</v>
+      </c>
+      <c r="AK8">
+        <v>0.8110859728506787</v>
+      </c>
+      <c r="AL8">
+        <v>0</v>
+      </c>
+      <c r="AM8">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Bangladesh</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Dhaka Bank PLC. (DSE:DHAKABANK)</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Bank (Money Center)</t>
+        </is>
+      </c>
+      <c r="D9">
+        <v>0.08900000000000001</v>
+      </c>
+      <c r="E9">
+        <v>0.0143</v>
+      </c>
+      <c r="G9">
+        <v>0</v>
+      </c>
+      <c r="H9">
+        <v>0</v>
+      </c>
+      <c r="I9">
+        <v>0</v>
+      </c>
+      <c r="J9">
+        <v>0</v>
+      </c>
+      <c r="K9">
+        <v>12.9</v>
+      </c>
+      <c r="L9">
+        <v>0.1253644314868805</v>
+      </c>
+      <c r="M9">
+        <v>8.41</v>
+      </c>
+      <c r="N9">
+        <v>0.09181222707423581</v>
+      </c>
+      <c r="O9">
+        <v>0.6519379844961241</v>
+      </c>
+      <c r="P9">
+        <v>8.41</v>
+      </c>
+      <c r="Q9">
+        <v>0.09181222707423581</v>
+      </c>
+      <c r="R9">
+        <v>0.6519379844961241</v>
+      </c>
+      <c r="S9">
+        <v>0</v>
+      </c>
+      <c r="T9">
+        <v>0</v>
+      </c>
+      <c r="U9">
+        <v>124.2</v>
+      </c>
+      <c r="V9">
+        <v>1.35589519650655</v>
+      </c>
+      <c r="W9">
+        <v>0.06240928882438317</v>
+      </c>
+      <c r="X9">
+        <v>0.1643793464370381</v>
+      </c>
+      <c r="Y9">
+        <v>-0.1019700576126549</v>
+      </c>
+      <c r="Z9">
+        <v>0.4070411392405063</v>
+      </c>
+      <c r="AA9">
+        <v>0</v>
+      </c>
+      <c r="AB9">
+        <v>0.1020168696282983</v>
+      </c>
+      <c r="AC9">
+        <v>-0.1020168696282983</v>
+      </c>
+      <c r="AD9">
+        <v>206.8</v>
+      </c>
+      <c r="AE9">
+        <v>0</v>
+      </c>
+      <c r="AF9">
+        <v>206.8</v>
+      </c>
+      <c r="AG9">
+        <v>82.60000000000001</v>
+      </c>
+      <c r="AH9">
+        <v>0.6930294906166221</v>
+      </c>
+      <c r="AI9">
+        <v>0.5172586293146574</v>
+      </c>
+      <c r="AJ9">
+        <v>0.4741676234213548</v>
+      </c>
+      <c r="AK9">
+        <v>0.2997097242380261</v>
+      </c>
+      <c r="AL9">
+        <v>0</v>
+      </c>
+      <c r="AM9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Bangladesh</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>IFIC Bank PLC (DSE:IFIC)</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Bank (Money Center)</t>
+        </is>
+      </c>
+      <c r="D10">
+        <v>0.106</v>
+      </c>
+      <c r="E10">
+        <v>-0.0416</v>
+      </c>
+      <c r="G10">
+        <v>0</v>
+      </c>
+      <c r="H10">
+        <v>0</v>
+      </c>
+      <c r="I10">
+        <v>0</v>
+      </c>
+      <c r="J10">
+        <v>0</v>
+      </c>
+      <c r="K10">
+        <v>20.2</v>
+      </c>
+      <c r="L10">
+        <v>0.1579358874120406</v>
+      </c>
+      <c r="M10">
+        <v>3.73</v>
+      </c>
+      <c r="N10">
+        <v>0.03226643598615917</v>
+      </c>
+      <c r="O10">
+        <v>0.1846534653465347</v>
+      </c>
+      <c r="P10">
+        <v>3.73</v>
+      </c>
+      <c r="Q10">
+        <v>0.03226643598615917</v>
+      </c>
+      <c r="R10">
+        <v>0.1846534653465347</v>
+      </c>
+      <c r="S10">
+        <v>0</v>
+      </c>
+      <c r="T10">
+        <v>0</v>
+      </c>
+      <c r="U10">
+        <v>199.5</v>
+      </c>
+      <c r="V10">
+        <v>1.725778546712803</v>
+      </c>
+      <c r="W10">
+        <v>0.0645367412140575</v>
+      </c>
+      <c r="X10">
+        <v>0.1302120647985056</v>
+      </c>
+      <c r="Y10">
+        <v>-0.06567532358444811</v>
+      </c>
+      <c r="Z10">
+        <v>0.3769525493663425</v>
+      </c>
+      <c r="AA10">
+        <v>0</v>
+      </c>
+      <c r="AB10">
+        <v>0.1021048458507525</v>
+      </c>
+      <c r="AC10">
+        <v>-0.1021048458507525</v>
+      </c>
+      <c r="AD10">
+        <v>138.2</v>
+      </c>
+      <c r="AE10">
+        <v>0</v>
+      </c>
+      <c r="AF10">
+        <v>138.2</v>
+      </c>
+      <c r="AG10">
+        <v>-61.30000000000001</v>
+      </c>
+      <c r="AH10">
+        <v>0.5445232466509062</v>
+      </c>
+      <c r="AI10">
+        <v>0.3102132435465769</v>
+      </c>
+      <c r="AJ10">
+        <v>-1.128913443830571</v>
+      </c>
+      <c r="AK10">
+        <v>-0.2491869918699187</v>
+      </c>
+      <c r="AL10">
+        <v>0</v>
+      </c>
+      <c r="AM10">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Bangladesh</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Standard Bank PLC. (DSE:STANDBANKL)</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Bank (Money Center)</t>
+        </is>
+      </c>
+      <c r="D11">
+        <v>0.0211</v>
+      </c>
+      <c r="E11">
+        <v>0.00402</v>
+      </c>
+      <c r="G11">
+        <v>0</v>
+      </c>
+      <c r="H11">
+        <v>0</v>
+      </c>
+      <c r="I11">
+        <v>0</v>
+      </c>
+      <c r="J11">
+        <v>0</v>
+      </c>
+      <c r="K11">
+        <v>13.4</v>
+      </c>
+      <c r="L11">
+        <v>0.2147435897435898</v>
+      </c>
+      <c r="M11">
+        <v>2.22</v>
+      </c>
+      <c r="N11">
+        <v>0.03971377459749553</v>
+      </c>
+      <c r="O11">
+        <v>0.1656716417910448</v>
+      </c>
+      <c r="P11">
+        <v>2.22</v>
+      </c>
+      <c r="Q11">
+        <v>0.03971377459749553</v>
+      </c>
+      <c r="R11">
+        <v>0.1656716417910448</v>
+      </c>
+      <c r="S11">
+        <v>0</v>
+      </c>
+      <c r="T11">
+        <v>0</v>
+      </c>
+      <c r="U11">
+        <v>193.4</v>
+      </c>
+      <c r="V11">
+        <v>3.459749552772809</v>
+      </c>
+      <c r="W11">
+        <v>0.08312655086848636</v>
+      </c>
+      <c r="X11">
+        <v>0.1707081738072264</v>
+      </c>
+      <c r="Y11">
+        <v>-0.08758162293874008</v>
+      </c>
+      <c r="Z11">
+        <v>0.3849475632325725</v>
+      </c>
+      <c r="AA11">
+        <v>0</v>
+      </c>
+      <c r="AB11">
+        <v>0.1022757538596558</v>
+      </c>
+      <c r="AC11">
+        <v>-0.1022757538596558</v>
+      </c>
+      <c r="AD11">
+        <v>137.2</v>
+      </c>
+      <c r="AE11">
+        <v>0</v>
+      </c>
+      <c r="AF11">
+        <v>137.2</v>
+      </c>
+      <c r="AG11">
+        <v>-56.20000000000002</v>
+      </c>
+      <c r="AH11">
+        <v>0.7105126877265665</v>
+      </c>
+      <c r="AI11">
+        <v>0.4677804295942721</v>
+      </c>
+      <c r="AJ11">
+        <v>187.3333333333219</v>
+      </c>
+      <c r="AK11">
+        <v>-0.5625625625625629</v>
+      </c>
+      <c r="AL11">
+        <v>0</v>
+      </c>
+      <c r="AM11">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>Bangladesh</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>The Premier Bank PLC. (DSE:PREMIERBAN)</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Bank (Money Center)</t>
+        </is>
+      </c>
+      <c r="D12">
+        <v>0.0595</v>
+      </c>
+      <c r="E12">
+        <v>0.0512</v>
+      </c>
+      <c r="G12">
+        <v>0</v>
+      </c>
+      <c r="H12">
+        <v>0</v>
+      </c>
+      <c r="I12">
+        <v>0</v>
+      </c>
+      <c r="J12">
+        <v>0</v>
+      </c>
+      <c r="K12">
+        <v>29.6</v>
+      </c>
+      <c r="L12">
+        <v>0.2426229508196721</v>
+      </c>
+      <c r="M12">
+        <v>14.5</v>
+      </c>
+      <c r="N12">
+        <v>0.1581243184296619</v>
+      </c>
+      <c r="O12">
+        <v>0.4898648648648649</v>
+      </c>
+      <c r="P12">
+        <v>14.5</v>
+      </c>
+      <c r="Q12">
+        <v>0.1581243184296619</v>
+      </c>
+      <c r="R12">
+        <v>0.4898648648648649</v>
+      </c>
+      <c r="S12">
+        <v>0</v>
+      </c>
+      <c r="T12">
+        <v>0</v>
+      </c>
+      <c r="U12">
+        <v>425.2</v>
+      </c>
+      <c r="V12">
+        <v>4.636859323882224</v>
+      </c>
+      <c r="W12">
+        <v>0.1234361968306922</v>
+      </c>
+      <c r="X12">
+        <v>0.1724387021299312</v>
+      </c>
+      <c r="Y12">
+        <v>-0.04900250529923895</v>
+      </c>
+      <c r="Z12">
+        <v>1.655359565807326</v>
+      </c>
+      <c r="AA12">
+        <v>0</v>
+      </c>
+      <c r="AB12">
+        <v>0.102341486742591</v>
+      </c>
+      <c r="AC12">
+        <v>-0.102341486742591</v>
+      </c>
+      <c r="AD12">
+        <v>230</v>
+      </c>
+      <c r="AE12">
+        <v>0</v>
+      </c>
+      <c r="AF12">
+        <v>230</v>
+      </c>
+      <c r="AG12">
+        <v>-195.2</v>
+      </c>
+      <c r="AH12">
+        <v>0.7149518184644078</v>
+      </c>
+      <c r="AI12">
+        <v>0.4949429739616957</v>
+      </c>
+      <c r="AJ12">
+        <v>1.885990338164251</v>
+      </c>
+      <c r="AK12">
+        <v>-4.941772151898734</v>
+      </c>
+      <c r="AL12">
+        <v>0</v>
+      </c>
+      <c r="AM12">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>Bangladesh</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>One Bank PLC. (DSE:ONEBANKPLC)</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Bank (Money Center)</t>
+        </is>
+      </c>
+      <c r="D13">
+        <v>0.07539999999999999</v>
+      </c>
+      <c r="E13">
+        <v>0.122</v>
+      </c>
+      <c r="G13">
+        <v>0</v>
+      </c>
+      <c r="H13">
+        <v>0</v>
+      </c>
+      <c r="I13">
+        <v>0</v>
+      </c>
+      <c r="J13">
+        <v>0</v>
+      </c>
+      <c r="K13">
+        <v>20.6</v>
+      </c>
+      <c r="L13">
+        <v>0.2417840375586855</v>
+      </c>
+      <c r="M13">
+        <v>2.89</v>
+      </c>
+      <c r="N13">
+        <v>0.03817701453104359</v>
+      </c>
+      <c r="O13">
+        <v>0.1402912621359223</v>
+      </c>
+      <c r="P13">
+        <v>2.89</v>
+      </c>
+      <c r="Q13">
+        <v>0.03817701453104359</v>
+      </c>
+      <c r="R13">
+        <v>0.1402912621359223</v>
+      </c>
+      <c r="S13">
+        <v>0</v>
+      </c>
+      <c r="T13">
+        <v>0</v>
+      </c>
+      <c r="U13">
+        <v>193.6</v>
+      </c>
+      <c r="V13">
+        <v>2.557463672391017</v>
+      </c>
+      <c r="W13">
+        <v>0.1185270425776755</v>
+      </c>
+      <c r="X13">
+        <v>0.1767012663918403</v>
+      </c>
+      <c r="Y13">
+        <v>-0.05817422381416484</v>
+      </c>
+      <c r="Z13">
+        <v>0.2789783889980354</v>
+      </c>
+      <c r="AA13">
+        <v>0</v>
+      </c>
+      <c r="AB13">
+        <v>0.1024951117936159</v>
+      </c>
+      <c r="AC13">
+        <v>-0.1024951117936159</v>
+      </c>
+      <c r="AD13">
+        <v>199.9</v>
+      </c>
+      <c r="AE13">
+        <v>0</v>
+      </c>
+      <c r="AF13">
+        <v>199.9</v>
+      </c>
+      <c r="AG13">
+        <v>6.300000000000011</v>
+      </c>
+      <c r="AH13">
+        <v>0.7253265602322205</v>
+      </c>
+      <c r="AI13">
+        <v>0.5346349291254346</v>
+      </c>
+      <c r="AJ13">
+        <v>0.07682926829268305</v>
+      </c>
+      <c r="AK13">
+        <v>0.03494176372712152</v>
+      </c>
+      <c r="AL13">
+        <v>0</v>
+      </c>
+      <c r="AM13">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>Bangladesh</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>AB Bank PLC. (DSE:ABBANK)</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Bank (Money Center)</t>
+        </is>
+      </c>
+      <c r="D14">
+        <v>0.06570000000000001</v>
+      </c>
+      <c r="G14">
+        <v>0</v>
+      </c>
+      <c r="H14">
+        <v>0</v>
+      </c>
+      <c r="I14">
+        <v>0</v>
+      </c>
+      <c r="J14">
+        <v>0</v>
+      </c>
+      <c r="K14">
+        <v>4.87</v>
+      </c>
+      <c r="L14">
+        <v>0.07367624810892588</v>
+      </c>
+      <c r="M14">
+        <v>4.51</v>
+      </c>
+      <c r="N14">
+        <v>0.07829861111111111</v>
+      </c>
+      <c r="O14">
+        <v>0.9260780287474332</v>
+      </c>
+      <c r="P14">
+        <v>4.51</v>
+      </c>
+      <c r="Q14">
+        <v>0.07829861111111111</v>
+      </c>
+      <c r="R14">
+        <v>0.9260780287474332</v>
+      </c>
+      <c r="S14">
+        <v>0</v>
+      </c>
+      <c r="T14">
+        <v>0</v>
+      </c>
+      <c r="U14">
+        <v>74.40000000000001</v>
+      </c>
+      <c r="V14">
+        <v>1.291666666666667</v>
+      </c>
+      <c r="W14">
+        <v>0.02072340425531915</v>
+      </c>
+      <c r="X14">
+        <v>0.1461505256406423</v>
+      </c>
+      <c r="Y14">
+        <v>-0.1254271213853232</v>
+      </c>
+      <c r="Z14">
+        <v>0.2334039548022598</v>
+      </c>
+      <c r="AA14">
+        <v>0</v>
+      </c>
+      <c r="AB14">
+        <v>0.1025992191496632</v>
+      </c>
+      <c r="AC14">
+        <v>-0.1025992191496632</v>
+      </c>
+      <c r="AD14">
+        <v>97.40000000000001</v>
+      </c>
+      <c r="AE14">
+        <v>0</v>
+      </c>
+      <c r="AF14">
+        <v>97.40000000000001</v>
+      </c>
+      <c r="AG14">
+        <v>23</v>
+      </c>
+      <c r="AH14">
+        <v>0.6283870967741936</v>
+      </c>
+      <c r="AI14">
+        <v>0.3102899012424339</v>
+      </c>
+      <c r="AJ14">
+        <v>0.2853598014888338</v>
+      </c>
+      <c r="AK14">
+        <v>0.09603340292275574</v>
+      </c>
+      <c r="AL14">
+        <v>0</v>
+      </c>
+      <c r="AM14">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>Bangladesh</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>NRBC Bank PLC. (DSE:NRBCBANK)</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Bank (Money Center)</t>
+        </is>
+      </c>
+      <c r="D15">
+        <v>0.173</v>
+      </c>
+      <c r="E15">
+        <v>0.132</v>
+      </c>
+      <c r="G15">
+        <v>0</v>
+      </c>
+      <c r="H15">
+        <v>0</v>
+      </c>
+      <c r="I15">
+        <v>0</v>
+      </c>
+      <c r="J15">
+        <v>0</v>
+      </c>
+      <c r="K15">
+        <v>14.8</v>
+      </c>
+      <c r="L15">
+        <v>0.2132564841498559</v>
+      </c>
+      <c r="M15">
+        <v>8.380000000000001</v>
+      </c>
+      <c r="N15">
+        <v>0.145993031358885</v>
+      </c>
+      <c r="O15">
+        <v>0.5662162162162162</v>
+      </c>
+      <c r="P15">
+        <v>8.380000000000001</v>
+      </c>
+      <c r="Q15">
+        <v>0.145993031358885</v>
+      </c>
+      <c r="R15">
+        <v>0.5662162162162162</v>
+      </c>
+      <c r="S15">
+        <v>0</v>
+      </c>
+      <c r="T15">
+        <v>0</v>
+      </c>
+      <c r="U15">
+        <v>74.5</v>
+      </c>
+      <c r="V15">
+        <v>1.297909407665505</v>
+      </c>
+      <c r="W15">
+        <v>0.1192586623690572</v>
+      </c>
+      <c r="X15">
+        <v>0.1815346824173665</v>
+      </c>
+      <c r="Y15">
+        <v>-0.06227602004830929</v>
+      </c>
+      <c r="Z15">
+        <v>0.2986230636833046</v>
+      </c>
+      <c r="AA15">
+        <v>0</v>
+      </c>
+      <c r="AB15">
+        <v>0.1026563173493111</v>
+      </c>
+      <c r="AC15">
+        <v>-0.1026563173493111</v>
+      </c>
+      <c r="AD15">
+        <v>160.2</v>
+      </c>
+      <c r="AE15">
+        <v>0</v>
+      </c>
+      <c r="AF15">
+        <v>160.2</v>
+      </c>
+      <c r="AG15">
+        <v>85.69999999999999</v>
+      </c>
+      <c r="AH15">
+        <v>0.7362132352941176</v>
+      </c>
+      <c r="AI15">
+        <v>0.5717344753747323</v>
+      </c>
+      <c r="AJ15">
+        <v>0.5988819007686932</v>
+      </c>
+      <c r="AK15">
+        <v>0.416626154594069</v>
+      </c>
+      <c r="AL15">
+        <v>0</v>
+      </c>
+      <c r="AM15">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>Bangladesh</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Shahjalal Islami Bank PLC. (DSE:SHAHJABANK)</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Bank (Money Center)</t>
+        </is>
+      </c>
+      <c r="D16">
+        <v>0.115</v>
+      </c>
+      <c r="E16">
+        <v>0.222</v>
+      </c>
+      <c r="G16">
+        <v>0</v>
+      </c>
+      <c r="H16">
+        <v>0</v>
+      </c>
+      <c r="I16">
+        <v>0</v>
+      </c>
+      <c r="J16">
+        <v>0</v>
+      </c>
+      <c r="K16">
+        <v>33.1</v>
+      </c>
+      <c r="L16">
+        <v>0.2677993527508091</v>
+      </c>
+      <c r="M16">
+        <v>17.3</v>
+      </c>
+      <c r="N16">
+        <v>0.1017048794826573</v>
+      </c>
+      <c r="O16">
+        <v>0.5226586102719033</v>
+      </c>
+      <c r="P16">
+        <v>17.3</v>
+      </c>
+      <c r="Q16">
+        <v>0.1017048794826573</v>
+      </c>
+      <c r="R16">
+        <v>0.5226586102719033</v>
+      </c>
+      <c r="S16">
+        <v>0</v>
+      </c>
+      <c r="T16">
+        <v>0</v>
+      </c>
+      <c r="U16">
+        <v>141.4</v>
+      </c>
+      <c r="V16">
+        <v>0.8312757201646092</v>
+      </c>
+      <c r="W16">
+        <v>0.151487414187643</v>
+      </c>
+      <c r="X16">
+        <v>0.1415107255381431</v>
+      </c>
+      <c r="Y16">
+        <v>0.009976688649499965</v>
+      </c>
+      <c r="Z16">
+        <v>0.2415949960906958</v>
+      </c>
+      <c r="AA16">
+        <v>0</v>
+      </c>
+      <c r="AB16">
+        <v>0.1032988554116992</v>
+      </c>
+      <c r="AC16">
+        <v>-0.1032988554116992</v>
+      </c>
+      <c r="AD16">
+        <v>263.1</v>
+      </c>
+      <c r="AE16">
+        <v>0</v>
+      </c>
+      <c r="AF16">
+        <v>263.1</v>
+      </c>
+      <c r="AG16">
+        <v>121.7</v>
+      </c>
+      <c r="AH16">
+        <v>0.6073407202216067</v>
+      </c>
+      <c r="AI16">
+        <v>0.5463039867109635</v>
+      </c>
+      <c r="AJ16">
+        <v>0.4170664838930775</v>
+      </c>
+      <c r="AK16">
+        <v>0.3577307466196355</v>
+      </c>
+      <c r="AL16">
+        <v>0</v>
+      </c>
+      <c r="AM16">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>Bangladesh</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>Bank Asia PLC. (DSE:BANKASIA)</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Bank (Money Center)</t>
+        </is>
+      </c>
+      <c r="D17">
+        <v>0.0347</v>
+      </c>
+      <c r="E17">
+        <v>-0.221</v>
+      </c>
+      <c r="G17">
+        <v>0</v>
+      </c>
+      <c r="H17">
+        <v>0</v>
+      </c>
+      <c r="I17">
+        <v>0</v>
+      </c>
+      <c r="J17">
+        <v>0</v>
+      </c>
+      <c r="K17">
+        <v>5.96</v>
+      </c>
+      <c r="L17">
+        <v>0.05102739726027397</v>
+      </c>
+      <c r="M17">
+        <v>17.5</v>
+      </c>
+      <c r="N17">
+        <v>0.1057401812688822</v>
+      </c>
+      <c r="O17">
+        <v>2.936241610738255</v>
+      </c>
+      <c r="P17">
+        <v>17.5</v>
+      </c>
+      <c r="Q17">
+        <v>0.1057401812688822</v>
+      </c>
+      <c r="R17">
+        <v>2.936241610738255</v>
+      </c>
+      <c r="S17">
+        <v>0</v>
+      </c>
+      <c r="T17">
+        <v>0</v>
+      </c>
+      <c r="U17">
+        <v>273.1</v>
+      </c>
+      <c r="V17">
+        <v>1.650151057401813</v>
+      </c>
+      <c r="W17">
+        <v>0.02142343637670741</v>
+      </c>
+      <c r="X17">
+        <v>0.1422328106219581</v>
+      </c>
+      <c r="Y17">
+        <v>-0.1208093742452507</v>
+      </c>
+      <c r="Z17">
+        <v>0.319387476073284</v>
+      </c>
+      <c r="AA17">
+        <v>0</v>
+      </c>
+      <c r="AB17">
+        <v>0.1033640644410495</v>
+      </c>
+      <c r="AC17">
+        <v>-0.1033640644410495</v>
+      </c>
+      <c r="AD17">
+        <v>259.7</v>
+      </c>
+      <c r="AE17">
+        <v>0</v>
+      </c>
+      <c r="AF17">
+        <v>259.7</v>
+      </c>
+      <c r="AG17">
+        <v>-13.40000000000003</v>
+      </c>
+      <c r="AH17">
+        <v>0.6107714016933208</v>
+      </c>
+      <c r="AI17">
+        <v>0.5011578541103821</v>
+      </c>
+      <c r="AJ17">
+        <v>-0.08809993425378065</v>
+      </c>
+      <c r="AK17">
+        <v>-0.05467156262749913</v>
+      </c>
+      <c r="AL17">
+        <v>0</v>
+      </c>
+      <c r="AM17">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>Bangladesh</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>Global Islami Bank PLC. (DSE:GIB)</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>Bank (Money Center)</t>
+        </is>
+      </c>
+      <c r="G18">
+        <v>0</v>
+      </c>
+      <c r="H18">
+        <v>0</v>
+      </c>
+      <c r="I18">
+        <v>0</v>
+      </c>
+      <c r="J18">
+        <v>0</v>
+      </c>
+      <c r="K18">
+        <v>13.1</v>
+      </c>
+      <c r="L18">
+        <v>0.2381818181818182</v>
+      </c>
+      <c r="M18">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="N18">
+        <v>0.1933962264150943</v>
+      </c>
+      <c r="O18">
+        <v>0.6259541984732824</v>
+      </c>
+      <c r="P18">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="Q18">
+        <v>0.1933962264150943</v>
+      </c>
+      <c r="R18">
+        <v>0.6259541984732824</v>
+      </c>
+      <c r="S18">
+        <v>0</v>
+      </c>
+      <c r="T18">
+        <v>0</v>
+      </c>
+      <c r="U18">
+        <v>98.3</v>
+      </c>
+      <c r="V18">
+        <v>2.318396226415094</v>
+      </c>
+      <c r="W18">
+        <v>0.1042163882259348</v>
+      </c>
+      <c r="X18">
+        <v>0.2281667139673647</v>
+      </c>
+      <c r="Y18">
+        <v>-0.12395032574143</v>
+      </c>
+      <c r="Z18">
+        <v>0.3144654088050314</v>
+      </c>
+      <c r="AA18">
+        <v>0</v>
+      </c>
+      <c r="AB18">
+        <v>0.1037367937836969</v>
+      </c>
+      <c r="AC18">
+        <v>-0.1037367937836969</v>
+      </c>
+      <c r="AD18">
+        <v>179.8</v>
+      </c>
+      <c r="AE18">
+        <v>0</v>
+      </c>
+      <c r="AF18">
+        <v>179.8</v>
+      </c>
+      <c r="AG18">
+        <v>81.50000000000001</v>
+      </c>
+      <c r="AH18">
+        <v>0.8091809180918091</v>
+      </c>
+      <c r="AI18">
+        <v>0.5977393617021277</v>
+      </c>
+      <c r="AJ18">
+        <v>0.6577885391444714</v>
+      </c>
+      <c r="AK18">
+        <v>0.4024691358024692</v>
+      </c>
+      <c r="AL18">
+        <v>0</v>
+      </c>
+      <c r="AM18">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>Bangladesh</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>Trust Bank PLC. (DSE:TRUSTBANK)</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>Bank (Money Center)</t>
+        </is>
+      </c>
+      <c r="D19">
+        <v>0.09630000000000001</v>
+      </c>
+      <c r="E19">
+        <v>0.114</v>
+      </c>
+      <c r="G19">
+        <v>0</v>
+      </c>
+      <c r="H19">
+        <v>0</v>
+      </c>
+      <c r="I19">
+        <v>0</v>
+      </c>
+      <c r="J19">
+        <v>0</v>
+      </c>
+      <c r="K19">
+        <v>36.1</v>
+      </c>
+      <c r="L19">
+        <v>0.3041280539174389</v>
+      </c>
+      <c r="M19">
+        <v>8.58</v>
+      </c>
+      <c r="N19">
+        <v>0.05050029429075927</v>
+      </c>
+      <c r="O19">
+        <v>0.2376731301939058</v>
+      </c>
+      <c r="P19">
+        <v>8.58</v>
+      </c>
+      <c r="Q19">
+        <v>0.05050029429075927</v>
+      </c>
+      <c r="R19">
+        <v>0.2376731301939058</v>
+      </c>
+      <c r="S19">
+        <v>0</v>
+      </c>
+      <c r="T19">
+        <v>0</v>
+      </c>
+      <c r="U19">
+        <v>202.7</v>
+      </c>
+      <c r="V19">
+        <v>1.193054738081224</v>
+      </c>
+      <c r="W19">
+        <v>0.183248730964467</v>
+      </c>
+      <c r="X19">
+        <v>0.1467949941788578</v>
+      </c>
+      <c r="Y19">
+        <v>0.0364537367856092</v>
+      </c>
+      <c r="Z19">
+        <v>0.6244082062072592</v>
+      </c>
+      <c r="AA19">
+        <v>0</v>
+      </c>
+      <c r="AB19">
+        <v>0.1037510953913832</v>
+      </c>
+      <c r="AC19">
+        <v>-0.1037510953913832</v>
+      </c>
+      <c r="AD19">
+        <v>290.7</v>
+      </c>
+      <c r="AE19">
+        <v>0</v>
+      </c>
+      <c r="AF19">
+        <v>290.7</v>
+      </c>
+      <c r="AG19">
+        <v>88</v>
+      </c>
+      <c r="AH19">
+        <v>0.631133304385584</v>
+      </c>
+      <c r="AI19">
+        <v>0.585262734044695</v>
+      </c>
+      <c r="AJ19">
+        <v>0.3412175261729353</v>
+      </c>
+      <c r="AK19">
+        <v>0.2993197278911565</v>
+      </c>
+      <c r="AL19">
+        <v>0</v>
+      </c>
+      <c r="AM19">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>Bangladesh</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>United Commercial Bank PLC (DSE:UCB)</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>Bank (Money Center)</t>
+        </is>
+      </c>
+      <c r="D20">
+        <v>0.121</v>
+      </c>
+      <c r="E20">
+        <v>0.0111</v>
+      </c>
+      <c r="G20">
+        <v>0</v>
+      </c>
+      <c r="H20">
+        <v>0</v>
+      </c>
+      <c r="I20">
+        <v>0</v>
+      </c>
+      <c r="J20">
+        <v>0</v>
+      </c>
+      <c r="K20">
+        <v>22.9</v>
+      </c>
+      <c r="L20">
+        <v>0.09178356713426854</v>
+      </c>
+      <c r="M20">
+        <v>7.15</v>
+      </c>
+      <c r="N20">
+        <v>0.06003358522250211</v>
+      </c>
+      <c r="O20">
+        <v>0.3122270742358079</v>
+      </c>
+      <c r="P20">
+        <v>7.15</v>
+      </c>
+      <c r="Q20">
+        <v>0.06003358522250211</v>
+      </c>
+      <c r="R20">
+        <v>0.3122270742358079</v>
+      </c>
+      <c r="S20">
+        <v>0</v>
+      </c>
+      <c r="T20">
+        <v>0</v>
+      </c>
+      <c r="U20">
+        <v>289.1</v>
+      </c>
+      <c r="V20">
+        <v>2.427371956339211</v>
+      </c>
+      <c r="W20">
+        <v>0.06155913978494623</v>
+      </c>
+      <c r="X20">
+        <v>0.2644266087720015</v>
+      </c>
+      <c r="Y20">
+        <v>-0.2028674689870552</v>
+      </c>
+      <c r="Z20">
+        <v>0.3521524347212421</v>
+      </c>
+      <c r="AA20">
+        <v>0</v>
+      </c>
+      <c r="AB20">
+        <v>0.1042369641283639</v>
+      </c>
+      <c r="AC20">
+        <v>-0.1042369641283639</v>
+      </c>
+      <c r="AD20">
+        <v>639.3</v>
+      </c>
+      <c r="AE20">
+        <v>0</v>
+      </c>
+      <c r="AF20">
+        <v>639.3</v>
+      </c>
+      <c r="AG20">
+        <v>350.1999999999999</v>
+      </c>
+      <c r="AH20">
+        <v>0.8429588607594937</v>
+      </c>
+      <c r="AI20">
+        <v>0.6434178743961353</v>
+      </c>
+      <c r="AJ20">
+        <v>0.7462177711485189</v>
+      </c>
+      <c r="AK20">
+        <v>0.4970901348474094</v>
+      </c>
+      <c r="AL20">
+        <v>0</v>
+      </c>
+      <c r="AM20">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>Bangladesh</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>City Bank PLC. (DSE:CITYBANK)</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>Bank (Money Center)</t>
+        </is>
+      </c>
+      <c r="D21">
+        <v>0.13</v>
+      </c>
+      <c r="E21">
+        <v>0.223</v>
+      </c>
+      <c r="F21">
+        <v>0.135</v>
+      </c>
+      <c r="G21">
+        <v>0</v>
+      </c>
+      <c r="H21">
+        <v>0</v>
+      </c>
+      <c r="I21">
+        <v>0</v>
+      </c>
+      <c r="J21">
+        <v>0</v>
+      </c>
+      <c r="K21">
+        <v>59.3</v>
+      </c>
+      <c r="L21">
+        <v>0.2368210862619808</v>
+      </c>
+      <c r="M21">
+        <v>18.8</v>
+      </c>
+      <c r="N21">
+        <v>0.0746031746031746</v>
+      </c>
+      <c r="O21">
+        <v>0.3170320404721754</v>
+      </c>
+      <c r="P21">
+        <v>18.8</v>
+      </c>
+      <c r="Q21">
+        <v>0.0746031746031746</v>
+      </c>
+      <c r="R21">
+        <v>0.3170320404721754</v>
+      </c>
+      <c r="S21">
+        <v>0</v>
+      </c>
+      <c r="T21">
+        <v>0</v>
+      </c>
+      <c r="U21">
+        <v>790.7</v>
+      </c>
+      <c r="V21">
+        <v>3.137698412698413</v>
+      </c>
+      <c r="W21">
+        <v>0.1815120906029997</v>
+      </c>
+      <c r="X21">
+        <v>0.1566913997443485</v>
+      </c>
+      <c r="Y21">
+        <v>0.02482069085865118</v>
+      </c>
+      <c r="Z21">
+        <v>0.3760324373028984</v>
+      </c>
+      <c r="AA21">
+        <v>0</v>
+      </c>
+      <c r="AB21">
+        <v>0.1044656456957774</v>
+      </c>
+      <c r="AC21">
+        <v>-0.1044656456957774</v>
+      </c>
+      <c r="AD21">
+        <v>508.7</v>
+      </c>
+      <c r="AE21">
+        <v>0</v>
+      </c>
+      <c r="AF21">
+        <v>508.7</v>
+      </c>
+      <c r="AG21">
+        <v>-282.0000000000001</v>
+      </c>
+      <c r="AH21">
+        <v>0.6687261732614697</v>
+      </c>
+      <c r="AI21">
+        <v>0.6019405987457106</v>
+      </c>
+      <c r="AJ21">
+        <v>9.399999999999984</v>
+      </c>
+      <c r="AK21">
+        <v>-5.183823529411773</v>
+      </c>
+      <c r="AL21">
+        <v>0</v>
+      </c>
+      <c r="AM21">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>Bangladesh</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>Social Islami Bank PLC. (DSE:SIBL)</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>Bank (Money Center)</t>
+        </is>
+      </c>
+      <c r="D22">
+        <v>0.0372</v>
+      </c>
+      <c r="E22">
+        <v>0.0243</v>
+      </c>
+      <c r="G22">
+        <v>0</v>
+      </c>
+      <c r="H22">
+        <v>0</v>
+      </c>
+      <c r="I22">
+        <v>0</v>
+      </c>
+      <c r="J22">
+        <v>0</v>
+      </c>
+      <c r="K22">
+        <v>14.8</v>
+      </c>
+      <c r="L22">
+        <v>0.1566137566137566</v>
+      </c>
+      <c r="M22">
+        <v>8.31</v>
+      </c>
+      <c r="N22">
+        <v>0.09916467780429596</v>
+      </c>
+      <c r="O22">
+        <v>0.5614864864864865</v>
+      </c>
+      <c r="P22">
+        <v>8.31</v>
+      </c>
+      <c r="Q22">
+        <v>0.09916467780429596</v>
+      </c>
+      <c r="R22">
+        <v>0.5614864864864865</v>
+      </c>
+      <c r="S22">
+        <v>0</v>
+      </c>
+      <c r="T22">
+        <v>0</v>
+      </c>
+      <c r="U22">
+        <v>112.6</v>
+      </c>
+      <c r="V22">
+        <v>1.343675417661098</v>
+      </c>
+      <c r="W22">
+        <v>0.07632800412583807</v>
+      </c>
+      <c r="X22">
+        <v>0.1860717089209164</v>
+      </c>
+      <c r="Y22">
+        <v>-0.1097437047950783</v>
+      </c>
+      <c r="Z22">
+        <v>0.375297855440826</v>
+      </c>
+      <c r="AA22">
+        <v>0</v>
+      </c>
+      <c r="AB22">
+        <v>0.1046233317318323</v>
+      </c>
+      <c r="AC22">
+        <v>-0.1046233317318323</v>
+      </c>
+      <c r="AD22">
+        <v>245.7</v>
+      </c>
+      <c r="AE22">
+        <v>0</v>
+      </c>
+      <c r="AF22">
+        <v>245.7</v>
+      </c>
+      <c r="AG22">
+        <v>133.1</v>
+      </c>
+      <c r="AH22">
+        <v>0.7456752655538694</v>
+      </c>
+      <c r="AI22">
+        <v>0.5711297071129707</v>
+      </c>
+      <c r="AJ22">
+        <v>0.6136468418626095</v>
+      </c>
+      <c r="AK22">
+        <v>0.419080604534005</v>
+      </c>
+      <c r="AL22">
+        <v>0</v>
+      </c>
+      <c r="AM22">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>Bangladesh</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>Union Bank PLC. (DSE:UNIONBANK)</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>Bank (Money Center)</t>
+        </is>
+      </c>
+      <c r="G23">
+        <v>0</v>
+      </c>
+      <c r="H23">
+        <v>0</v>
+      </c>
+      <c r="I23">
+        <v>0</v>
+      </c>
+      <c r="J23">
+        <v>0</v>
+      </c>
+      <c r="K23">
+        <v>3.24</v>
+      </c>
+      <c r="L23">
+        <v>0.05754884547069272</v>
+      </c>
+      <c r="M23">
+        <v>4.33</v>
+      </c>
+      <c r="N23">
+        <v>0.1043373493975904</v>
+      </c>
+      <c r="O23">
+        <v>1.33641975308642</v>
+      </c>
+      <c r="P23">
+        <v>4.33</v>
+      </c>
+      <c r="Q23">
+        <v>0.1043373493975904</v>
+      </c>
+      <c r="R23">
+        <v>1.33641975308642</v>
+      </c>
+      <c r="S23">
+        <v>0</v>
+      </c>
+      <c r="T23">
+        <v>0</v>
+      </c>
+      <c r="U23">
+        <v>54.4</v>
+      </c>
+      <c r="V23">
+        <v>1.310843373493976</v>
+      </c>
+      <c r="W23">
+        <v>0.02214627477785373</v>
+      </c>
+      <c r="X23">
+        <v>0.3256146852450564</v>
+      </c>
+      <c r="Y23">
+        <v>-0.3034684104672027</v>
+      </c>
+      <c r="Z23">
+        <v>0.3074822501365374</v>
+      </c>
+      <c r="AA23">
+        <v>0</v>
+      </c>
+      <c r="AB23">
+        <v>0.1047718205509113</v>
+      </c>
+      <c r="AC23">
+        <v>-0.1047718205509113</v>
+      </c>
+      <c r="AD23">
+        <v>301.7</v>
+      </c>
+      <c r="AE23">
+        <v>0</v>
+      </c>
+      <c r="AF23">
+        <v>301.7</v>
+      </c>
+      <c r="AG23">
+        <v>247.3</v>
+      </c>
+      <c r="AH23">
+        <v>0.879079254079254</v>
+      </c>
+      <c r="AI23">
+        <v>0.6935632183908046</v>
+      </c>
+      <c r="AJ23">
+        <v>0.8563019390581719</v>
+      </c>
+      <c r="AK23">
+        <v>0.6497635312664214</v>
+      </c>
+      <c r="AL23">
+        <v>0</v>
+      </c>
+      <c r="AM23">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>Bangladesh</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>Pubali Bank PLC. (DSE:PUBALIBANK)</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>Bank (Money Center)</t>
+        </is>
+      </c>
+      <c r="D24">
+        <v>0.174</v>
+      </c>
+      <c r="E24">
+        <v>0.208</v>
+      </c>
+      <c r="G24">
+        <v>0</v>
+      </c>
+      <c r="H24">
+        <v>0</v>
+      </c>
+      <c r="I24">
+        <v>0</v>
+      </c>
+      <c r="J24">
+        <v>0</v>
+      </c>
+      <c r="K24">
+        <v>80.09999999999999</v>
+      </c>
+      <c r="L24">
+        <v>0.2863782624240258</v>
+      </c>
+      <c r="M24">
+        <v>10.4</v>
+      </c>
+      <c r="N24">
+        <v>0.03673613564111621</v>
+      </c>
+      <c r="O24">
+        <v>0.1298377028714107</v>
+      </c>
+      <c r="P24">
+        <v>10.4</v>
+      </c>
+      <c r="Q24">
+        <v>0.03673613564111621</v>
+      </c>
+      <c r="R24">
+        <v>0.1298377028714107</v>
+      </c>
+      <c r="S24">
+        <v>0</v>
+      </c>
+      <c r="T24">
+        <v>0</v>
+      </c>
+      <c r="U24">
+        <v>146.9</v>
+      </c>
+      <c r="V24">
+        <v>0.5188979159307665</v>
+      </c>
+      <c r="W24">
+        <v>0.1871932694554803</v>
+      </c>
+      <c r="X24">
+        <v>0.1621364910313766</v>
+      </c>
+      <c r="Y24">
+        <v>0.02505677842410364</v>
+      </c>
+      <c r="Z24">
+        <v>0.2914148780996041</v>
+      </c>
+      <c r="AA24">
+        <v>0</v>
+      </c>
+      <c r="AB24">
+        <v>0.1047999821269796</v>
+      </c>
+      <c r="AC24">
+        <v>-0.1047999821269796</v>
+      </c>
+      <c r="AD24">
+        <v>619.4</v>
+      </c>
+      <c r="AE24">
+        <v>0</v>
+      </c>
+      <c r="AF24">
+        <v>619.4</v>
+      </c>
+      <c r="AG24">
+        <v>472.5</v>
+      </c>
+      <c r="AH24">
+        <v>0.6863157894736842</v>
+      </c>
+      <c r="AI24">
+        <v>0.5697727899917211</v>
+      </c>
+      <c r="AJ24">
+        <v>0.6253308628904182</v>
+      </c>
+      <c r="AK24">
+        <v>0.5025526483726867</v>
+      </c>
+      <c r="AL24">
+        <v>0</v>
+      </c>
+      <c r="AM24">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>Bangladesh</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>Eastern Bank PLC. (DSE:EBL)</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>Bank (Money Center)</t>
+        </is>
+      </c>
+      <c r="D25">
+        <v>0.139</v>
+      </c>
+      <c r="E25">
+        <v>0.137</v>
+      </c>
+      <c r="G25">
+        <v>0</v>
+      </c>
+      <c r="H25">
+        <v>0</v>
+      </c>
+      <c r="I25">
+        <v>0</v>
+      </c>
+      <c r="J25">
+        <v>0</v>
+      </c>
+      <c r="K25">
+        <v>54.2</v>
+      </c>
+      <c r="L25">
+        <v>0.2788065843621399</v>
+      </c>
+      <c r="M25">
+        <v>12.6</v>
+      </c>
+      <c r="N25">
+        <v>0.04498393430917529</v>
+      </c>
+      <c r="O25">
+        <v>0.2324723247232472</v>
+      </c>
+      <c r="P25">
+        <v>12.6</v>
+      </c>
+      <c r="Q25">
+        <v>0.04498393430917529</v>
+      </c>
+      <c r="R25">
+        <v>0.2324723247232472</v>
+      </c>
+      <c r="S25">
+        <v>0</v>
+      </c>
+      <c r="T25">
+        <v>0</v>
+      </c>
+      <c r="U25">
+        <v>256.4</v>
+      </c>
+      <c r="V25">
+        <v>0.9153873616565511</v>
+      </c>
+      <c r="W25">
+        <v>0.15494568324757</v>
+      </c>
+      <c r="X25">
+        <v>0.1634186028531574</v>
+      </c>
+      <c r="Y25">
+        <v>-0.008472919605587326</v>
+      </c>
+      <c r="Z25">
+        <v>0.2265734265734266</v>
+      </c>
+      <c r="AA25">
+        <v>0</v>
+      </c>
+      <c r="AB25">
+        <v>0.1048736052027224</v>
+      </c>
+      <c r="AC25">
+        <v>-0.1048736052027224</v>
+      </c>
+      <c r="AD25">
+        <v>624</v>
+      </c>
+      <c r="AE25">
+        <v>0</v>
+      </c>
+      <c r="AF25">
+        <v>624</v>
+      </c>
+      <c r="AG25">
+        <v>367.6</v>
+      </c>
+      <c r="AH25">
+        <v>0.6901891383696493</v>
+      </c>
+      <c r="AI25">
+        <v>0.6319627304030788</v>
+      </c>
+      <c r="AJ25">
+        <v>0.5675467037208585</v>
+      </c>
+      <c r="AK25">
+        <v>0.5028727770177839</v>
+      </c>
+      <c r="AL25">
+        <v>0</v>
+      </c>
+      <c r="AM25">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>Bangladesh</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>Export Import Bank of Bangladesh PLC. (DSE:EXIMBANK)</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>Bank (Money Center)</t>
+        </is>
+      </c>
+      <c r="D26">
+        <v>-0.08789999999999999</v>
+      </c>
+      <c r="G26">
+        <v>0</v>
+      </c>
+      <c r="H26">
+        <v>0</v>
+      </c>
+      <c r="I26">
+        <v>0</v>
+      </c>
+      <c r="J26">
+        <v>0</v>
+      </c>
+      <c r="K26">
+        <v>-24.4</v>
+      </c>
+      <c r="L26">
+        <v>-0.4303350970017636</v>
+      </c>
+      <c r="M26">
+        <v>12.1</v>
+      </c>
+      <c r="N26">
+        <v>0.1390804597701149</v>
+      </c>
+      <c r="O26">
+        <v>-0.4959016393442623</v>
+      </c>
+      <c r="P26">
+        <v>12.1</v>
+      </c>
+      <c r="Q26">
+        <v>0.1390804597701149</v>
+      </c>
+      <c r="R26">
+        <v>-0.4959016393442623</v>
+      </c>
+      <c r="S26">
+        <v>0</v>
+      </c>
+      <c r="T26">
+        <v>0</v>
+      </c>
+      <c r="U26">
+        <v>126.9</v>
+      </c>
+      <c r="V26">
+        <v>1.458620689655173</v>
+      </c>
+      <c r="W26">
+        <v>-0.08265582655826557</v>
+      </c>
+      <c r="X26">
+        <v>0.3660360404203288</v>
+      </c>
+      <c r="Y26">
+        <v>-0.4486918669785944</v>
+      </c>
+      <c r="Z26">
+        <v>0.08958761257702641</v>
+      </c>
+      <c r="AA26">
+        <v>0</v>
+      </c>
+      <c r="AB26">
+        <v>0.1050079974178762</v>
+      </c>
+      <c r="AC26">
+        <v>-0.1050079974178762</v>
+      </c>
+      <c r="AD26">
+        <v>741.8</v>
+      </c>
+      <c r="AE26">
+        <v>0</v>
+      </c>
+      <c r="AF26">
+        <v>741.8</v>
+      </c>
+      <c r="AG26">
+        <v>614.9</v>
+      </c>
+      <c r="AH26">
+        <v>0.8950289575289575</v>
+      </c>
+      <c r="AI26">
+        <v>0.7612889983579638</v>
+      </c>
+      <c r="AJ26">
+        <v>0.8760507194757088</v>
+      </c>
+      <c r="AK26">
+        <v>0.7255457227138643</v>
+      </c>
+      <c r="AL26">
+        <v>0</v>
+      </c>
+      <c r="AM26">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>Bangladesh</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>Islami Bank Bangladesh PLC. (DSE:ISLAMIBANK)</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>Bank (Money Center)</t>
+        </is>
+      </c>
+      <c r="D27">
+        <v>0.114</v>
+      </c>
+      <c r="E27">
+        <v>-0.06179999999999999</v>
+      </c>
+      <c r="G27">
+        <v>0</v>
+      </c>
+      <c r="H27">
+        <v>0</v>
+      </c>
+      <c r="I27">
+        <v>0</v>
+      </c>
+      <c r="J27">
+        <v>0</v>
+      </c>
+      <c r="K27">
+        <v>38.9</v>
+      </c>
+      <c r="L27">
+        <v>0.0761998041136141</v>
+      </c>
+      <c r="M27">
+        <v>13.4</v>
+      </c>
+      <c r="N27">
+        <v>0.02059320731519901</v>
+      </c>
+      <c r="O27">
+        <v>0.3444730077120823</v>
+      </c>
+      <c r="P27">
+        <v>13.4</v>
+      </c>
+      <c r="Q27">
+        <v>0.02059320731519901</v>
+      </c>
+      <c r="R27">
+        <v>0.3444730077120823</v>
+      </c>
+      <c r="S27">
+        <v>0</v>
+      </c>
+      <c r="T27">
+        <v>0</v>
+      </c>
+      <c r="U27">
+        <v>1025.6</v>
+      </c>
+      <c r="V27">
+        <v>1.576148762870754</v>
+      </c>
+      <c r="W27">
+        <v>0.06022604118284564</v>
+      </c>
+      <c r="X27">
+        <v>0.2097498195188819</v>
+      </c>
+      <c r="Y27">
+        <v>-0.1495237783360363</v>
+      </c>
+      <c r="Z27">
+        <v>0.5395265271612768</v>
+      </c>
+      <c r="AA27">
+        <v>0</v>
+      </c>
+      <c r="AB27">
+        <v>0.1053154049427414</v>
+      </c>
+      <c r="AC27">
+        <v>-0.1053154049427414</v>
+      </c>
+      <c r="AD27">
+        <v>2386.8</v>
+      </c>
+      <c r="AE27">
+        <v>0</v>
+      </c>
+      <c r="AF27">
+        <v>2386.8</v>
+      </c>
+      <c r="AG27">
+        <v>1361.2</v>
+      </c>
+      <c r="AH27">
+        <v>0.7857777777777778</v>
+      </c>
+      <c r="AI27">
+        <v>0.7964495461825948</v>
+      </c>
+      <c r="AJ27">
+        <v>0.6765743824245738</v>
+      </c>
+      <c r="AK27">
+        <v>0.6905438311688312</v>
+      </c>
+      <c r="AL27">
+        <v>0</v>
+      </c>
+      <c r="AM27">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>Bangladesh</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>National Credit and Commerce Bank PLC. (DSE:NCCBANK)</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>Bank (Money Center)</t>
+        </is>
+      </c>
+      <c r="D28">
+        <v>0.0594</v>
+      </c>
+      <c r="E28">
+        <v>0.026</v>
+      </c>
+      <c r="G28">
+        <v>0</v>
+      </c>
+      <c r="H28">
+        <v>0</v>
+      </c>
+      <c r="I28">
+        <v>0</v>
+      </c>
+      <c r="J28">
+        <v>0</v>
+      </c>
+      <c r="K28">
+        <v>20.9</v>
+      </c>
+      <c r="L28">
+        <v>0.2106854838709677</v>
+      </c>
+      <c r="M28">
+        <v>11.1</v>
+      </c>
+      <c r="N28">
+        <v>0.1108891108891109</v>
+      </c>
+      <c r="O28">
+        <v>0.5311004784688995</v>
+      </c>
+      <c r="P28">
+        <v>11.1</v>
+      </c>
+      <c r="Q28">
+        <v>0.1108891108891109</v>
+      </c>
+      <c r="R28">
+        <v>0.5311004784688995</v>
+      </c>
+      <c r="S28">
+        <v>0</v>
+      </c>
+      <c r="T28">
+        <v>0</v>
+      </c>
+      <c r="U28">
+        <v>69.59999999999999</v>
+      </c>
+      <c r="V28">
+        <v>0.6953046953046953</v>
+      </c>
+      <c r="W28">
+        <v>0.09338695263628238</v>
+      </c>
+      <c r="X28">
+        <v>0.1741519785680992</v>
+      </c>
+      <c r="Y28">
+        <v>-0.08076502593181678</v>
+      </c>
+      <c r="Z28">
+        <v>0.2253521126760563</v>
+      </c>
+      <c r="AA28">
+        <v>0</v>
+      </c>
+      <c r="AB28">
+        <v>0.1054253093754025</v>
+      </c>
+      <c r="AC28">
+        <v>-0.1054253093754025</v>
+      </c>
+      <c r="AD28">
+        <v>256.4</v>
+      </c>
+      <c r="AE28">
+        <v>0</v>
+      </c>
+      <c r="AF28">
+        <v>256.4</v>
+      </c>
+      <c r="AG28">
+        <v>186.8</v>
+      </c>
+      <c r="AH28">
+        <v>0.7192145862552594</v>
+      </c>
+      <c r="AI28">
+        <v>0.5463456211378649</v>
+      </c>
+      <c r="AJ28">
+        <v>0.6510979435343325</v>
+      </c>
+      <c r="AK28">
+        <v>0.4673505128846634</v>
+      </c>
+      <c r="AL28">
+        <v>0</v>
+      </c>
+      <c r="AM28">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>Bangladesh</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>Southeast Bank PLC (DSE:SOUTHEASTB)</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>Bank (Money Center)</t>
+        </is>
+      </c>
+      <c r="D29">
+        <v>-0.0182</v>
+      </c>
+      <c r="E29">
+        <v>-0.266</v>
+      </c>
+      <c r="G29">
+        <v>0</v>
+      </c>
+      <c r="H29">
+        <v>0</v>
+      </c>
+      <c r="I29">
+        <v>0</v>
+      </c>
+      <c r="J29">
+        <v>0</v>
+      </c>
+      <c r="K29">
+        <v>5.82</v>
+      </c>
+      <c r="L29">
+        <v>0.06871310507674144</v>
+      </c>
+      <c r="M29">
+        <v>6.44</v>
+      </c>
+      <c r="N29">
+        <v>0.06407960199004975</v>
+      </c>
+      <c r="O29">
+        <v>1.106529209621993</v>
+      </c>
+      <c r="P29">
+        <v>6.44</v>
+      </c>
+      <c r="Q29">
+        <v>0.06407960199004975</v>
+      </c>
+      <c r="R29">
+        <v>1.106529209621993</v>
+      </c>
+      <c r="S29">
+        <v>0</v>
+      </c>
+      <c r="T29">
+        <v>0</v>
+      </c>
+      <c r="U29">
+        <v>357.5</v>
+      </c>
+      <c r="V29">
+        <v>3.557213930348259</v>
+      </c>
+      <c r="W29">
+        <v>0.01937416777629827</v>
+      </c>
+      <c r="X29">
+        <v>0.1762246514826465</v>
+      </c>
+      <c r="Y29">
+        <v>-0.1568504837063482</v>
+      </c>
+      <c r="Z29">
+        <v>0.2174582798459564</v>
+      </c>
+      <c r="AA29">
+        <v>0</v>
+      </c>
+      <c r="AB29">
+        <v>0.1055201494229046</v>
+      </c>
+      <c r="AC29">
+        <v>-0.1055201494229046</v>
+      </c>
+      <c r="AD29">
+        <v>263.9</v>
+      </c>
+      <c r="AE29">
+        <v>0</v>
+      </c>
+      <c r="AF29">
+        <v>263.9</v>
+      </c>
+      <c r="AG29">
+        <v>-93.60000000000002</v>
+      </c>
+      <c r="AH29">
+        <v>0.7242041712403952</v>
+      </c>
+      <c r="AI29">
+        <v>0.4917085895286006</v>
+      </c>
+      <c r="AJ29">
+        <v>-13.5652173913044</v>
+      </c>
+      <c r="AK29">
+        <v>-0.5223214285714287</v>
+      </c>
+      <c r="AL29">
+        <v>0</v>
+      </c>
+      <c r="AM29">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>Bangladesh</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>First Security Islami Bank PLC (DSE:FIRSTSBANK)</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>Bank (Money Center)</t>
+        </is>
+      </c>
+      <c r="D30">
+        <v>0.09699999999999999</v>
+      </c>
+      <c r="E30">
+        <v>0.00297</v>
+      </c>
+      <c r="G30">
+        <v>0</v>
+      </c>
+      <c r="H30">
+        <v>0</v>
+      </c>
+      <c r="I30">
+        <v>0</v>
+      </c>
+      <c r="J30">
+        <v>0</v>
+      </c>
+      <c r="K30">
+        <v>19.1</v>
+      </c>
+      <c r="L30">
+        <v>0.1437170805116629</v>
+      </c>
+      <c r="M30">
+        <v>9.35</v>
+      </c>
+      <c r="N30">
+        <v>0.1815533980582524</v>
+      </c>
+      <c r="O30">
+        <v>0.4895287958115183</v>
+      </c>
+      <c r="P30">
+        <v>9.35</v>
+      </c>
+      <c r="Q30">
+        <v>0.1815533980582524</v>
+      </c>
+      <c r="R30">
+        <v>0.4895287958115183</v>
+      </c>
+      <c r="S30">
+        <v>0</v>
+      </c>
+      <c r="T30">
+        <v>0</v>
+      </c>
+      <c r="U30">
+        <v>14.2</v>
+      </c>
+      <c r="V30">
+        <v>0.2757281553398058</v>
+      </c>
+      <c r="W30">
+        <v>0.08822170900692841</v>
+      </c>
+      <c r="X30">
+        <v>0.8278787054897638</v>
+      </c>
+      <c r="Y30">
+        <v>-0.7396569964828354</v>
+      </c>
+      <c r="Z30">
+        <v>0.1081807081807082</v>
+      </c>
+      <c r="AA30">
+        <v>0</v>
+      </c>
+      <c r="AB30">
+        <v>0.1059423737692232</v>
+      </c>
+      <c r="AC30">
+        <v>-0.1059423737692232</v>
+      </c>
+      <c r="AD30">
+        <v>1178.5</v>
+      </c>
+      <c r="AE30">
+        <v>0</v>
+      </c>
+      <c r="AF30">
+        <v>1178.5</v>
+      </c>
+      <c r="AG30">
+        <v>1164.3</v>
+      </c>
+      <c r="AH30">
+        <v>0.958130081300813</v>
+      </c>
+      <c r="AI30">
+        <v>0.847841726618705</v>
+      </c>
+      <c r="AJ30">
+        <v>0.9576410593847672</v>
+      </c>
+      <c r="AK30">
+        <v>0.8462712603576101</v>
+      </c>
+      <c r="AL30">
+        <v>0</v>
+      </c>
+      <c r="AM30">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>Bangladesh</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>Dutch-Bangla Bank PLC. (DSE:DUTCHBANGL)</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>Bank (Money Center)</t>
+        </is>
+      </c>
+      <c r="D31">
+        <v>0.0736</v>
+      </c>
+      <c r="E31">
+        <v>0.04969999999999999</v>
+      </c>
+      <c r="G31">
+        <v>0</v>
+      </c>
+      <c r="H31">
+        <v>0</v>
+      </c>
+      <c r="I31">
+        <v>0</v>
+      </c>
+      <c r="J31">
+        <v>0</v>
+      </c>
+      <c r="K31">
+        <v>52.2</v>
+      </c>
+      <c r="L31">
+        <v>0.1832865168539326</v>
+      </c>
+      <c r="M31">
+        <v>10.7</v>
+      </c>
+      <c r="N31">
+        <v>0.03044096728307254</v>
+      </c>
+      <c r="O31">
+        <v>0.2049808429118774</v>
+      </c>
+      <c r="P31">
+        <v>10.7</v>
+      </c>
+      <c r="Q31">
+        <v>0.03044096728307254</v>
+      </c>
+      <c r="R31">
+        <v>0.2049808429118774</v>
+      </c>
+      <c r="S31">
+        <v>0</v>
+      </c>
+      <c r="T31">
+        <v>0</v>
+      </c>
+      <c r="U31">
+        <v>367.7</v>
+      </c>
+      <c r="V31">
+        <v>1.046088193456614</v>
+      </c>
+      <c r="W31">
+        <v>0.1293039385682438</v>
+      </c>
+      <c r="X31">
+        <v>0.1185418816833869</v>
+      </c>
+      <c r="Y31">
+        <v>0.01076205688485687</v>
+      </c>
+      <c r="Z31">
+        <v>0.878199198273204</v>
+      </c>
+      <c r="AA31">
+        <v>0</v>
+      </c>
+      <c r="AB31">
+        <v>0.1061160579035548</v>
+      </c>
+      <c r="AC31">
+        <v>-0.1061160579035548</v>
+      </c>
+      <c r="AD31">
+        <v>292.7</v>
+      </c>
+      <c r="AE31">
+        <v>0</v>
+      </c>
+      <c r="AF31">
+        <v>292.7</v>
+      </c>
+      <c r="AG31">
+        <v>-75</v>
+      </c>
+      <c r="AH31">
+        <v>0.4543619993790748</v>
+      </c>
+      <c r="AI31">
+        <v>0.416180861652211</v>
+      </c>
+      <c r="AJ31">
+        <v>-0.27124773960217</v>
+      </c>
+      <c r="AK31">
+        <v>-0.2234803337306317</v>
+      </c>
+      <c r="AL31">
+        <v>0</v>
+      </c>
+      <c r="AM31">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>Bangladesh</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>Prime Bank PLC. (DSE:PRIMEBANK)</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>Bank (Money Center)</t>
+        </is>
+      </c>
+      <c r="D32">
+        <v>0.0987</v>
+      </c>
+      <c r="E32">
+        <v>0.204</v>
+      </c>
+      <c r="G32">
+        <v>0</v>
+      </c>
+      <c r="H32">
+        <v>0</v>
+      </c>
+      <c r="I32">
+        <v>0</v>
+      </c>
+      <c r="J32">
+        <v>0</v>
+      </c>
+      <c r="K32">
+        <v>52.6</v>
+      </c>
+      <c r="L32">
+        <v>0.3166767007826611</v>
+      </c>
+      <c r="M32">
+        <v>16.5</v>
+      </c>
+      <c r="N32">
+        <v>0.07455942159963849</v>
+      </c>
+      <c r="O32">
+        <v>0.3136882129277567</v>
+      </c>
+      <c r="P32">
+        <v>16.5</v>
+      </c>
+      <c r="Q32">
+        <v>0.07455942159963849</v>
+      </c>
+      <c r="R32">
+        <v>0.3136882129277567</v>
+      </c>
+      <c r="S32">
+        <v>0</v>
+      </c>
+      <c r="T32">
+        <v>0</v>
+      </c>
+      <c r="U32">
+        <v>149.3</v>
+      </c>
+      <c r="V32">
+        <v>0.6746497966561229</v>
+      </c>
+      <c r="W32">
+        <v>0.1718392682130023</v>
+      </c>
+      <c r="X32">
+        <v>0.2085666674129856</v>
+      </c>
+      <c r="Y32">
+        <v>-0.03672739919998333</v>
+      </c>
+      <c r="Z32">
+        <v>0.1662496246621959</v>
+      </c>
+      <c r="AA32">
+        <v>0</v>
+      </c>
+      <c r="AB32">
+        <v>0.1066581787523458</v>
+      </c>
+      <c r="AC32">
+        <v>-0.1066581787523458</v>
+      </c>
+      <c r="AD32">
+        <v>803.6</v>
+      </c>
+      <c r="AE32">
+        <v>0</v>
+      </c>
+      <c r="AF32">
+        <v>803.6</v>
+      </c>
+      <c r="AG32">
+        <v>654.3</v>
+      </c>
+      <c r="AH32">
+        <v>0.784076495267831</v>
+      </c>
+      <c r="AI32">
+        <v>0.7175640682203768</v>
+      </c>
+      <c r="AJ32">
+        <v>0.7472590223846506</v>
+      </c>
+      <c r="AK32">
+        <v>0.6741191015866475</v>
+      </c>
+      <c r="AL32">
+        <v>0</v>
+      </c>
+      <c r="AM32">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>Bangladesh</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>Al-Arafah Islami Bank PLC. (DSE:ALARABANK)</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>Bank (Money Center)</t>
+        </is>
+      </c>
+      <c r="D33">
+        <v>0.0682</v>
+      </c>
+      <c r="E33">
+        <v>-0.0227</v>
+      </c>
+      <c r="G33">
+        <v>0</v>
+      </c>
+      <c r="H33">
+        <v>0</v>
+      </c>
+      <c r="I33">
+        <v>0</v>
+      </c>
+      <c r="J33">
+        <v>0</v>
+      </c>
+      <c r="K33">
+        <v>14.4</v>
+      </c>
+      <c r="L33">
+        <v>0.1156626506024096</v>
+      </c>
+      <c r="M33">
+        <v>9.48</v>
+      </c>
+      <c r="N33">
+        <v>0.05056</v>
+      </c>
+      <c r="O33">
+        <v>0.6583333333333333</v>
+      </c>
+      <c r="P33">
+        <v>9.48</v>
+      </c>
+      <c r="Q33">
+        <v>0.05056</v>
+      </c>
+      <c r="R33">
+        <v>0.6583333333333333</v>
+      </c>
+      <c r="S33">
+        <v>0</v>
+      </c>
+      <c r="T33">
+        <v>0</v>
+      </c>
+      <c r="U33">
+        <v>565.7</v>
+      </c>
+      <c r="V33">
+        <v>3.017066666666667</v>
+      </c>
+      <c r="W33">
+        <v>0.06542480690595184</v>
+      </c>
+      <c r="X33">
+        <v>0.2161046807995941</v>
+      </c>
+      <c r="Y33">
+        <v>-0.1506798738936422</v>
+      </c>
+      <c r="Z33">
+        <v>0.4712339137017412</v>
+      </c>
+      <c r="AA33">
+        <v>0</v>
+      </c>
+      <c r="AB33">
+        <v>0.1068558389277018</v>
+      </c>
+      <c r="AC33">
+        <v>-0.1068558389277018</v>
+      </c>
+      <c r="AD33">
+        <v>724.8</v>
+      </c>
+      <c r="AE33">
+        <v>0</v>
+      </c>
+      <c r="AF33">
+        <v>724.8</v>
+      </c>
+      <c r="AG33">
+        <v>159.0999999999999</v>
+      </c>
+      <c r="AH33">
+        <v>0.7944755014797764</v>
+      </c>
+      <c r="AI33">
+        <v>0.7690185676392572</v>
+      </c>
+      <c r="AJ33">
+        <v>0.4590305828043853</v>
+      </c>
+      <c r="AK33">
+        <v>0.4222399150743099</v>
+      </c>
+      <c r="AL33">
+        <v>0</v>
+      </c>
+      <c r="AM33">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>Bangladesh</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>Mutual Trust Bank PLC. (DSE:MTB)</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>Bank (Money Center)</t>
+        </is>
+      </c>
+      <c r="D34">
+        <v>0.121</v>
+      </c>
+      <c r="E34">
+        <v>0.105</v>
+      </c>
+      <c r="G34">
+        <v>0</v>
+      </c>
+      <c r="H34">
+        <v>0</v>
+      </c>
+      <c r="I34">
+        <v>0</v>
+      </c>
+      <c r="J34">
+        <v>0</v>
+      </c>
+      <c r="K34">
+        <v>25</v>
+      </c>
+      <c r="L34">
+        <v>0.205761316872428</v>
+      </c>
+      <c r="M34">
+        <v>8.210000000000001</v>
+      </c>
+      <c r="N34">
+        <v>0.08128712871287129</v>
+      </c>
+      <c r="O34">
+        <v>0.3284</v>
+      </c>
+      <c r="P34">
+        <v>8.210000000000001</v>
+      </c>
+      <c r="Q34">
+        <v>0.08128712871287129</v>
+      </c>
+      <c r="R34">
+        <v>0.3284</v>
+      </c>
+      <c r="S34">
+        <v>0</v>
+      </c>
+      <c r="T34">
+        <v>0</v>
+      </c>
+      <c r="U34">
+        <v>78.90000000000001</v>
+      </c>
+      <c r="V34">
+        <v>0.7811881188118812</v>
+      </c>
+      <c r="W34">
+        <v>0.117813383600377</v>
+      </c>
+      <c r="X34">
+        <v>0.2432644380076059</v>
+      </c>
+      <c r="Y34">
+        <v>-0.1254510544072289</v>
+      </c>
+      <c r="Z34">
+        <v>0.2109375</v>
+      </c>
+      <c r="AA34">
+        <v>0</v>
+      </c>
+      <c r="AB34">
+        <v>0.1074334821165441</v>
+      </c>
+      <c r="AC34">
+        <v>-0.1074334821165441</v>
+      </c>
+      <c r="AD34">
+        <v>475.7</v>
+      </c>
+      <c r="AE34">
+        <v>0</v>
+      </c>
+      <c r="AF34">
+        <v>475.7</v>
+      </c>
+      <c r="AG34">
+        <v>396.8</v>
+      </c>
+      <c r="AH34">
+        <v>0.8248656147043523</v>
+      </c>
+      <c r="AI34">
+        <v>0.6891206721715196</v>
+      </c>
+      <c r="AJ34">
+        <v>0.7971072719967859</v>
+      </c>
+      <c r="AK34">
+        <v>0.6490022898266273</v>
+      </c>
+      <c r="AL34">
+        <v>0</v>
+      </c>
+      <c r="AM34">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>Bangladesh</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
           <t>BRAC Bank PLC. (DSE:BRACBANK)</t>
         </is>
       </c>
-      <c r="C4" t="inlineStr">
+      <c r="C35" t="inlineStr">
         <is>
           <t>Bank (Money Center)</t>
         </is>
       </c>
-      <c r="D4">
+      <c r="D35">
         <v>0.153</v>
       </c>
-      <c r="E4">
+      <c r="E35">
         <v>0.177</v>
       </c>
-      <c r="G4">
-        <v>0</v>
-      </c>
-      <c r="H4">
-        <v>0</v>
-      </c>
-      <c r="I4">
-        <v>0</v>
-      </c>
-      <c r="J4">
-        <v>0</v>
-      </c>
-      <c r="K4">
+      <c r="G35">
+        <v>0</v>
+      </c>
+      <c r="H35">
+        <v>0</v>
+      </c>
+      <c r="I35">
+        <v>0</v>
+      </c>
+      <c r="J35">
+        <v>0</v>
+      </c>
+      <c r="K35">
         <v>92.40000000000001</v>
       </c>
-      <c r="L4">
+      <c r="L35">
         <v>0.2016586643387167</v>
       </c>
-      <c r="M4">
+      <c r="M35">
         <v>13.5</v>
       </c>
-      <c r="N4">
+      <c r="N35">
         <v>0.01864125932062966</v>
       </c>
-      <c r="O4">
+      <c r="O35">
         <v>0.1461038961038961</v>
       </c>
-      <c r="P4">
+      <c r="P35">
         <v>13.5</v>
       </c>
-      <c r="Q4">
+      <c r="Q35">
         <v>0.01864125932062966</v>
       </c>
-      <c r="R4">
+      <c r="R35">
         <v>0.1461038961038961</v>
       </c>
-      <c r="S4">
-        <v>0</v>
-      </c>
-      <c r="T4">
-        <v>0</v>
-      </c>
-      <c r="U4">
+      <c r="S35">
+        <v>0</v>
+      </c>
+      <c r="T35">
+        <v>0</v>
+      </c>
+      <c r="U35">
         <v>424.8</v>
       </c>
-      <c r="V4">
+      <c r="V35">
         <v>0.5865782932891466</v>
       </c>
-      <c r="W4">
+      <c r="W35">
         <v>0.1571161367114436</v>
       </c>
-      <c r="X4">
-        <v>0.137846789283938</v>
-      </c>
-      <c r="Y4">
-        <v>0.01926934742750566</v>
-      </c>
-      <c r="Z4">
+      <c r="X35">
+        <v>0.1378529393089656</v>
+      </c>
+      <c r="Y35">
+        <v>0.01926319740247806</v>
+      </c>
+      <c r="Z35">
         <v>0.4578337330135891</v>
       </c>
-      <c r="AA4">
-        <v>0</v>
-      </c>
-      <c r="AB4">
-        <v>0.1087608495671342</v>
-      </c>
-      <c r="AC4">
-        <v>-0.1087608495671342</v>
-      </c>
-      <c r="AD4">
+      <c r="AA35">
+        <v>0</v>
+      </c>
+      <c r="AB35">
+        <v>0.1087633772902472</v>
+      </c>
+      <c r="AC35">
+        <v>-0.1087633772902472</v>
+      </c>
+      <c r="AD35">
         <v>1037.8</v>
       </c>
-      <c r="AE4">
-        <v>0</v>
-      </c>
-      <c r="AF4">
+      <c r="AE35">
+        <v>0</v>
+      </c>
+      <c r="AF35">
         <v>1037.8</v>
       </c>
-      <c r="AG4">
+      <c r="AG35">
         <v>613</v>
       </c>
-      <c r="AH4">
+      <c r="AH35">
         <v>0.5889897843359818</v>
       </c>
-      <c r="AI4">
+      <c r="AI35">
         <v>0.5619449859215941</v>
       </c>
-      <c r="AJ4">
+      <c r="AJ35">
         <v>0.4584205803170804</v>
       </c>
-      <c r="AK4">
+      <c r="AK35">
         <v>0.4310829817158931</v>
       </c>
-      <c r="AL4">
-        <v>0</v>
-      </c>
-      <c r="AM4">
+      <c r="AL35">
+        <v>0</v>
+      </c>
+      <c r="AM35">
         <v>0</v>
       </c>
     </row>
